--- a/AAII_Financials/Quarterly/EOSE_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/EOSE_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="361" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="362" uniqueCount="92">
   <si>
     <t>EOSE</t>
   </si>
@@ -656,90 +656,90 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:W102"/>
+  <dimension ref="A5:X102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="23" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="24" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:24" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:24" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E7" s="2">
         <v>45199</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45107</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45016</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44926</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44834</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44742</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44651</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44561</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44469</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44377</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44286</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44196</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44104</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44012</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>43921</v>
       </c>
-      <c r="S7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="T7" s="2" t="s">
         <v>3</v>
       </c>
@@ -752,49 +752,52 @@
       <c r="W7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>6600</v>
+      </c>
+      <c r="E8" s="3">
         <v>700</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>200</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>8800</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>2700</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>6100</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>5900</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>3300</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>3100</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>700</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>600</v>
-      </c>
-      <c r="N8" s="3">
-        <v>200</v>
       </c>
       <c r="O8" s="3">
         <v>200</v>
       </c>
-      <c r="P8" s="3" t="s">
-        <v>3</v>
+      <c r="P8" s="3">
+        <v>200</v>
       </c>
       <c r="Q8" s="3" t="s">
         <v>3</v>
@@ -811,56 +814,59 @@
       <c r="U8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V8" s="3">
-        <v>0</v>
+      <c r="V8" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="W8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>30400</v>
+      </c>
+      <c r="E9" s="3">
         <v>21300</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>11200</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>26900</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>30800</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>50000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>36900</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>35600</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>21100</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>12900</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>12400</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>100</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>5500</v>
       </c>
-      <c r="P9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q9" s="3" t="s">
         <v>3</v>
       </c>
@@ -882,50 +888,53 @@
       <c r="W9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>-23800</v>
+      </c>
+      <c r="E10" s="3">
         <v>-20600</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>-11000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>-18100</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>-28100</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>-43900</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>-31000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>-32300</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>-18000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>-12200</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>-11800</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>100</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>-5300</v>
       </c>
-      <c r="P10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q10" s="3" t="s">
         <v>3</v>
       </c>
@@ -947,8 +956,11 @@
       <c r="W10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -972,50 +984,51 @@
       <c r="U11" s="3"/>
       <c r="V11" s="3"/>
       <c r="W11" s="3"/>
-    </row>
-    <row r="12" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X11" s="3"/>
+    </row>
+    <row r="12" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>5000</v>
+      </c>
+      <c r="E12" s="3">
         <v>3200</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>5000</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>5400</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>3600</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>4500</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>5500</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>5000</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>5400</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>5100</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>3600</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>5000</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>14000</v>
       </c>
-      <c r="P12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q12" s="3" t="s">
         <v>3</v>
       </c>
@@ -1037,8 +1050,11 @@
       <c r="W12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1102,49 +1118,52 @@
       <c r="W13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>0</v>
+      </c>
+      <c r="E14" s="3">
         <v>1000</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>7300</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>2400</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>4300</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>1400</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>2000</v>
       </c>
-      <c r="J14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K14" s="3">
-        <v>0</v>
+      <c r="K14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L14" s="3">
+        <v>0</v>
+      </c>
+      <c r="M14" s="3">
         <v>-1300</v>
       </c>
-      <c r="M14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="N14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O14" s="3">
-        <v>0</v>
-      </c>
-      <c r="P14" s="3" t="s">
-        <v>3</v>
+      <c r="O14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P14" s="3">
+        <v>0</v>
       </c>
       <c r="Q14" s="3" t="s">
         <v>3</v>
@@ -1152,8 +1171,8 @@
       <c r="R14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S14" s="3">
-        <v>0</v>
+      <c r="S14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="T14" s="3">
         <v>0</v>
@@ -1167,8 +1186,11 @@
       <c r="W14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:24" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1232,8 +1254,11 @@
       <c r="W15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:24" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1254,58 +1279,59 @@
       <c r="U16" s="3"/>
       <c r="V16" s="3"/>
       <c r="W16" s="3"/>
-    </row>
-    <row r="17" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X16" s="3"/>
+    </row>
+    <row r="17" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>48800</v>
+      </c>
+      <c r="E17" s="3">
         <v>38500</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>36700</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>48700</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>51300</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>70600</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>63300</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>55000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>40700</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>25700</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>49800</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>21800</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>37200</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>2000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>100</v>
       </c>
-      <c r="R17" s="3">
-        <v>0</v>
-      </c>
-      <c r="S17" s="3" t="s">
-        <v>3</v>
+      <c r="S17" s="3">
+        <v>0</v>
       </c>
       <c r="T17" s="3" t="s">
         <v>3</v>
@@ -1319,50 +1345,53 @@
       <c r="W17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-42200</v>
+      </c>
+      <c r="E18" s="3">
         <v>-37800</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-36500</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-39900</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-48600</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-64500</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-57400</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-51700</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-37600</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-25000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-49200</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-21600</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-37000</v>
       </c>
-      <c r="P18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1384,8 +1413,11 @@
       <c r="W18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1409,50 +1441,51 @@
       <c r="U19" s="3"/>
       <c r="V19" s="3"/>
       <c r="W19" s="3"/>
-    </row>
-    <row r="20" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X19" s="3"/>
+    </row>
+    <row r="20" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>9600</v>
+      </c>
+      <c r="E20" s="3">
         <v>62200</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-75500</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-13100</v>
-      </c>
-      <c r="G20" s="3">
-        <v>-400</v>
       </c>
       <c r="H20" s="3">
         <v>-400</v>
       </c>
       <c r="I20" s="3">
+        <v>-400</v>
+      </c>
+      <c r="J20" s="3">
         <v>3600</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>8400</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>8300</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>10700</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-4700</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>200</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-5900</v>
       </c>
-      <c r="P20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q20" s="3" t="s">
         <v>3</v>
       </c>
@@ -1474,47 +1507,50 @@
       <c r="W20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-30200</v>
+      </c>
+      <c r="E21" s="3">
         <v>26600</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-109500</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-50300</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-46000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-63300</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-52500</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-42300</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-28500</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-13700</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-53300</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-21000</v>
       </c>
-      <c r="O21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1539,50 +1575,53 @@
       <c r="W21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>8600</v>
+      </c>
+      <c r="E22" s="3">
         <v>9400</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>19600</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>18600</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>7600</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>5700</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>2900</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>2500</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>1300</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>3700</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>200</v>
       </c>
-      <c r="N22" s="3">
-        <v>0</v>
-      </c>
       <c r="O22" s="3">
+        <v>0</v>
+      </c>
+      <c r="P22" s="3">
         <v>23800</v>
       </c>
-      <c r="P22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q22" s="3" t="s">
         <v>3</v>
       </c>
@@ -1598,64 +1637,67 @@
       <c r="U22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V22" s="3">
-        <v>0</v>
+      <c r="V22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="W22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-41200</v>
+      </c>
+      <c r="E23" s="3">
         <v>14900</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-131600</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-71600</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-56600</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-70600</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-56700</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-45800</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-30600</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-18100</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-54000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-21500</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-66700</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-2000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-100</v>
       </c>
-      <c r="R23" s="3">
-        <v>0</v>
-      </c>
-      <c r="S23" s="3" t="s">
-        <v>3</v>
+      <c r="S23" s="3">
+        <v>0</v>
       </c>
       <c r="T23" s="3" t="s">
         <v>3</v>
@@ -1669,8 +1711,11 @@
       <c r="W23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1687,16 +1732,16 @@
         <v>0</v>
       </c>
       <c r="H24" s="3">
+        <v>0</v>
+      </c>
+      <c r="I24" s="3">
         <v>100</v>
       </c>
-      <c r="I24" s="3">
-        <v>0</v>
-      </c>
       <c r="J24" s="3">
         <v>0</v>
       </c>
-      <c r="K24" s="3" t="s">
-        <v>3</v>
+      <c r="K24" s="3">
+        <v>0</v>
       </c>
       <c r="L24" s="3" t="s">
         <v>3</v>
@@ -1713,8 +1758,8 @@
       <c r="P24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q24" s="3">
-        <v>0</v>
+      <c r="Q24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R24" s="3">
         <v>0</v>
@@ -1734,8 +1779,11 @@
       <c r="W24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1799,58 +1847,61 @@
       <c r="W25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-41200</v>
+      </c>
+      <c r="E26" s="3">
         <v>14900</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-131600</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-71600</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-56600</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-70700</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-56700</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-45800</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-30600</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-18100</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-54000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-21500</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-66700</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-2000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-100</v>
       </c>
-      <c r="R26" s="3">
-        <v>0</v>
-      </c>
-      <c r="S26" s="3" t="s">
-        <v>3</v>
+      <c r="S26" s="3">
+        <v>0</v>
       </c>
       <c r="T26" s="3" t="s">
         <v>3</v>
@@ -1864,58 +1915,61 @@
       <c r="W26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-41200</v>
+      </c>
+      <c r="E27" s="3">
         <v>14900</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-131600</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-71600</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-56600</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-70700</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-56700</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-45800</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-30600</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-18100</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-54000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-21500</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-66700</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-2000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-100</v>
       </c>
-      <c r="R27" s="3">
-        <v>0</v>
-      </c>
-      <c r="S27" s="3" t="s">
-        <v>3</v>
+      <c r="S27" s="3">
+        <v>0</v>
       </c>
       <c r="T27" s="3" t="s">
         <v>3</v>
@@ -1929,8 +1983,11 @@
       <c r="W27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1994,8 +2051,11 @@
       <c r="W28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2059,8 +2119,11 @@
       <c r="W29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2124,8 +2187,11 @@
       <c r="W30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2189,50 +2255,53 @@
       <c r="W31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-9600</v>
+      </c>
+      <c r="E32" s="3">
         <v>-62200</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>75500</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>13100</v>
-      </c>
-      <c r="G32" s="3">
-        <v>400</v>
       </c>
       <c r="H32" s="3">
         <v>400</v>
       </c>
       <c r="I32" s="3">
+        <v>400</v>
+      </c>
+      <c r="J32" s="3">
         <v>-3600</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-8400</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-8300</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-10700</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>4700</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-200</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>5900</v>
       </c>
-      <c r="P32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q32" s="3" t="s">
         <v>3</v>
       </c>
@@ -2254,58 +2323,61 @@
       <c r="W32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-41200</v>
+      </c>
+      <c r="E33" s="3">
         <v>14900</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-131600</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-71600</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-56600</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-70700</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-56700</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-45800</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-30600</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-18100</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-54000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-21500</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-66700</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-2000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-100</v>
       </c>
-      <c r="R33" s="3">
-        <v>0</v>
-      </c>
-      <c r="S33" s="3" t="s">
-        <v>3</v>
+      <c r="S33" s="3">
+        <v>0</v>
       </c>
       <c r="T33" s="3" t="s">
         <v>3</v>
@@ -2319,8 +2391,11 @@
       <c r="W33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2384,58 +2459,61 @@
       <c r="W34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-41200</v>
+      </c>
+      <c r="E35" s="3">
         <v>14900</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-131600</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-71600</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-56600</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-70700</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-56700</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-45800</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-30600</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-18100</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-54000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-21500</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-66700</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-2000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-100</v>
       </c>
-      <c r="R35" s="3">
-        <v>0</v>
-      </c>
-      <c r="S35" s="3" t="s">
-        <v>3</v>
+      <c r="S35" s="3">
+        <v>0</v>
       </c>
       <c r="T35" s="3" t="s">
         <v>3</v>
@@ -2449,64 +2527,67 @@
       <c r="W35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E38" s="2">
         <v>45199</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45107</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45016</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44926</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44834</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44742</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44651</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44561</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44469</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44377</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44286</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44196</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44104</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44012</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>43921</v>
       </c>
-      <c r="S38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="T38" s="2" t="s">
         <v>3</v>
       </c>
@@ -2519,8 +2600,11 @@
       <c r="W38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2544,8 +2628,9 @@
       <c r="U39" s="3"/>
       <c r="V39" s="3"/>
       <c r="W39" s="3"/>
-    </row>
-    <row r="40" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X39" s="3"/>
+    </row>
+    <row r="40" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2569,58 +2654,59 @@
       <c r="U40" s="3"/>
       <c r="V40" s="3"/>
       <c r="W40" s="3"/>
-    </row>
-    <row r="41" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X40" s="3"/>
+    </row>
+    <row r="41" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>69500</v>
+      </c>
+      <c r="E41" s="3">
         <v>58000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>23200</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>16100</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>17100</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>38400</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>16300</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>55400</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>104800</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>144200</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>74700</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>100700</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>121900</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>300</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>500</v>
       </c>
-      <c r="R41" s="3">
-        <v>0</v>
-      </c>
-      <c r="S41" s="3" t="s">
-        <v>3</v>
+      <c r="S41" s="3">
+        <v>0</v>
       </c>
       <c r="T41" s="3" t="s">
         <v>3</v>
@@ -2634,8 +2720,11 @@
       <c r="W41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2699,58 +2788,61 @@
       <c r="W42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>20500</v>
+      </c>
+      <c r="E43" s="3">
         <v>4000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>3600</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>7500</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>3600</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>6400</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>3600</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>3700</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>2000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>2400</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>400</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>300</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>100</v>
       </c>
-      <c r="P43" s="3">
-        <v>0</v>
-      </c>
       <c r="Q43" s="3">
         <v>0</v>
       </c>
       <c r="R43" s="3">
         <v>0</v>
       </c>
-      <c r="S43" s="3" t="s">
-        <v>3</v>
+      <c r="S43" s="3">
+        <v>0</v>
       </c>
       <c r="T43" s="3" t="s">
         <v>3</v>
@@ -2764,50 +2856,53 @@
       <c r="W43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>17100</v>
+      </c>
+      <c r="E44" s="3">
         <v>20600</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>16600</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>14100</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>23300</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>23200</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>12900</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>10300</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>13000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>5000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>4400</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>100</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>200</v>
       </c>
-      <c r="P44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q44" s="3" t="s">
         <v>3</v>
       </c>
@@ -2823,62 +2918,65 @@
       <c r="U44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V44" s="3">
-        <v>0</v>
+      <c r="V44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="W44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>15300</v>
+      </c>
+      <c r="E45" s="3">
         <v>25900</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>20500</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>12300</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>11300</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>13600</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>27600</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>26800</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>22700</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>17400</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>12200</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>6200</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>5200</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>200</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>300</v>
       </c>
-      <c r="R45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S45" s="3" t="s">
         <v>3</v>
       </c>
@@ -2894,58 +2992,61 @@
       <c r="W45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>122300</v>
+      </c>
+      <c r="E46" s="3">
         <v>108500</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>64000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>50000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>55100</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>81600</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>60500</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>96200</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>142600</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>169100</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>91700</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>107400</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>127400</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>600</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>800</v>
       </c>
-      <c r="R46" s="3">
-        <v>0</v>
-      </c>
-      <c r="S46" s="3" t="s">
-        <v>3</v>
+      <c r="S46" s="3">
+        <v>0</v>
       </c>
       <c r="T46" s="3" t="s">
         <v>3</v>
@@ -2959,13 +3060,16 @@
       <c r="W46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3">
-        <v>800</v>
+      <c r="D47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="E47" s="3">
         <v>800</v>
@@ -2977,32 +3081,32 @@
         <v>800</v>
       </c>
       <c r="H47" s="3">
-        <v>3700</v>
+        <v>800</v>
       </c>
       <c r="I47" s="3">
         <v>3700</v>
       </c>
       <c r="J47" s="3">
-        <v>3500</v>
+        <v>3700</v>
       </c>
       <c r="K47" s="3">
         <v>3500</v>
       </c>
       <c r="L47" s="3">
+        <v>3500</v>
+      </c>
+      <c r="M47" s="3">
         <v>4700</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>4100</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>11100</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>3700</v>
       </c>
-      <c r="P47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q47" s="3" t="s">
         <v>3</v>
       </c>
@@ -3018,56 +3122,59 @@
       <c r="U47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V47" s="3">
-        <v>0</v>
+      <c r="V47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="W47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>41900</v>
+      </c>
+      <c r="E48" s="3">
         <v>24300</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>23900</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>28700</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>31500</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>34400</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>25800</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>19500</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>16400</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>10300</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>8400</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>8000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>5700</v>
       </c>
-      <c r="P48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q48" s="3" t="s">
         <v>3</v>
       </c>
@@ -3083,14 +3190,17 @@
       <c r="U48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V48" s="3">
-        <v>0</v>
+      <c r="V48" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="W48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -3098,13 +3208,13 @@
         <v>4600</v>
       </c>
       <c r="E49" s="3">
-        <v>4700</v>
+        <v>4600</v>
       </c>
       <c r="F49" s="3">
         <v>4700</v>
       </c>
       <c r="G49" s="3">
-        <v>4600</v>
+        <v>4700</v>
       </c>
       <c r="H49" s="3">
         <v>4600</v>
@@ -3125,13 +3235,13 @@
         <v>4600</v>
       </c>
       <c r="N49" s="3">
-        <v>300</v>
+        <v>4600</v>
       </c>
       <c r="O49" s="3">
         <v>300</v>
       </c>
-      <c r="P49" s="3" t="s">
-        <v>3</v>
+      <c r="P49" s="3">
+        <v>300</v>
       </c>
       <c r="Q49" s="3" t="s">
         <v>3</v>
@@ -3148,14 +3258,17 @@
       <c r="U49" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V49" s="3">
-        <v>0</v>
+      <c r="V49" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="W49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3219,8 +3332,11 @@
       <c r="W50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3284,59 +3400,62 @@
       <c r="W51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>17600</v>
+      </c>
+      <c r="E52" s="3">
         <v>15900</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>15600</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>15500</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>14800</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>14200</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>3200</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>3100</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>2100</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>1400</v>
-      </c>
-      <c r="M52" s="3">
-        <v>1000</v>
       </c>
       <c r="N52" s="3">
         <v>1000</v>
       </c>
       <c r="O52" s="3">
+        <v>1000</v>
+      </c>
+      <c r="P52" s="3">
         <v>1200</v>
-      </c>
-      <c r="P52" s="3">
-        <v>176800</v>
       </c>
       <c r="Q52" s="3">
         <v>176800</v>
       </c>
       <c r="R52" s="3">
+        <v>176800</v>
+      </c>
+      <c r="S52" s="3">
         <v>100</v>
       </c>
-      <c r="S52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T52" s="3" t="s">
         <v>3</v>
       </c>
@@ -3349,8 +3468,11 @@
       <c r="W52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3414,59 +3536,62 @@
       <c r="W53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>186500</v>
+      </c>
+      <c r="E54" s="3">
         <v>154100</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>109000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>99700</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>106800</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>138500</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>97700</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>126900</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>169200</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>190100</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>109900</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>127800</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>138300</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>177300</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>177500</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>100</v>
       </c>
-      <c r="S54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3479,8 +3604,11 @@
       <c r="W54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3504,8 +3632,9 @@
       <c r="U55" s="3"/>
       <c r="V55" s="3"/>
       <c r="W55" s="3"/>
-    </row>
-    <row r="56" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X55" s="3"/>
+    </row>
+    <row r="56" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3529,58 +3658,59 @@
       <c r="U56" s="3"/>
       <c r="V56" s="3"/>
       <c r="W56" s="3"/>
-    </row>
-    <row r="57" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X56" s="3"/>
+    </row>
+    <row r="57" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>20500</v>
+      </c>
+      <c r="E57" s="3">
         <v>13800</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>15400</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>32500</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>34700</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>35500</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>29100</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>11700</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>13700</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>13200</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>15200</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>20200</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>11400</v>
       </c>
-      <c r="P57" s="3">
-        <v>0</v>
-      </c>
       <c r="Q57" s="3">
         <v>0</v>
       </c>
       <c r="R57" s="3">
         <v>0</v>
       </c>
-      <c r="S57" s="3" t="s">
-        <v>3</v>
+      <c r="S57" s="3">
+        <v>0</v>
       </c>
       <c r="T57" s="3" t="s">
         <v>3</v>
@@ -3594,59 +3724,62 @@
       <c r="W57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>3400</v>
+      </c>
+      <c r="E58" s="3">
         <v>3200</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>3100</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>11200</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>5600</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>2900</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>14000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>6700</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>6600</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>6500</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>6100</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>1200</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>1100</v>
       </c>
-      <c r="P58" s="3">
-        <v>0</v>
-      </c>
       <c r="Q58" s="3">
         <v>0</v>
       </c>
       <c r="R58" s="3">
+        <v>0</v>
+      </c>
+      <c r="S58" s="3">
         <v>100</v>
       </c>
-      <c r="S58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T58" s="3" t="s">
         <v>3</v>
       </c>
@@ -3659,55 +3792,58 @@
       <c r="W58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>36900</v>
+      </c>
+      <c r="E59" s="3">
         <v>29700</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>24500</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>21900</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>20300</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>17500</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>16600</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>15500</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>9600</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>1200</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>3400</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>800</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>1700</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>1800</v>
       </c>
-      <c r="Q59" s="3">
-        <v>0</v>
-      </c>
-      <c r="R59" s="3" t="s">
-        <v>3</v>
+      <c r="R59" s="3">
+        <v>0</v>
       </c>
       <c r="S59" s="3" t="s">
         <v>3</v>
@@ -3724,58 +3860,61 @@
       <c r="W59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>60900</v>
+      </c>
+      <c r="E60" s="3">
         <v>46800</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>43000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>65700</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>60600</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>55800</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>59600</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>33800</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>29900</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>20900</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>24600</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>22200</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>14100</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>1900</v>
-      </c>
-      <c r="Q60" s="3">
-        <v>100</v>
       </c>
       <c r="R60" s="3">
         <v>100</v>
       </c>
-      <c r="S60" s="3" t="s">
-        <v>3</v>
+      <c r="S60" s="3">
+        <v>100</v>
       </c>
       <c r="T60" s="3" t="s">
         <v>3</v>
@@ -3789,50 +3928,53 @@
       <c r="W60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>200600</v>
+      </c>
+      <c r="E61" s="3">
         <v>204100</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>229500</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>198600</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>170400</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>160800</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>90300</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>95300</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>102700</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>106800</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>13500</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>100</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>300</v>
       </c>
-      <c r="P61" s="3">
-        <v>0</v>
-      </c>
       <c r="Q61" s="3">
         <v>0</v>
       </c>
@@ -3854,50 +3996,53 @@
       <c r="W61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>35800</v>
+      </c>
+      <c r="E62" s="3">
         <v>31600</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>65900</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>11100</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>8500</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>10100</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>5700</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>8000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>4200</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>3900</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>3100</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>3700</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>800</v>
       </c>
-      <c r="P62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q62" s="3" t="s">
         <v>3</v>
       </c>
@@ -3913,14 +4058,17 @@
       <c r="U62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V62" s="3">
-        <v>0</v>
+      <c r="V62" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="W62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3984,8 +4132,11 @@
       <c r="W63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4049,8 +4200,11 @@
       <c r="W64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4114,58 +4268,61 @@
       <c r="W65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>297300</v>
+      </c>
+      <c r="E66" s="3">
         <v>282400</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>338500</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>275300</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>239500</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>226800</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>155600</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>137100</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>136700</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>131700</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>41300</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>26000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>15200</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>1900</v>
-      </c>
-      <c r="Q66" s="3">
-        <v>100</v>
       </c>
       <c r="R66" s="3">
         <v>100</v>
       </c>
-      <c r="S66" s="3" t="s">
-        <v>3</v>
+      <c r="S66" s="3">
+        <v>100</v>
       </c>
       <c r="T66" s="3" t="s">
         <v>3</v>
@@ -4179,8 +4336,11 @@
       <c r="W66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4204,8 +4364,9 @@
       <c r="U67" s="3"/>
       <c r="V67" s="3"/>
       <c r="W67" s="3"/>
-    </row>
-    <row r="68" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X67" s="3"/>
+    </row>
+    <row r="68" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4269,8 +4430,11 @@
       <c r="W68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4334,8 +4498,11 @@
       <c r="W69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4399,8 +4566,11 @@
       <c r="W70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4464,58 +4634,61 @@
       <c r="W71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-875800</v>
+      </c>
+      <c r="E72" s="3">
         <v>-834600</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-849600</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-717900</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-646300</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-589700</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-519000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-462300</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-416500</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-385900</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-367800</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-313800</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-290800</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-2000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-100</v>
       </c>
-      <c r="R72" s="3">
-        <v>0</v>
-      </c>
-      <c r="S72" s="3" t="s">
-        <v>3</v>
+      <c r="S72" s="3">
+        <v>0</v>
       </c>
       <c r="T72" s="3" t="s">
         <v>3</v>
@@ -4529,8 +4702,11 @@
       <c r="W72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4594,8 +4770,11 @@
       <c r="W73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4659,8 +4838,11 @@
       <c r="W74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4724,58 +4906,61 @@
       <c r="W75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>-110800</v>
+      </c>
+      <c r="E76" s="3">
         <v>-128300</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>-229500</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>-175600</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>-132700</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>-88300</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>-57800</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>-10200</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>32400</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>58400</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>68600</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>101800</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>123100</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>175500</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>177400</v>
       </c>
-      <c r="R76" s="3">
-        <v>0</v>
-      </c>
-      <c r="S76" s="3" t="s">
-        <v>3</v>
+      <c r="S76" s="3">
+        <v>0</v>
       </c>
       <c r="T76" s="3" t="s">
         <v>3</v>
@@ -4789,8 +4974,11 @@
       <c r="W76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4854,64 +5042,67 @@
       <c r="W77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:24" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:24" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E80" s="2">
         <v>45199</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45107</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45016</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44926</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44834</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44742</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44651</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44561</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44469</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44377</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44286</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44196</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44104</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44012</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>43921</v>
       </c>
-      <c r="S80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="T80" s="2" t="s">
         <v>3</v>
       </c>
@@ -4924,58 +5115,61 @@
       <c r="W80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-41200</v>
+      </c>
+      <c r="E81" s="3">
         <v>14900</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-131600</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-71600</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-56600</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-70700</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-56700</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-45800</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-30600</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-18100</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-54000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-21500</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-66700</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-2000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-100</v>
       </c>
-      <c r="R81" s="3">
-        <v>0</v>
-      </c>
-      <c r="S81" s="3" t="s">
-        <v>3</v>
+      <c r="S81" s="3">
+        <v>0</v>
       </c>
       <c r="T81" s="3" t="s">
         <v>3</v>
@@ -4989,8 +5183,11 @@
       <c r="W81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5014,47 +5211,48 @@
       <c r="U82" s="3"/>
       <c r="V82" s="3"/>
       <c r="W82" s="3"/>
-    </row>
-    <row r="83" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X82" s="3"/>
+    </row>
+    <row r="83" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>2400</v>
+      </c>
+      <c r="E83" s="3">
         <v>2200</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>2500</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>2700</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>3000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>1600</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>1300</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>1000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>800</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>700</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>600</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>500</v>
       </c>
-      <c r="O83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P83" s="3" t="s">
         <v>3</v>
       </c>
@@ -5070,8 +5268,8 @@
       <c r="T83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U83" s="3">
-        <v>0</v>
+      <c r="U83" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="V83" s="3">
         <v>0</v>
@@ -5079,8 +5277,11 @@
       <c r="W83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5144,8 +5345,11 @@
       <c r="W84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5209,8 +5413,11 @@
       <c r="W85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5274,8 +5481,11 @@
       <c r="W86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5339,8 +5549,11 @@
       <c r="W87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5404,58 +5617,61 @@
       <c r="W88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-37400</v>
+      </c>
+      <c r="E89" s="3">
         <v>-32000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-45100</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-30500</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-37700</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-72100</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-44300</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-42700</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-35500</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-31700</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-39200</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-9700</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-26100</v>
-      </c>
-      <c r="P89" s="3">
-        <v>-200</v>
       </c>
       <c r="Q89" s="3">
         <v>-200</v>
       </c>
       <c r="R89" s="3">
-        <v>0</v>
-      </c>
-      <c r="S89" s="3" t="s">
-        <v>3</v>
+        <v>-200</v>
+      </c>
+      <c r="S89" s="3">
+        <v>0</v>
       </c>
       <c r="T89" s="3" t="s">
         <v>3</v>
@@ -5469,8 +5685,11 @@
       <c r="W89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5494,47 +5713,48 @@
       <c r="U90" s="3"/>
       <c r="V90" s="3"/>
       <c r="W90" s="3"/>
-    </row>
-    <row r="91" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X90" s="3"/>
+    </row>
+    <row r="91" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-8300</v>
+      </c>
+      <c r="E91" s="3">
         <v>-11100</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-7200</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-2900</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-1300</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-7300</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-6400</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-5100</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-4200</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-3800</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-3100</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-4500</v>
       </c>
-      <c r="O91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P91" s="3" t="s">
         <v>3</v>
       </c>
@@ -5550,8 +5770,8 @@
       <c r="T91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U91" s="3">
-        <v>0</v>
+      <c r="U91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="V91" s="3">
         <v>0</v>
@@ -5559,8 +5779,11 @@
       <c r="W91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5624,8 +5847,11 @@
       <c r="W92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5689,52 +5915,55 @@
       <c r="W93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-8300</v>
+      </c>
+      <c r="E94" s="3">
         <v>-11100</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-7200</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-2900</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>1900</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-7300</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-6600</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-5100</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-3100</v>
-      </c>
-      <c r="L94" s="3">
-        <v>-4400</v>
       </c>
       <c r="M94" s="3">
         <v>-4400</v>
       </c>
       <c r="N94" s="3">
+        <v>-4400</v>
+      </c>
+      <c r="O94" s="3">
         <v>-11400</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>170100</v>
       </c>
-      <c r="P94" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q94" s="3" t="s">
-        <v>3</v>
+      <c r="Q94" s="3">
+        <v>0</v>
       </c>
       <c r="R94" s="3" t="s">
         <v>3</v>
@@ -5748,14 +5977,17 @@
       <c r="U94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V94" s="3">
-        <v>0</v>
+      <c r="V94" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="W94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5779,8 +6011,9 @@
       <c r="U95" s="3"/>
       <c r="V95" s="3"/>
       <c r="W95" s="3"/>
-    </row>
-    <row r="96" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X95" s="3"/>
+    </row>
+    <row r="96" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -5844,8 +6077,11 @@
       <c r="W96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5909,8 +6145,11 @@
       <c r="W97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5974,8 +6213,11 @@
       <c r="W98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6039,59 +6281,62 @@
       <c r="W99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>57300</v>
+      </c>
+      <c r="E100" s="3">
         <v>78000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>60200</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>32500</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>16000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>112900</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>11800</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-1200</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-400</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>106200</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>17600</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-100</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-23300</v>
       </c>
-      <c r="P100" s="3">
-        <v>0</v>
-      </c>
       <c r="Q100" s="3">
+        <v>0</v>
+      </c>
+      <c r="R100" s="3">
         <v>177500</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>100</v>
       </c>
-      <c r="S100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T100" s="3" t="s">
         <v>3</v>
       </c>
@@ -6104,8 +6349,11 @@
       <c r="W100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -6124,8 +6372,8 @@
       <c r="H101" s="3">
         <v>0</v>
       </c>
-      <c r="I101" s="3" t="s">
-        <v>3</v>
+      <c r="I101" s="3">
+        <v>0</v>
       </c>
       <c r="J101" s="3" t="s">
         <v>3</v>
@@ -6142,8 +6390,8 @@
       <c r="N101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O101" s="3">
-        <v>0</v>
+      <c r="O101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P101" s="3">
         <v>0</v>
@@ -6169,58 +6417,61 @@
       <c r="W101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:24" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>11600</v>
+      </c>
+      <c r="E102" s="3">
         <v>34900</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>7900</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-900</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-19800</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>33500</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-39100</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-49100</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-39000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>70000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-26000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-21100</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>120700</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-200</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>500</v>
       </c>
-      <c r="R102" s="3">
-        <v>0</v>
-      </c>
-      <c r="S102" s="3" t="s">
-        <v>3</v>
+      <c r="S102" s="3">
+        <v>0</v>
       </c>
       <c r="T102" s="3" t="s">
         <v>3</v>
@@ -6232,6 +6483,9 @@
         <v>3</v>
       </c>
       <c r="W102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/EOSE_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/EOSE_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="362" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="363" uniqueCount="92">
   <si>
     <t>EOSE</t>
   </si>
@@ -656,93 +656,94 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:X102"/>
+  <dimension ref="A5:Y102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="24" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="25" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E7" s="2">
         <v>45291</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45199</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45107</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45016</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44926</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44834</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44742</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44651</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44561</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44469</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44377</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44286</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44196</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44104</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44012</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43921</v>
       </c>
-      <c r="T7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="U7" s="2" t="s">
         <v>3</v>
       </c>
@@ -755,8 +756,11 @@
       <c r="X7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
@@ -764,43 +768,43 @@
         <v>6600</v>
       </c>
       <c r="E8" s="3">
+        <v>6600</v>
+      </c>
+      <c r="F8" s="3">
         <v>700</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>200</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>8800</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>2700</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>6100</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>5900</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>3300</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>3100</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>700</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>600</v>
-      </c>
-      <c r="O8" s="3">
-        <v>200</v>
       </c>
       <c r="P8" s="3">
         <v>200</v>
       </c>
-      <c r="Q8" s="3" t="s">
-        <v>3</v>
+      <c r="Q8" s="3">
+        <v>200</v>
       </c>
       <c r="R8" s="3" t="s">
         <v>3</v>
@@ -817,59 +821,62 @@
       <c r="V8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="W8" s="3">
-        <v>0</v>
+      <c r="W8" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="X8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>28200</v>
+      </c>
+      <c r="E9" s="3">
         <v>30400</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>21300</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>11200</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>26900</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>30800</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>50000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>36900</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>35600</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>21100</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>12900</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>12400</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>100</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>5500</v>
       </c>
-      <c r="Q9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R9" s="3" t="s">
         <v>3</v>
       </c>
@@ -891,53 +898,56 @@
       <c r="X9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>-21600</v>
+      </c>
+      <c r="E10" s="3">
         <v>-23800</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>-20600</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>-11000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>-18100</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>-28100</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>-43900</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>-31000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>-32300</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>-18000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>-12200</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>-11800</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>100</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>-5300</v>
       </c>
-      <c r="Q10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R10" s="3" t="s">
         <v>3</v>
       </c>
@@ -959,8 +969,11 @@
       <c r="X10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -985,53 +998,54 @@
       <c r="V11" s="3"/>
       <c r="W11" s="3"/>
       <c r="X11" s="3"/>
-    </row>
-    <row r="12" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y11" s="3"/>
+    </row>
+    <row r="12" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>5200</v>
+      </c>
+      <c r="E12" s="3">
         <v>5000</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>3200</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>5000</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>5400</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>3600</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>4500</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>5500</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>5000</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>5400</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>5100</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>3600</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>5000</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>14000</v>
       </c>
-      <c r="Q12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R12" s="3" t="s">
         <v>3</v>
       </c>
@@ -1053,8 +1067,11 @@
       <c r="X12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1121,52 +1138,55 @@
       <c r="X13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E14" s="3">
+        <v>0</v>
+      </c>
+      <c r="F14" s="3">
         <v>1000</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>7300</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>2400</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>4300</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>1400</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>2000</v>
       </c>
-      <c r="K14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L14" s="3">
-        <v>0</v>
+      <c r="L14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M14" s="3">
+        <v>0</v>
+      </c>
+      <c r="N14" s="3">
         <v>-1300</v>
       </c>
-      <c r="N14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="O14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P14" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q14" s="3" t="s">
-        <v>3</v>
+      <c r="P14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q14" s="3">
+        <v>0</v>
       </c>
       <c r="R14" s="3" t="s">
         <v>3</v>
@@ -1174,8 +1194,8 @@
       <c r="S14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T14" s="3">
-        <v>0</v>
+      <c r="T14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="U14" s="3">
         <v>0</v>
@@ -1189,8 +1209,11 @@
       <c r="X14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1257,8 +1280,11 @@
       <c r="X15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:25" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1280,61 +1306,62 @@
       <c r="V16" s="3"/>
       <c r="W16" s="3"/>
       <c r="X16" s="3"/>
-    </row>
-    <row r="17" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y16" s="3"/>
+    </row>
+    <row r="17" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>47700</v>
+      </c>
+      <c r="E17" s="3">
         <v>48800</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>38500</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>36700</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>48700</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>51300</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>70600</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>63300</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>55000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>40700</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>25700</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>49800</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>21800</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>37200</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>2000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>100</v>
       </c>
-      <c r="S17" s="3">
-        <v>0</v>
-      </c>
-      <c r="T17" s="3" t="s">
-        <v>3</v>
+      <c r="T17" s="3">
+        <v>0</v>
       </c>
       <c r="U17" s="3" t="s">
         <v>3</v>
@@ -1348,53 +1375,56 @@
       <c r="X17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-41100</v>
+      </c>
+      <c r="E18" s="3">
         <v>-42200</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-37800</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-36500</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-39900</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-48600</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-64500</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-57400</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-51700</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-37600</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-25000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-49200</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-21600</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-37000</v>
       </c>
-      <c r="Q18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1416,8 +1446,11 @@
       <c r="X18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1442,53 +1475,54 @@
       <c r="V19" s="3"/>
       <c r="W19" s="3"/>
       <c r="X19" s="3"/>
-    </row>
-    <row r="20" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y19" s="3"/>
+    </row>
+    <row r="20" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>3600</v>
+      </c>
+      <c r="E20" s="3">
         <v>9600</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>62200</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-75500</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-13100</v>
-      </c>
-      <c r="H20" s="3">
-        <v>-400</v>
       </c>
       <c r="I20" s="3">
         <v>-400</v>
       </c>
       <c r="J20" s="3">
+        <v>-400</v>
+      </c>
+      <c r="K20" s="3">
         <v>3600</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>8400</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>8300</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>10700</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-4700</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>200</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-5900</v>
       </c>
-      <c r="Q20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R20" s="3" t="s">
         <v>3</v>
       </c>
@@ -1510,50 +1544,53 @@
       <c r="X20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-36400</v>
+      </c>
+      <c r="E21" s="3">
         <v>-30200</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>26600</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-109500</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-50300</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-46000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-63300</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-52500</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-42300</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-28500</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-13700</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-53300</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-21000</v>
       </c>
-      <c r="P21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1578,53 +1615,56 @@
       <c r="X21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>9100</v>
+      </c>
+      <c r="E22" s="3">
         <v>8600</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>9400</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>19600</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>18600</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>7600</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>5700</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>2900</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>2500</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>1300</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>3700</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>200</v>
       </c>
-      <c r="O22" s="3">
-        <v>0</v>
-      </c>
       <c r="P22" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q22" s="3">
         <v>23800</v>
       </c>
-      <c r="Q22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R22" s="3" t="s">
         <v>3</v>
       </c>
@@ -1640,67 +1680,70 @@
       <c r="V22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="W22" s="3">
-        <v>0</v>
+      <c r="W22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="X22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-46700</v>
+      </c>
+      <c r="E23" s="3">
         <v>-41200</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>14900</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-131600</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-71600</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-56600</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-70600</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-56700</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-45800</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-30600</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-18100</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-54000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-21500</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-66700</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-2000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-100</v>
       </c>
-      <c r="S23" s="3">
-        <v>0</v>
-      </c>
-      <c r="T23" s="3" t="s">
-        <v>3</v>
+      <c r="T23" s="3">
+        <v>0</v>
       </c>
       <c r="U23" s="3" t="s">
         <v>3</v>
@@ -1714,8 +1757,11 @@
       <c r="X23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1735,16 +1781,16 @@
         <v>0</v>
       </c>
       <c r="I24" s="3">
+        <v>0</v>
+      </c>
+      <c r="J24" s="3">
         <v>100</v>
       </c>
-      <c r="J24" s="3">
-        <v>0</v>
-      </c>
       <c r="K24" s="3">
         <v>0</v>
       </c>
-      <c r="L24" s="3" t="s">
-        <v>3</v>
+      <c r="L24" s="3">
+        <v>0</v>
       </c>
       <c r="M24" s="3" t="s">
         <v>3</v>
@@ -1761,8 +1807,8 @@
       <c r="Q24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R24" s="3">
-        <v>0</v>
+      <c r="R24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="S24" s="3">
         <v>0</v>
@@ -1782,8 +1828,11 @@
       <c r="X24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1850,61 +1899,64 @@
       <c r="X25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-46700</v>
+      </c>
+      <c r="E26" s="3">
         <v>-41200</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>14900</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-131600</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-71600</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-56600</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-70700</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-56700</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-45800</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-30600</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-18100</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-54000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-21500</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-66700</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-2000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-100</v>
       </c>
-      <c r="S26" s="3">
-        <v>0</v>
-      </c>
-      <c r="T26" s="3" t="s">
-        <v>3</v>
+      <c r="T26" s="3">
+        <v>0</v>
       </c>
       <c r="U26" s="3" t="s">
         <v>3</v>
@@ -1918,61 +1970,64 @@
       <c r="X26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-46700</v>
+      </c>
+      <c r="E27" s="3">
         <v>-41200</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>14900</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-131600</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-71600</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-56600</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-70700</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-56700</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-45800</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-30600</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-18100</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-54000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-21500</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-66700</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-2000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-100</v>
       </c>
-      <c r="S27" s="3">
-        <v>0</v>
-      </c>
-      <c r="T27" s="3" t="s">
-        <v>3</v>
+      <c r="T27" s="3">
+        <v>0</v>
       </c>
       <c r="U27" s="3" t="s">
         <v>3</v>
@@ -1986,8 +2041,11 @@
       <c r="X27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2054,8 +2112,11 @@
       <c r="X28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2122,8 +2183,11 @@
       <c r="X29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2190,8 +2254,11 @@
       <c r="X30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2258,53 +2325,56 @@
       <c r="X31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-3600</v>
+      </c>
+      <c r="E32" s="3">
         <v>-9600</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-62200</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>75500</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>13100</v>
-      </c>
-      <c r="H32" s="3">
-        <v>400</v>
       </c>
       <c r="I32" s="3">
         <v>400</v>
       </c>
       <c r="J32" s="3">
+        <v>400</v>
+      </c>
+      <c r="K32" s="3">
         <v>-3600</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-8400</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-8300</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-10700</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>4700</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-200</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>5900</v>
       </c>
-      <c r="Q32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R32" s="3" t="s">
         <v>3</v>
       </c>
@@ -2326,61 +2396,64 @@
       <c r="X32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-46700</v>
+      </c>
+      <c r="E33" s="3">
         <v>-41200</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>14900</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-131600</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-71600</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-56600</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-70700</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-56700</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-45800</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-30600</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-18100</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-54000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-21500</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-66700</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-2000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-100</v>
       </c>
-      <c r="S33" s="3">
-        <v>0</v>
-      </c>
-      <c r="T33" s="3" t="s">
-        <v>3</v>
+      <c r="T33" s="3">
+        <v>0</v>
       </c>
       <c r="U33" s="3" t="s">
         <v>3</v>
@@ -2394,8 +2467,11 @@
       <c r="X33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2462,61 +2538,64 @@
       <c r="X34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-46700</v>
+      </c>
+      <c r="E35" s="3">
         <v>-41200</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>14900</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-131600</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-71600</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-56600</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-70700</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-56700</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-45800</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-30600</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-18100</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-54000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-21500</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-66700</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-2000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-100</v>
       </c>
-      <c r="S35" s="3">
-        <v>0</v>
-      </c>
-      <c r="T35" s="3" t="s">
-        <v>3</v>
+      <c r="T35" s="3">
+        <v>0</v>
       </c>
       <c r="U35" s="3" t="s">
         <v>3</v>
@@ -2530,67 +2609,70 @@
       <c r="X35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E38" s="2">
         <v>45291</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45199</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45107</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45016</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44926</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44834</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44742</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44651</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44561</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44469</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44377</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44286</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44196</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44104</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44012</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43921</v>
       </c>
-      <c r="T38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="U38" s="2" t="s">
         <v>3</v>
       </c>
@@ -2603,8 +2685,11 @@
       <c r="X38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2629,8 +2714,9 @@
       <c r="V39" s="3"/>
       <c r="W39" s="3"/>
       <c r="X39" s="3"/>
-    </row>
-    <row r="40" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y39" s="3"/>
+    </row>
+    <row r="40" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2655,61 +2741,62 @@
       <c r="V40" s="3"/>
       <c r="W40" s="3"/>
       <c r="X40" s="3"/>
-    </row>
-    <row r="41" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y40" s="3"/>
+    </row>
+    <row r="41" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>31800</v>
+      </c>
+      <c r="E41" s="3">
         <v>69500</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>58000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>23200</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>16100</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>17100</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>38400</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>16300</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>55400</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>104800</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>144200</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>74700</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>100700</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>121900</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>300</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>500</v>
       </c>
-      <c r="S41" s="3">
-        <v>0</v>
-      </c>
-      <c r="T41" s="3" t="s">
-        <v>3</v>
+      <c r="T41" s="3">
+        <v>0</v>
       </c>
       <c r="U41" s="3" t="s">
         <v>3</v>
@@ -2723,8 +2810,11 @@
       <c r="X41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2791,61 +2881,64 @@
       <c r="X42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>27300</v>
+      </c>
+      <c r="E43" s="3">
         <v>20500</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>4000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>3600</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>7500</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>3600</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>6400</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>3600</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>3700</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>2000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>2400</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>400</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>300</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>100</v>
       </c>
-      <c r="Q43" s="3">
-        <v>0</v>
-      </c>
       <c r="R43" s="3">
         <v>0</v>
       </c>
       <c r="S43" s="3">
         <v>0</v>
       </c>
-      <c r="T43" s="3" t="s">
-        <v>3</v>
+      <c r="T43" s="3">
+        <v>0</v>
       </c>
       <c r="U43" s="3" t="s">
         <v>3</v>
@@ -2859,53 +2952,56 @@
       <c r="X43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>14400</v>
+      </c>
+      <c r="E44" s="3">
         <v>17100</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>20600</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>16600</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>14100</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>23300</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>23200</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>12900</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>10300</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>13000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>5000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>4400</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>100</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>200</v>
       </c>
-      <c r="Q44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R44" s="3" t="s">
         <v>3</v>
       </c>
@@ -2921,65 +3017,68 @@
       <c r="V44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="W44" s="3">
-        <v>0</v>
+      <c r="W44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="X44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>13500</v>
+      </c>
+      <c r="E45" s="3">
         <v>15300</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>25900</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>20500</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>12300</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>11300</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>13600</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>27600</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>26800</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>22700</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>17400</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>12200</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>6200</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>5200</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>200</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>300</v>
       </c>
-      <c r="S45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T45" s="3" t="s">
         <v>3</v>
       </c>
@@ -2995,61 +3094,64 @@
       <c r="X45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>87000</v>
+      </c>
+      <c r="E46" s="3">
         <v>122300</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>108500</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>64000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>50000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>55100</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>81600</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>60500</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>96200</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>142600</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>169100</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>91700</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>107400</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>127400</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>600</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>800</v>
       </c>
-      <c r="S46" s="3">
-        <v>0</v>
-      </c>
-      <c r="T46" s="3" t="s">
-        <v>3</v>
+      <c r="T46" s="3">
+        <v>0</v>
       </c>
       <c r="U46" s="3" t="s">
         <v>3</v>
@@ -3063,16 +3165,19 @@
       <c r="X46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E47" s="3">
-        <v>800</v>
+      <c r="E47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="F47" s="3">
         <v>800</v>
@@ -3084,32 +3189,32 @@
         <v>800</v>
       </c>
       <c r="I47" s="3">
-        <v>3700</v>
+        <v>800</v>
       </c>
       <c r="J47" s="3">
         <v>3700</v>
       </c>
       <c r="K47" s="3">
-        <v>3500</v>
+        <v>3700</v>
       </c>
       <c r="L47" s="3">
         <v>3500</v>
       </c>
       <c r="M47" s="3">
+        <v>3500</v>
+      </c>
+      <c r="N47" s="3">
         <v>4700</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>4100</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>11100</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>3700</v>
       </c>
-      <c r="Q47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R47" s="3" t="s">
         <v>3</v>
       </c>
@@ -3125,59 +3230,62 @@
       <c r="V47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="W47" s="3">
-        <v>0</v>
+      <c r="W47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="X47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>46500</v>
+      </c>
+      <c r="E48" s="3">
         <v>41900</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>24300</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>23900</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>28700</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>31500</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>34400</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>25800</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>19500</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>16400</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>10300</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>8400</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>8000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>5700</v>
       </c>
-      <c r="Q48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R48" s="3" t="s">
         <v>3</v>
       </c>
@@ -3193,14 +3301,17 @@
       <c r="V48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="W48" s="3">
-        <v>0</v>
+      <c r="W48" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="X48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -3211,13 +3322,13 @@
         <v>4600</v>
       </c>
       <c r="F49" s="3">
-        <v>4700</v>
+        <v>4600</v>
       </c>
       <c r="G49" s="3">
         <v>4700</v>
       </c>
       <c r="H49" s="3">
-        <v>4600</v>
+        <v>4700</v>
       </c>
       <c r="I49" s="3">
         <v>4600</v>
@@ -3238,13 +3349,13 @@
         <v>4600</v>
       </c>
       <c r="O49" s="3">
-        <v>300</v>
+        <v>4600</v>
       </c>
       <c r="P49" s="3">
         <v>300</v>
       </c>
-      <c r="Q49" s="3" t="s">
-        <v>3</v>
+      <c r="Q49" s="3">
+        <v>300</v>
       </c>
       <c r="R49" s="3" t="s">
         <v>3</v>
@@ -3261,14 +3372,17 @@
       <c r="V49" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="W49" s="3">
-        <v>0</v>
+      <c r="W49" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="X49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3335,8 +3449,11 @@
       <c r="X50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3403,8 +3520,11 @@
       <c r="X51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -3412,53 +3532,53 @@
         <v>17600</v>
       </c>
       <c r="E52" s="3">
+        <v>17600</v>
+      </c>
+      <c r="F52" s="3">
         <v>15900</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>15600</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>15500</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>14800</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>14200</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>3200</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>3100</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>2100</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>1400</v>
-      </c>
-      <c r="N52" s="3">
-        <v>1000</v>
       </c>
       <c r="O52" s="3">
         <v>1000</v>
       </c>
       <c r="P52" s="3">
+        <v>1000</v>
+      </c>
+      <c r="Q52" s="3">
         <v>1200</v>
-      </c>
-      <c r="Q52" s="3">
-        <v>176800</v>
       </c>
       <c r="R52" s="3">
         <v>176800</v>
       </c>
       <c r="S52" s="3">
+        <v>176800</v>
+      </c>
+      <c r="T52" s="3">
         <v>100</v>
       </c>
-      <c r="T52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U52" s="3" t="s">
         <v>3</v>
       </c>
@@ -3471,8 +3591,11 @@
       <c r="X52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3539,62 +3662,65 @@
       <c r="X53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>155700</v>
+      </c>
+      <c r="E54" s="3">
         <v>186500</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>154100</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>109000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>99700</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>106800</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>138500</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>97700</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>126900</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>169200</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>190100</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>109900</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>127800</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>138300</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>177300</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>177500</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>100</v>
       </c>
-      <c r="T54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3607,8 +3733,11 @@
       <c r="X54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3633,8 +3762,9 @@
       <c r="V55" s="3"/>
       <c r="W55" s="3"/>
       <c r="X55" s="3"/>
-    </row>
-    <row r="56" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y55" s="3"/>
+    </row>
+    <row r="56" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3659,61 +3789,62 @@
       <c r="V56" s="3"/>
       <c r="W56" s="3"/>
       <c r="X56" s="3"/>
-    </row>
-    <row r="57" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y56" s="3"/>
+    </row>
+    <row r="57" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>18300</v>
+      </c>
+      <c r="E57" s="3">
         <v>20500</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>13800</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>15400</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>32500</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>34700</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>35500</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>29100</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>11700</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>13700</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>13200</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>15200</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>20200</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>11400</v>
       </c>
-      <c r="Q57" s="3">
-        <v>0</v>
-      </c>
       <c r="R57" s="3">
         <v>0</v>
       </c>
       <c r="S57" s="3">
         <v>0</v>
       </c>
-      <c r="T57" s="3" t="s">
-        <v>3</v>
+      <c r="T57" s="3">
+        <v>0</v>
       </c>
       <c r="U57" s="3" t="s">
         <v>3</v>
@@ -3727,62 +3858,65 @@
       <c r="X57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>3500</v>
+      </c>
+      <c r="E58" s="3">
         <v>3400</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>3200</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>3100</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>11200</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>5600</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>2900</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>14000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>6700</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>6600</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>6500</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>6100</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>1200</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>1100</v>
       </c>
-      <c r="Q58" s="3">
-        <v>0</v>
-      </c>
       <c r="R58" s="3">
         <v>0</v>
       </c>
       <c r="S58" s="3">
+        <v>0</v>
+      </c>
+      <c r="T58" s="3">
         <v>100</v>
       </c>
-      <c r="T58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U58" s="3" t="s">
         <v>3</v>
       </c>
@@ -3795,58 +3929,61 @@
       <c r="X58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>43100</v>
+      </c>
+      <c r="E59" s="3">
         <v>36900</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>29700</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>24500</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>21900</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>20300</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>17500</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>16600</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>15500</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>9600</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>1200</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>3400</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>800</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>1700</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>1800</v>
       </c>
-      <c r="R59" s="3">
-        <v>0</v>
-      </c>
-      <c r="S59" s="3" t="s">
-        <v>3</v>
+      <c r="S59" s="3">
+        <v>0</v>
       </c>
       <c r="T59" s="3" t="s">
         <v>3</v>
@@ -3863,61 +4000,64 @@
       <c r="X59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>64900</v>
+      </c>
+      <c r="E60" s="3">
         <v>60900</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>46800</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>43000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>65700</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>60600</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>55800</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>59600</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>33800</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>29900</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>20900</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>24600</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>22200</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>14100</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>1900</v>
-      </c>
-      <c r="R60" s="3">
-        <v>100</v>
       </c>
       <c r="S60" s="3">
         <v>100</v>
       </c>
-      <c r="T60" s="3" t="s">
-        <v>3</v>
+      <c r="T60" s="3">
+        <v>100</v>
       </c>
       <c r="U60" s="3" t="s">
         <v>3</v>
@@ -3931,53 +4071,56 @@
       <c r="X60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>202200</v>
+      </c>
+      <c r="E61" s="3">
         <v>200600</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>204100</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>229500</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>198600</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>170400</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>160800</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>90300</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>95300</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>102700</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>106800</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>13500</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>100</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>300</v>
       </c>
-      <c r="Q61" s="3">
-        <v>0</v>
-      </c>
       <c r="R61" s="3">
         <v>0</v>
       </c>
@@ -3999,53 +4142,56 @@
       <c r="X61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>36300</v>
+      </c>
+      <c r="E62" s="3">
         <v>35800</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>31600</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>65900</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>11100</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>8500</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>10100</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>5700</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>8000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>4200</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>3900</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>3100</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>3700</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>800</v>
       </c>
-      <c r="Q62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R62" s="3" t="s">
         <v>3</v>
       </c>
@@ -4061,14 +4207,17 @@
       <c r="V62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="W62" s="3">
-        <v>0</v>
+      <c r="W62" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="X62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4135,8 +4284,11 @@
       <c r="X63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4203,8 +4355,11 @@
       <c r="X64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4271,61 +4426,64 @@
       <c r="X65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>303400</v>
+      </c>
+      <c r="E66" s="3">
         <v>297300</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>282400</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>338500</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>275300</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>239500</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>226800</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>155600</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>137100</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>136700</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>131700</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>41300</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>26000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>15200</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>1900</v>
-      </c>
-      <c r="R66" s="3">
-        <v>100</v>
       </c>
       <c r="S66" s="3">
         <v>100</v>
       </c>
-      <c r="T66" s="3" t="s">
-        <v>3</v>
+      <c r="T66" s="3">
+        <v>100</v>
       </c>
       <c r="U66" s="3" t="s">
         <v>3</v>
@@ -4339,8 +4497,11 @@
       <c r="X66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4365,8 +4526,9 @@
       <c r="V67" s="3"/>
       <c r="W67" s="3"/>
       <c r="X67" s="3"/>
-    </row>
-    <row r="68" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y67" s="3"/>
+    </row>
+    <row r="68" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4433,8 +4595,11 @@
       <c r="X68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4501,8 +4666,11 @@
       <c r="X69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4569,8 +4737,11 @@
       <c r="X70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4637,61 +4808,64 @@
       <c r="X71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-922600</v>
+      </c>
+      <c r="E72" s="3">
         <v>-875800</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-834600</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-849600</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-717900</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-646300</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-589700</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-519000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-462300</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-416500</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-385900</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-367800</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-313800</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-290800</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-2000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-100</v>
       </c>
-      <c r="S72" s="3">
-        <v>0</v>
-      </c>
-      <c r="T72" s="3" t="s">
-        <v>3</v>
+      <c r="T72" s="3">
+        <v>0</v>
       </c>
       <c r="U72" s="3" t="s">
         <v>3</v>
@@ -4705,8 +4879,11 @@
       <c r="X72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4773,8 +4950,11 @@
       <c r="X73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4841,8 +5021,11 @@
       <c r="X74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4909,61 +5092,64 @@
       <c r="X75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>-147700</v>
+      </c>
+      <c r="E76" s="3">
         <v>-110800</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>-128300</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>-229500</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>-175600</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>-132700</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>-88300</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>-57800</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>-10200</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>32400</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>58400</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>68600</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>101800</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>123100</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>175500</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>177400</v>
       </c>
-      <c r="S76" s="3">
-        <v>0</v>
-      </c>
-      <c r="T76" s="3" t="s">
-        <v>3</v>
+      <c r="T76" s="3">
+        <v>0</v>
       </c>
       <c r="U76" s="3" t="s">
         <v>3</v>
@@ -4977,8 +5163,11 @@
       <c r="X76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5045,67 +5234,70 @@
       <c r="X77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E80" s="2">
         <v>45291</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45199</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45107</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45016</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44926</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44834</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44742</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44651</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44561</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44469</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44377</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44286</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44196</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44104</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44012</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43921</v>
       </c>
-      <c r="T80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="U80" s="2" t="s">
         <v>3</v>
       </c>
@@ -5118,61 +5310,64 @@
       <c r="X80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-46700</v>
+      </c>
+      <c r="E81" s="3">
         <v>-41200</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>14900</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-131600</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-71600</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-56600</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-70700</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-56700</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-45800</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-30600</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-18100</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-54000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-21500</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-66700</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-2000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-100</v>
       </c>
-      <c r="S81" s="3">
-        <v>0</v>
-      </c>
-      <c r="T81" s="3" t="s">
-        <v>3</v>
+      <c r="T81" s="3">
+        <v>0</v>
       </c>
       <c r="U81" s="3" t="s">
         <v>3</v>
@@ -5186,8 +5381,11 @@
       <c r="X81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5212,50 +5410,51 @@
       <c r="V82" s="3"/>
       <c r="W82" s="3"/>
       <c r="X82" s="3"/>
-    </row>
-    <row r="83" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y82" s="3"/>
+    </row>
+    <row r="83" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>1200</v>
+      </c>
+      <c r="E83" s="3">
         <v>2400</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>2200</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>2500</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>2700</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>3000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>1600</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>1300</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>1000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>800</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>700</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>600</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>500</v>
       </c>
-      <c r="P83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q83" s="3" t="s">
         <v>3</v>
       </c>
@@ -5271,8 +5470,8 @@
       <c r="U83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V83" s="3">
-        <v>0</v>
+      <c r="V83" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="W83" s="3">
         <v>0</v>
@@ -5280,8 +5479,11 @@
       <c r="X83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5348,8 +5550,11 @@
       <c r="X84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5416,8 +5621,11 @@
       <c r="X85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5484,8 +5692,11 @@
       <c r="X86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5552,8 +5763,11 @@
       <c r="X87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5620,61 +5834,64 @@
       <c r="X88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-40500</v>
+      </c>
+      <c r="E89" s="3">
         <v>-37400</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-32000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-45100</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-30500</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-37700</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-72100</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-44300</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-42700</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-35500</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-31700</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-39200</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-9700</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-26100</v>
-      </c>
-      <c r="Q89" s="3">
-        <v>-200</v>
       </c>
       <c r="R89" s="3">
         <v>-200</v>
       </c>
       <c r="S89" s="3">
-        <v>0</v>
-      </c>
-      <c r="T89" s="3" t="s">
-        <v>3</v>
+        <v>-200</v>
+      </c>
+      <c r="T89" s="3">
+        <v>0</v>
       </c>
       <c r="U89" s="3" t="s">
         <v>3</v>
@@ -5688,8 +5905,11 @@
       <c r="X89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5714,50 +5934,51 @@
       <c r="V90" s="3"/>
       <c r="W90" s="3"/>
       <c r="X90" s="3"/>
-    </row>
-    <row r="91" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y90" s="3"/>
+    </row>
+    <row r="91" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-4000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-8300</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-11100</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-7200</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-2900</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-1300</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-7300</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-6400</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-5100</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-4200</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-3800</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-3100</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-4500</v>
       </c>
-      <c r="P91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q91" s="3" t="s">
         <v>3</v>
       </c>
@@ -5773,8 +5994,8 @@
       <c r="U91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V91" s="3">
-        <v>0</v>
+      <c r="V91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="W91" s="3">
         <v>0</v>
@@ -5782,8 +6003,11 @@
       <c r="X91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5850,8 +6074,11 @@
       <c r="X92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5918,55 +6145,58 @@
       <c r="X93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-4000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-8300</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-11100</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-7200</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-2900</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>1900</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-7300</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-6600</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-5100</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-3100</v>
-      </c>
-      <c r="M94" s="3">
-        <v>-4400</v>
       </c>
       <c r="N94" s="3">
         <v>-4400</v>
       </c>
       <c r="O94" s="3">
+        <v>-4400</v>
+      </c>
+      <c r="P94" s="3">
         <v>-11400</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>170100</v>
       </c>
-      <c r="Q94" s="3">
-        <v>0</v>
-      </c>
-      <c r="R94" s="3" t="s">
-        <v>3</v>
+      <c r="R94" s="3">
+        <v>0</v>
       </c>
       <c r="S94" s="3" t="s">
         <v>3</v>
@@ -5980,14 +6210,17 @@
       <c r="V94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="W94" s="3">
-        <v>0</v>
+      <c r="W94" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="X94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6012,8 +6245,9 @@
       <c r="V95" s="3"/>
       <c r="W95" s="3"/>
       <c r="X95" s="3"/>
-    </row>
-    <row r="96" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y95" s="3"/>
+    </row>
+    <row r="96" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -6080,8 +6314,11 @@
       <c r="X96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6148,8 +6385,11 @@
       <c r="X97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6216,8 +6456,11 @@
       <c r="X98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6284,62 +6527,65 @@
       <c r="X99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>6100</v>
+      </c>
+      <c r="E100" s="3">
         <v>57300</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>78000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>60200</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>32500</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>16000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>112900</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>11800</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-1200</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-400</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>106200</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>17600</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-100</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-23300</v>
       </c>
-      <c r="Q100" s="3">
-        <v>0</v>
-      </c>
       <c r="R100" s="3">
+        <v>0</v>
+      </c>
+      <c r="S100" s="3">
         <v>177500</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>100</v>
       </c>
-      <c r="T100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U100" s="3" t="s">
         <v>3</v>
       </c>
@@ -6352,8 +6598,11 @@
       <c r="X100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -6375,8 +6624,8 @@
       <c r="I101" s="3">
         <v>0</v>
       </c>
-      <c r="J101" s="3" t="s">
-        <v>3</v>
+      <c r="J101" s="3">
+        <v>0</v>
       </c>
       <c r="K101" s="3" t="s">
         <v>3</v>
@@ -6393,8 +6642,8 @@
       <c r="O101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P101" s="3">
-        <v>0</v>
+      <c r="P101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q101" s="3">
         <v>0</v>
@@ -6420,61 +6669,64 @@
       <c r="X101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-38400</v>
+      </c>
+      <c r="E102" s="3">
         <v>11600</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>34900</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>7900</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-900</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-19800</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>33500</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-39100</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-49100</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-39000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>70000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-26000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-21100</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>120700</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-200</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>500</v>
       </c>
-      <c r="S102" s="3">
-        <v>0</v>
-      </c>
-      <c r="T102" s="3" t="s">
-        <v>3</v>
+      <c r="T102" s="3">
+        <v>0</v>
       </c>
       <c r="U102" s="3" t="s">
         <v>3</v>
@@ -6486,6 +6738,9 @@
         <v>3</v>
       </c>
       <c r="X102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/EOSE_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/EOSE_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="363" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="364" uniqueCount="92">
   <si>
     <t>EOSE</t>
   </si>
@@ -656,97 +656,98 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Y102"/>
+  <dimension ref="A5:Z102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="25" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="26" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:26" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E7" s="2">
         <v>45382</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45199</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45107</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45016</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44926</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44834</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44742</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44651</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44561</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44469</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44377</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44286</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44196</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44104</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44012</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43921</v>
       </c>
-      <c r="U7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="V7" s="2" t="s">
         <v>3</v>
       </c>
@@ -759,55 +760,58 @@
       <c r="Y7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
-        <v>6600</v>
+        <v>900</v>
       </c>
       <c r="E8" s="3">
         <v>6600</v>
       </c>
       <c r="F8" s="3">
+        <v>6600</v>
+      </c>
+      <c r="G8" s="3">
         <v>700</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>200</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>8800</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>2700</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>6100</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>5900</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>3300</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>3100</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>700</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>600</v>
-      </c>
-      <c r="P8" s="3">
-        <v>200</v>
       </c>
       <c r="Q8" s="3">
         <v>200</v>
       </c>
-      <c r="R8" s="3" t="s">
-        <v>3</v>
+      <c r="R8" s="3">
+        <v>200</v>
       </c>
       <c r="S8" s="3" t="s">
         <v>3</v>
@@ -824,62 +828,65 @@
       <c r="W8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="X8" s="3">
-        <v>0</v>
+      <c r="X8" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Y8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>14100</v>
+      </c>
+      <c r="E9" s="3">
         <v>28200</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>30400</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>21300</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>11200</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>26900</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>30800</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>50000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>36900</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>35600</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>21100</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>12900</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>12400</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>100</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>5500</v>
       </c>
-      <c r="R9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S9" s="3" t="s">
         <v>3</v>
       </c>
@@ -901,56 +908,59 @@
       <c r="Y9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>-13200</v>
+      </c>
+      <c r="E10" s="3">
         <v>-21600</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>-23800</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>-20600</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>-11000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>-18100</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>-28100</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>-43900</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>-31000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>-32300</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>-18000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>-12200</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>-11800</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>100</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>-5300</v>
       </c>
-      <c r="R10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S10" s="3" t="s">
         <v>3</v>
       </c>
@@ -972,8 +982,11 @@
       <c r="Y10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -999,56 +1012,57 @@
       <c r="W11" s="3"/>
       <c r="X11" s="3"/>
       <c r="Y11" s="3"/>
-    </row>
-    <row r="12" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z11" s="3"/>
+    </row>
+    <row r="12" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>4300</v>
+      </c>
+      <c r="E12" s="3">
         <v>5200</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>5000</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>3200</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>5000</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>5400</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>3600</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>4500</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>5500</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>5000</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>5400</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>5100</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>3600</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>5000</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>14000</v>
       </c>
-      <c r="R12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S12" s="3" t="s">
         <v>3</v>
       </c>
@@ -1070,8 +1084,11 @@
       <c r="Y12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1141,55 +1158,58 @@
       <c r="Y13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>-68200</v>
+      </c>
+      <c r="E14" s="3">
         <v>100</v>
       </c>
-      <c r="E14" s="3">
-        <v>0</v>
-      </c>
       <c r="F14" s="3">
+        <v>0</v>
+      </c>
+      <c r="G14" s="3">
         <v>1000</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>7300</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>2400</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>4300</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>1400</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>2000</v>
       </c>
-      <c r="L14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M14" s="3">
-        <v>0</v>
+      <c r="M14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N14" s="3">
+        <v>0</v>
+      </c>
+      <c r="O14" s="3">
         <v>-1300</v>
       </c>
-      <c r="O14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="P14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q14" s="3">
-        <v>0</v>
-      </c>
-      <c r="R14" s="3" t="s">
-        <v>3</v>
+      <c r="Q14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R14" s="3">
+        <v>0</v>
       </c>
       <c r="S14" s="3" t="s">
         <v>3</v>
@@ -1197,8 +1217,8 @@
       <c r="T14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U14" s="3">
-        <v>0</v>
+      <c r="U14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="V14" s="3">
         <v>0</v>
@@ -1212,8 +1232,11 @@
       <c r="Y14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:26" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1283,8 +1306,11 @@
       <c r="Y15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:25" x14ac:dyDescent="0.2">
+      <c r="Z15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:26" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1307,64 +1333,65 @@
       <c r="W16" s="3"/>
       <c r="X16" s="3"/>
       <c r="Y16" s="3"/>
-    </row>
-    <row r="17" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z16" s="3"/>
+    </row>
+    <row r="17" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>-38500</v>
+      </c>
+      <c r="E17" s="3">
         <v>47700</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>48800</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>38500</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>36700</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>48700</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>51300</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>70600</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>63300</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>55000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>40700</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>25700</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>49800</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>21800</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>37200</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>2000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>100</v>
       </c>
-      <c r="T17" s="3">
-        <v>0</v>
-      </c>
-      <c r="U17" s="3" t="s">
-        <v>3</v>
+      <c r="U17" s="3">
+        <v>0</v>
       </c>
       <c r="V17" s="3" t="s">
         <v>3</v>
@@ -1378,56 +1405,59 @@
       <c r="Y17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>39400</v>
+      </c>
+      <c r="E18" s="3">
         <v>-41100</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-42200</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-37800</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-36500</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-39900</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-48600</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-64500</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-57400</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-51700</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-37600</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-25000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-49200</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-21600</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-37000</v>
       </c>
-      <c r="R18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1449,8 +1479,11 @@
       <c r="Y18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1476,56 +1509,57 @@
       <c r="W19" s="3"/>
       <c r="X19" s="3"/>
       <c r="Y19" s="3"/>
-    </row>
-    <row r="20" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z19" s="3"/>
+    </row>
+    <row r="20" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-59200</v>
+      </c>
+      <c r="E20" s="3">
         <v>3600</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>9600</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>62200</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-75500</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-13100</v>
-      </c>
-      <c r="I20" s="3">
-        <v>-400</v>
       </c>
       <c r="J20" s="3">
         <v>-400</v>
       </c>
       <c r="K20" s="3">
+        <v>-400</v>
+      </c>
+      <c r="L20" s="3">
         <v>3600</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>8400</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>8300</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>10700</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-4700</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>200</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-5900</v>
       </c>
-      <c r="R20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S20" s="3" t="s">
         <v>3</v>
       </c>
@@ -1547,53 +1581,56 @@
       <c r="Y20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-18400</v>
+      </c>
+      <c r="E21" s="3">
         <v>-36400</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-30200</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>26600</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-109500</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-50300</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-46000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-63300</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-52500</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-42300</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-28500</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-13700</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-53300</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-21000</v>
       </c>
-      <c r="Q21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1618,56 +1655,59 @@
       <c r="Y21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>8400</v>
+      </c>
+      <c r="E22" s="3">
         <v>9100</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>8600</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>9400</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>19600</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>18600</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>7600</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>5700</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>2900</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>2500</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>1300</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>3700</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>200</v>
       </c>
-      <c r="P22" s="3">
-        <v>0</v>
-      </c>
       <c r="Q22" s="3">
+        <v>0</v>
+      </c>
+      <c r="R22" s="3">
         <v>23800</v>
       </c>
-      <c r="R22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S22" s="3" t="s">
         <v>3</v>
       </c>
@@ -1683,70 +1723,73 @@
       <c r="W22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="X22" s="3">
-        <v>0</v>
+      <c r="X22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Y22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-28200</v>
+      </c>
+      <c r="E23" s="3">
         <v>-46700</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-41200</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>14900</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-131600</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-71600</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-56600</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-70600</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-56700</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-45800</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-30600</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-18100</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-54000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-21500</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-66700</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-2000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-100</v>
       </c>
-      <c r="T23" s="3">
-        <v>0</v>
-      </c>
-      <c r="U23" s="3" t="s">
-        <v>3</v>
+      <c r="U23" s="3">
+        <v>0</v>
       </c>
       <c r="V23" s="3" t="s">
         <v>3</v>
@@ -1760,8 +1803,11 @@
       <c r="Y23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1784,16 +1830,16 @@
         <v>0</v>
       </c>
       <c r="J24" s="3">
+        <v>0</v>
+      </c>
+      <c r="K24" s="3">
         <v>100</v>
       </c>
-      <c r="K24" s="3">
-        <v>0</v>
-      </c>
       <c r="L24" s="3">
         <v>0</v>
       </c>
-      <c r="M24" s="3" t="s">
-        <v>3</v>
+      <c r="M24" s="3">
+        <v>0</v>
       </c>
       <c r="N24" s="3" t="s">
         <v>3</v>
@@ -1810,8 +1856,8 @@
       <c r="R24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S24" s="3">
-        <v>0</v>
+      <c r="S24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="T24" s="3">
         <v>0</v>
@@ -1831,8 +1877,11 @@
       <c r="Y24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1902,64 +1951,67 @@
       <c r="Y25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-28200</v>
+      </c>
+      <c r="E26" s="3">
         <v>-46700</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-41200</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>14900</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-131600</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-71600</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-56600</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-70700</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-56700</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-45800</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-30600</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-18100</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-54000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-21500</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-66700</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-2000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-100</v>
       </c>
-      <c r="T26" s="3">
-        <v>0</v>
-      </c>
-      <c r="U26" s="3" t="s">
-        <v>3</v>
+      <c r="U26" s="3">
+        <v>0</v>
       </c>
       <c r="V26" s="3" t="s">
         <v>3</v>
@@ -1973,64 +2025,67 @@
       <c r="Y26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-51800</v>
+      </c>
+      <c r="E27" s="3">
         <v>-46700</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-41200</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>14900</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-131600</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-71600</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-56600</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-70700</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-56700</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-45800</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-30600</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-18100</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-54000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-21500</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-66700</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-2000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-100</v>
       </c>
-      <c r="T27" s="3">
-        <v>0</v>
-      </c>
-      <c r="U27" s="3" t="s">
-        <v>3</v>
+      <c r="U27" s="3">
+        <v>0</v>
       </c>
       <c r="V27" s="3" t="s">
         <v>3</v>
@@ -2044,8 +2099,11 @@
       <c r="Y27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2115,8 +2173,11 @@
       <c r="Y28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2186,8 +2247,11 @@
       <c r="Y29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2257,8 +2321,11 @@
       <c r="Y30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2328,56 +2395,59 @@
       <c r="Y31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>59200</v>
+      </c>
+      <c r="E32" s="3">
         <v>-3600</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-9600</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-62200</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>75500</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>13100</v>
-      </c>
-      <c r="I32" s="3">
-        <v>400</v>
       </c>
       <c r="J32" s="3">
         <v>400</v>
       </c>
       <c r="K32" s="3">
+        <v>400</v>
+      </c>
+      <c r="L32" s="3">
         <v>-3600</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-8400</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-8300</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-10700</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>4700</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-200</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>5900</v>
       </c>
-      <c r="R32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S32" s="3" t="s">
         <v>3</v>
       </c>
@@ -2399,64 +2469,67 @@
       <c r="Y32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-51800</v>
+      </c>
+      <c r="E33" s="3">
         <v>-46700</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-41200</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>14900</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-131600</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-71600</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-56600</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-70700</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-56700</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-45800</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-30600</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-18100</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-54000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-21500</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-66700</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-2000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-100</v>
       </c>
-      <c r="T33" s="3">
-        <v>0</v>
-      </c>
-      <c r="U33" s="3" t="s">
-        <v>3</v>
+      <c r="U33" s="3">
+        <v>0</v>
       </c>
       <c r="V33" s="3" t="s">
         <v>3</v>
@@ -2470,8 +2543,11 @@
       <c r="Y33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2541,64 +2617,67 @@
       <c r="Y34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-51800</v>
+      </c>
+      <c r="E35" s="3">
         <v>-46700</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-41200</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>14900</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-131600</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-71600</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-56600</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-70700</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-56700</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-45800</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-30600</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-18100</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-54000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-21500</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-66700</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-2000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-100</v>
       </c>
-      <c r="T35" s="3">
-        <v>0</v>
-      </c>
-      <c r="U35" s="3" t="s">
-        <v>3</v>
+      <c r="U35" s="3">
+        <v>0</v>
       </c>
       <c r="V35" s="3" t="s">
         <v>3</v>
@@ -2612,70 +2691,73 @@
       <c r="Y35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E38" s="2">
         <v>45382</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45199</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45107</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45016</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44926</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44834</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44742</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44651</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44561</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44469</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44377</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44286</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44196</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44104</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44012</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43921</v>
       </c>
-      <c r="U38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="V38" s="2" t="s">
         <v>3</v>
       </c>
@@ -2688,8 +2770,11 @@
       <c r="Y38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2715,8 +2800,9 @@
       <c r="W39" s="3"/>
       <c r="X39" s="3"/>
       <c r="Y39" s="3"/>
-    </row>
-    <row r="40" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z39" s="3"/>
+    </row>
+    <row r="40" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2742,64 +2828,65 @@
       <c r="W40" s="3"/>
       <c r="X40" s="3"/>
       <c r="Y40" s="3"/>
-    </row>
-    <row r="41" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z40" s="3"/>
+    </row>
+    <row r="41" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>52500</v>
+      </c>
+      <c r="E41" s="3">
         <v>31800</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>69500</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>58000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>23200</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>16100</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>17100</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>38400</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>16300</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>55400</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>104800</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>144200</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>74700</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>100700</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>121900</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>300</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>500</v>
       </c>
-      <c r="T41" s="3">
-        <v>0</v>
-      </c>
-      <c r="U41" s="3" t="s">
-        <v>3</v>
+      <c r="U41" s="3">
+        <v>0</v>
       </c>
       <c r="V41" s="3" t="s">
         <v>3</v>
@@ -2813,8 +2900,11 @@
       <c r="Y41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2884,64 +2974,67 @@
       <c r="Y42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>100800</v>
+      </c>
+      <c r="E43" s="3">
         <v>27300</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>20500</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>4000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>3600</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>7500</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>3600</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>6400</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>3600</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>3700</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>2000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>2400</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>400</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>300</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>100</v>
       </c>
-      <c r="R43" s="3">
-        <v>0</v>
-      </c>
       <c r="S43" s="3">
         <v>0</v>
       </c>
       <c r="T43" s="3">
         <v>0</v>
       </c>
-      <c r="U43" s="3" t="s">
-        <v>3</v>
+      <c r="U43" s="3">
+        <v>0</v>
       </c>
       <c r="V43" s="3" t="s">
         <v>3</v>
@@ -2955,56 +3048,59 @@
       <c r="Y43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>17800</v>
+      </c>
+      <c r="E44" s="3">
         <v>14400</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>17100</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>20600</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>16600</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>14100</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>23300</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>23200</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>12900</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>10300</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>13000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>5000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>4400</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>100</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>200</v>
       </c>
-      <c r="R44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S44" s="3" t="s">
         <v>3</v>
       </c>
@@ -3020,68 +3116,71 @@
       <c r="W44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="X44" s="3">
-        <v>0</v>
+      <c r="X44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Y44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>12500</v>
+      </c>
+      <c r="E45" s="3">
         <v>13500</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>15300</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>25900</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>20500</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>12300</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>11300</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>13600</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>27600</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>26800</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>22700</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>17400</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>12200</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>6200</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>5200</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>200</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>300</v>
       </c>
-      <c r="T45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U45" s="3" t="s">
         <v>3</v>
       </c>
@@ -3097,64 +3196,67 @@
       <c r="Y45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>183500</v>
+      </c>
+      <c r="E46" s="3">
         <v>87000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>122300</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>108500</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>64000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>50000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>55100</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>81600</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>60500</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>96200</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>142600</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>169100</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>91700</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>107400</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>127400</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>600</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>800</v>
       </c>
-      <c r="T46" s="3">
-        <v>0</v>
-      </c>
-      <c r="U46" s="3" t="s">
-        <v>3</v>
+      <c r="U46" s="3">
+        <v>0</v>
       </c>
       <c r="V46" s="3" t="s">
         <v>3</v>
@@ -3168,8 +3270,11 @@
       <c r="Y46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3179,8 +3284,8 @@
       <c r="E47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F47" s="3">
-        <v>800</v>
+      <c r="F47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="G47" s="3">
         <v>800</v>
@@ -3192,32 +3297,32 @@
         <v>800</v>
       </c>
       <c r="J47" s="3">
-        <v>3700</v>
+        <v>800</v>
       </c>
       <c r="K47" s="3">
         <v>3700</v>
       </c>
       <c r="L47" s="3">
-        <v>3500</v>
+        <v>3700</v>
       </c>
       <c r="M47" s="3">
         <v>3500</v>
       </c>
       <c r="N47" s="3">
+        <v>3500</v>
+      </c>
+      <c r="O47" s="3">
         <v>4700</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>4100</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>11100</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>3700</v>
       </c>
-      <c r="R47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S47" s="3" t="s">
         <v>3</v>
       </c>
@@ -3233,62 +3338,65 @@
       <c r="W47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="X47" s="3">
-        <v>0</v>
+      <c r="X47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Y47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>54000</v>
+      </c>
+      <c r="E48" s="3">
         <v>46500</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>41900</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>24300</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>23900</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>28700</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>31500</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>34400</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>25800</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>19500</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>16400</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>10300</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>8400</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>8000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>5700</v>
       </c>
-      <c r="R48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S48" s="3" t="s">
         <v>3</v>
       </c>
@@ -3304,14 +3412,17 @@
       <c r="W48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="X48" s="3">
-        <v>0</v>
+      <c r="X48" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Y48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -3325,13 +3436,13 @@
         <v>4600</v>
       </c>
       <c r="G49" s="3">
-        <v>4700</v>
+        <v>4600</v>
       </c>
       <c r="H49" s="3">
         <v>4700</v>
       </c>
       <c r="I49" s="3">
-        <v>4600</v>
+        <v>4700</v>
       </c>
       <c r="J49" s="3">
         <v>4600</v>
@@ -3352,13 +3463,13 @@
         <v>4600</v>
       </c>
       <c r="P49" s="3">
-        <v>300</v>
+        <v>4600</v>
       </c>
       <c r="Q49" s="3">
         <v>300</v>
       </c>
-      <c r="R49" s="3" t="s">
-        <v>3</v>
+      <c r="R49" s="3">
+        <v>300</v>
       </c>
       <c r="S49" s="3" t="s">
         <v>3</v>
@@ -3375,14 +3486,17 @@
       <c r="W49" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="X49" s="3">
-        <v>0</v>
+      <c r="X49" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Y49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3452,8 +3566,11 @@
       <c r="Y50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3523,65 +3640,68 @@
       <c r="Y51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>17600</v>
+        <v>6600</v>
       </c>
       <c r="E52" s="3">
         <v>17600</v>
       </c>
       <c r="F52" s="3">
+        <v>17600</v>
+      </c>
+      <c r="G52" s="3">
         <v>15900</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>15600</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>15500</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>14800</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>14200</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>3200</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>3100</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>2100</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>1400</v>
-      </c>
-      <c r="O52" s="3">
-        <v>1000</v>
       </c>
       <c r="P52" s="3">
         <v>1000</v>
       </c>
       <c r="Q52" s="3">
+        <v>1000</v>
+      </c>
+      <c r="R52" s="3">
         <v>1200</v>
-      </c>
-      <c r="R52" s="3">
-        <v>176800</v>
       </c>
       <c r="S52" s="3">
         <v>176800</v>
       </c>
       <c r="T52" s="3">
+        <v>176800</v>
+      </c>
+      <c r="U52" s="3">
         <v>100</v>
       </c>
-      <c r="U52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V52" s="3" t="s">
         <v>3</v>
       </c>
@@ -3594,8 +3714,11 @@
       <c r="Y52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3665,65 +3788,68 @@
       <c r="Y53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>248800</v>
+      </c>
+      <c r="E54" s="3">
         <v>155700</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>186500</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>154100</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>109000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>99700</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>106800</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>138500</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>97700</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>126900</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>169200</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>190100</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>109900</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>127800</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>138300</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>177300</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>177500</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>100</v>
       </c>
-      <c r="U54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3736,8 +3862,11 @@
       <c r="Y54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3763,8 +3892,9 @@
       <c r="W55" s="3"/>
       <c r="X55" s="3"/>
       <c r="Y55" s="3"/>
-    </row>
-    <row r="56" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z55" s="3"/>
+    </row>
+    <row r="56" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3790,64 +3920,65 @@
       <c r="W56" s="3"/>
       <c r="X56" s="3"/>
       <c r="Y56" s="3"/>
-    </row>
-    <row r="57" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z56" s="3"/>
+    </row>
+    <row r="57" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>24100</v>
+      </c>
+      <c r="E57" s="3">
         <v>18300</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>20500</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>13800</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>15400</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>32500</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>34700</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>35500</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>29100</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>11700</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>13700</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>13200</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>15200</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>20200</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>11400</v>
       </c>
-      <c r="R57" s="3">
-        <v>0</v>
-      </c>
       <c r="S57" s="3">
         <v>0</v>
       </c>
       <c r="T57" s="3">
         <v>0</v>
       </c>
-      <c r="U57" s="3" t="s">
-        <v>3</v>
+      <c r="U57" s="3">
+        <v>0</v>
       </c>
       <c r="V57" s="3" t="s">
         <v>3</v>
@@ -3861,65 +3992,68 @@
       <c r="Y57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>3000</v>
+      </c>
+      <c r="E58" s="3">
         <v>3500</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>3400</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>3200</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>3100</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>11200</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>5600</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>2900</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>14000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>6700</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>6600</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>6500</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>6100</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>1200</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>1100</v>
       </c>
-      <c r="R58" s="3">
-        <v>0</v>
-      </c>
       <c r="S58" s="3">
         <v>0</v>
       </c>
       <c r="T58" s="3">
+        <v>0</v>
+      </c>
+      <c r="U58" s="3">
         <v>100</v>
       </c>
-      <c r="U58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V58" s="3" t="s">
         <v>3</v>
       </c>
@@ -3932,61 +4066,64 @@
       <c r="Y58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>41300</v>
+      </c>
+      <c r="E59" s="3">
         <v>43100</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>36900</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>29700</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>24500</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>21900</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>20300</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>17500</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>16600</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>15500</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>9600</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>1200</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>3400</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>800</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>1700</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>1800</v>
       </c>
-      <c r="S59" s="3">
-        <v>0</v>
-      </c>
-      <c r="T59" s="3" t="s">
-        <v>3</v>
+      <c r="T59" s="3">
+        <v>0</v>
       </c>
       <c r="U59" s="3" t="s">
         <v>3</v>
@@ -4003,64 +4140,67 @@
       <c r="Y59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>68500</v>
+      </c>
+      <c r="E60" s="3">
         <v>64900</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>60900</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>46800</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>43000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>65700</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>60600</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>55800</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>59600</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>33800</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>29900</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>20900</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>24600</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>22200</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>14100</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>1900</v>
-      </c>
-      <c r="S60" s="3">
-        <v>100</v>
       </c>
       <c r="T60" s="3">
         <v>100</v>
       </c>
-      <c r="U60" s="3" t="s">
-        <v>3</v>
+      <c r="U60" s="3">
+        <v>100</v>
       </c>
       <c r="V60" s="3" t="s">
         <v>3</v>
@@ -4074,56 +4214,59 @@
       <c r="Y60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>150200</v>
+      </c>
+      <c r="E61" s="3">
         <v>202200</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>200600</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>204100</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>229500</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>198600</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>170400</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>160800</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>90300</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>95300</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>102700</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>106800</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>13500</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>100</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>300</v>
       </c>
-      <c r="R61" s="3">
-        <v>0</v>
-      </c>
       <c r="S61" s="3">
         <v>0</v>
       </c>
@@ -4145,56 +4288,59 @@
       <c r="Y61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>180800</v>
+      </c>
+      <c r="E62" s="3">
         <v>36300</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>35800</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>31600</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>65900</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>11100</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>8500</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>10100</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>5700</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>8000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>4200</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>3900</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>3100</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>3700</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>800</v>
       </c>
-      <c r="R62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S62" s="3" t="s">
         <v>3</v>
       </c>
@@ -4210,14 +4356,17 @@
       <c r="W62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="X62" s="3">
-        <v>0</v>
+      <c r="X62" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Y62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4287,8 +4436,11 @@
       <c r="Y63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4358,8 +4510,11 @@
       <c r="Y64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4429,64 +4584,67 @@
       <c r="Y65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>399500</v>
+      </c>
+      <c r="E66" s="3">
         <v>303400</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>297300</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>282400</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>338500</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>275300</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>239500</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>226800</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>155600</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>137100</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>136700</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>131700</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>41300</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>26000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>15200</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>1900</v>
-      </c>
-      <c r="S66" s="3">
-        <v>100</v>
       </c>
       <c r="T66" s="3">
         <v>100</v>
       </c>
-      <c r="U66" s="3" t="s">
-        <v>3</v>
+      <c r="U66" s="3">
+        <v>100</v>
       </c>
       <c r="V66" s="3" t="s">
         <v>3</v>
@@ -4500,8 +4658,11 @@
       <c r="Y66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4527,8 +4688,9 @@
       <c r="W67" s="3"/>
       <c r="X67" s="3"/>
       <c r="Y67" s="3"/>
-    </row>
-    <row r="68" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z67" s="3"/>
+    </row>
+    <row r="68" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4598,8 +4760,11 @@
       <c r="Y68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4669,13 +4834,16 @@
       <c r="Y69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
       <c r="D70" s="3">
-        <v>0</v>
+        <v>40100</v>
       </c>
       <c r="E70" s="3">
         <v>0</v>
@@ -4740,8 +4908,11 @@
       <c r="Y70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4811,64 +4982,67 @@
       <c r="Y71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-950700</v>
+      </c>
+      <c r="E72" s="3">
         <v>-922600</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-875800</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-834600</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-849600</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-717900</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-646300</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-589700</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-519000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-462300</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-416500</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-385900</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-367800</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-313800</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-290800</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-2000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-100</v>
       </c>
-      <c r="T72" s="3">
-        <v>0</v>
-      </c>
-      <c r="U72" s="3" t="s">
-        <v>3</v>
+      <c r="U72" s="3">
+        <v>0</v>
       </c>
       <c r="V72" s="3" t="s">
         <v>3</v>
@@ -4882,8 +5056,11 @@
       <c r="Y72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4953,8 +5130,11 @@
       <c r="Y73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5024,8 +5204,11 @@
       <c r="Y74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5095,64 +5278,67 @@
       <c r="Y75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>-190800</v>
+      </c>
+      <c r="E76" s="3">
         <v>-147700</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>-110800</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>-128300</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>-229500</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>-175600</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>-132700</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>-88300</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>-57800</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>-10200</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>32400</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>58400</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>68600</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>101800</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>123100</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>175500</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>177400</v>
       </c>
-      <c r="T76" s="3">
-        <v>0</v>
-      </c>
-      <c r="U76" s="3" t="s">
-        <v>3</v>
+      <c r="U76" s="3">
+        <v>0</v>
       </c>
       <c r="V76" s="3" t="s">
         <v>3</v>
@@ -5166,8 +5352,11 @@
       <c r="Y76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5237,70 +5426,73 @@
       <c r="Y77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:25" x14ac:dyDescent="0.2">
+      <c r="Z77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:26" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:25" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:26" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E80" s="2">
         <v>45382</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45199</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45107</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45016</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44926</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44834</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44742</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44651</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44561</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44469</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44377</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44286</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44196</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44104</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44012</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43921</v>
       </c>
-      <c r="U80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="V80" s="2" t="s">
         <v>3</v>
       </c>
@@ -5313,64 +5505,67 @@
       <c r="Y80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-51800</v>
+      </c>
+      <c r="E81" s="3">
         <v>-46700</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-41200</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>14900</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-131600</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-71600</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-56600</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-70700</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-56700</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-45800</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-30600</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-18100</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-54000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-21500</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-66700</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-2000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-100</v>
       </c>
-      <c r="T81" s="3">
-        <v>0</v>
-      </c>
-      <c r="U81" s="3" t="s">
-        <v>3</v>
+      <c r="U81" s="3">
+        <v>0</v>
       </c>
       <c r="V81" s="3" t="s">
         <v>3</v>
@@ -5384,8 +5579,11 @@
       <c r="Y81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5411,53 +5609,54 @@
       <c r="W82" s="3"/>
       <c r="X82" s="3"/>
       <c r="Y82" s="3"/>
-    </row>
-    <row r="83" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z82" s="3"/>
+    </row>
+    <row r="83" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>1400</v>
+      </c>
+      <c r="E83" s="3">
         <v>1200</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>2400</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>2200</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>2500</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>2700</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>3000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>1600</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>1300</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>1000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>800</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>700</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>600</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>500</v>
       </c>
-      <c r="Q83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R83" s="3" t="s">
         <v>3</v>
       </c>
@@ -5473,8 +5672,8 @@
       <c r="V83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="W83" s="3">
-        <v>0</v>
+      <c r="W83" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="X83" s="3">
         <v>0</v>
@@ -5482,8 +5681,11 @@
       <c r="Y83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5553,8 +5755,11 @@
       <c r="Y84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5624,8 +5829,11 @@
       <c r="Y85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5695,8 +5903,11 @@
       <c r="Y86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5766,8 +5977,11 @@
       <c r="Y87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5837,64 +6051,67 @@
       <c r="Y88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-26300</v>
+      </c>
+      <c r="E89" s="3">
         <v>-40500</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-37400</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-32000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-45100</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-30500</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-37700</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-72100</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-44300</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-42700</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-35500</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-31700</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-39200</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-9700</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-26100</v>
-      </c>
-      <c r="R89" s="3">
-        <v>-200</v>
       </c>
       <c r="S89" s="3">
         <v>-200</v>
       </c>
       <c r="T89" s="3">
-        <v>0</v>
-      </c>
-      <c r="U89" s="3" t="s">
-        <v>3</v>
+        <v>-200</v>
+      </c>
+      <c r="U89" s="3">
+        <v>0</v>
       </c>
       <c r="V89" s="3" t="s">
         <v>3</v>
@@ -5908,8 +6125,11 @@
       <c r="Y89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5935,53 +6155,54 @@
       <c r="W90" s="3"/>
       <c r="X90" s="3"/>
       <c r="Y90" s="3"/>
-    </row>
-    <row r="91" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z90" s="3"/>
+    </row>
+    <row r="91" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-6200</v>
+      </c>
+      <c r="E91" s="3">
         <v>-4000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-8300</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-11100</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-7200</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-2900</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-1300</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-7300</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-6400</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-5100</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-4200</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-3800</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-3100</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-4500</v>
       </c>
-      <c r="Q91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R91" s="3" t="s">
         <v>3</v>
       </c>
@@ -5997,8 +6218,8 @@
       <c r="V91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="W91" s="3">
-        <v>0</v>
+      <c r="W91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="X91" s="3">
         <v>0</v>
@@ -6006,8 +6227,11 @@
       <c r="Y91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6077,8 +6301,11 @@
       <c r="Y92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6148,58 +6375,61 @@
       <c r="Y93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-6300</v>
+      </c>
+      <c r="E94" s="3">
         <v>-4000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-8300</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-11100</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-7200</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-2900</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>1900</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-7300</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-6600</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-5100</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-3100</v>
-      </c>
-      <c r="N94" s="3">
-        <v>-4400</v>
       </c>
       <c r="O94" s="3">
         <v>-4400</v>
       </c>
       <c r="P94" s="3">
+        <v>-4400</v>
+      </c>
+      <c r="Q94" s="3">
         <v>-11400</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>170100</v>
       </c>
-      <c r="R94" s="3">
-        <v>0</v>
-      </c>
-      <c r="S94" s="3" t="s">
-        <v>3</v>
+      <c r="S94" s="3">
+        <v>0</v>
       </c>
       <c r="T94" s="3" t="s">
         <v>3</v>
@@ -6213,14 +6443,17 @@
       <c r="W94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="X94" s="3">
-        <v>0</v>
+      <c r="X94" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Y94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6246,8 +6479,9 @@
       <c r="W95" s="3"/>
       <c r="X95" s="3"/>
       <c r="Y95" s="3"/>
-    </row>
-    <row r="96" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z95" s="3"/>
+    </row>
+    <row r="96" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -6317,8 +6551,11 @@
       <c r="Y96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6388,8 +6625,11 @@
       <c r="Y97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6459,8 +6699,11 @@
       <c r="Y98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6530,65 +6773,68 @@
       <c r="Y99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>43900</v>
+      </c>
+      <c r="E100" s="3">
         <v>6100</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>57300</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>78000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>60200</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>32500</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>16000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>112900</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>11800</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-1200</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-400</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>106200</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>17600</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-100</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-23300</v>
       </c>
-      <c r="R100" s="3">
-        <v>0</v>
-      </c>
       <c r="S100" s="3">
+        <v>0</v>
+      </c>
+      <c r="T100" s="3">
         <v>177500</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>100</v>
       </c>
-      <c r="U100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V100" s="3" t="s">
         <v>3</v>
       </c>
@@ -6601,8 +6847,11 @@
       <c r="Y100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -6627,8 +6876,8 @@
       <c r="J101" s="3">
         <v>0</v>
       </c>
-      <c r="K101" s="3" t="s">
-        <v>3</v>
+      <c r="K101" s="3">
+        <v>0</v>
       </c>
       <c r="L101" s="3" t="s">
         <v>3</v>
@@ -6645,8 +6894,8 @@
       <c r="P101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q101" s="3">
-        <v>0</v>
+      <c r="Q101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R101" s="3">
         <v>0</v>
@@ -6672,64 +6921,67 @@
       <c r="Y101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:25" x14ac:dyDescent="0.2">
+      <c r="Z101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:26" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>11300</v>
+      </c>
+      <c r="E102" s="3">
         <v>-38400</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>11600</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>34900</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>7900</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-900</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-19800</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>33500</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-39100</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-49100</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-39000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>70000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-26000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-21100</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>120700</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-200</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>500</v>
       </c>
-      <c r="T102" s="3">
-        <v>0</v>
-      </c>
-      <c r="U102" s="3" t="s">
-        <v>3</v>
+      <c r="U102" s="3">
+        <v>0</v>
       </c>
       <c r="V102" s="3" t="s">
         <v>3</v>
@@ -6741,6 +6993,9 @@
         <v>3</v>
       </c>
       <c r="Y102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/EOSE_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/EOSE_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="364" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="376" uniqueCount="92">
   <si>
     <t>EOSE</t>
   </si>
@@ -656,101 +656,102 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Z102"/>
+  <dimension ref="A5:AA102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="26" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="27" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:27" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:26" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E7" s="2">
         <v>45473</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45382</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45291</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45199</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45107</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45016</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44926</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44834</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44742</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44651</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44561</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44469</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44377</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44286</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44196</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44104</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44012</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43921</v>
       </c>
-      <c r="V7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="W7" s="2" t="s">
         <v>3</v>
       </c>
@@ -763,8 +764,11 @@
       <c r="Z7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
@@ -772,49 +776,49 @@
         <v>900</v>
       </c>
       <c r="E8" s="3">
-        <v>6600</v>
+        <v>900</v>
       </c>
       <c r="F8" s="3">
         <v>6600</v>
       </c>
       <c r="G8" s="3">
+        <v>6600</v>
+      </c>
+      <c r="H8" s="3">
         <v>700</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>200</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>8800</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>2700</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>6100</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>5900</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>3300</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>3100</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>700</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>600</v>
-      </c>
-      <c r="Q8" s="3">
-        <v>200</v>
       </c>
       <c r="R8" s="3">
         <v>200</v>
       </c>
-      <c r="S8" s="3" t="s">
-        <v>3</v>
+      <c r="S8" s="3">
+        <v>200</v>
       </c>
       <c r="T8" s="3" t="s">
         <v>3</v>
@@ -831,65 +835,68 @@
       <c r="X8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Y8" s="3">
-        <v>0</v>
+      <c r="Y8" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Z8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>25800</v>
+      </c>
+      <c r="E9" s="3">
         <v>14100</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>28200</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>30400</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>21300</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>11200</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>26900</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>30800</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>50000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>36900</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>35600</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>21100</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>12900</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>12400</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>100</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>5500</v>
       </c>
-      <c r="S9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T9" s="3" t="s">
         <v>3</v>
       </c>
@@ -911,59 +918,62 @@
       <c r="Z9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>-24900</v>
+      </c>
+      <c r="E10" s="3">
         <v>-13200</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>-21600</v>
       </c>
-      <c r="F10" s="3">
-        <v>-23800</v>
-      </c>
       <c r="G10" s="3">
+        <v>-23700</v>
+      </c>
+      <c r="H10" s="3">
         <v>-20600</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>-11000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>-18100</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>-28100</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>-43900</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>-31000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>-32300</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>-18000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>-12200</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>-11800</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>100</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>-5300</v>
       </c>
-      <c r="S10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T10" s="3" t="s">
         <v>3</v>
       </c>
@@ -985,8 +995,11 @@
       <c r="Z10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1013,59 +1026,60 @@
       <c r="X11" s="3"/>
       <c r="Y11" s="3"/>
       <c r="Z11" s="3"/>
-    </row>
-    <row r="12" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA11" s="3"/>
+    </row>
+    <row r="12" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>7400</v>
+      </c>
+      <c r="E12" s="3">
         <v>4300</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>5200</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>5000</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>3200</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>5000</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>5400</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>3600</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>4500</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>5500</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>5000</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>5400</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>5100</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>3600</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>5000</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>14000</v>
       </c>
-      <c r="S12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T12" s="3" t="s">
         <v>3</v>
       </c>
@@ -1087,8 +1101,11 @@
       <c r="Z12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1161,58 +1178,61 @@
       <c r="Z13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>-68200</v>
+        <v>6200</v>
       </c>
       <c r="E14" s="3">
+        <v>-68000</v>
+      </c>
+      <c r="F14" s="3">
         <v>100</v>
       </c>
-      <c r="F14" s="3">
-        <v>0</v>
-      </c>
       <c r="G14" s="3">
+        <v>0</v>
+      </c>
+      <c r="H14" s="3">
         <v>1000</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>7300</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>2400</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>4300</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>1400</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>2000</v>
       </c>
-      <c r="M14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="N14" s="3">
-        <v>0</v>
+      <c r="N14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="O14" s="3">
+        <v>0</v>
+      </c>
+      <c r="P14" s="3">
         <v>-1300</v>
       </c>
-      <c r="P14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Q14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R14" s="3">
-        <v>0</v>
-      </c>
-      <c r="S14" s="3" t="s">
-        <v>3</v>
+      <c r="R14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S14" s="3">
+        <v>0</v>
       </c>
       <c r="T14" s="3" t="s">
         <v>3</v>
@@ -1220,8 +1240,8 @@
       <c r="U14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V14" s="3">
-        <v>0</v>
+      <c r="V14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="W14" s="3">
         <v>0</v>
@@ -1235,31 +1255,34 @@
       <c r="Z14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:27" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>0</v>
+        <v>2700</v>
       </c>
       <c r="E15" s="3">
-        <v>0</v>
+        <v>1400</v>
       </c>
       <c r="F15" s="3">
-        <v>0</v>
+        <v>1200</v>
       </c>
       <c r="G15" s="3">
-        <v>0</v>
+        <v>2400</v>
       </c>
       <c r="H15" s="3">
-        <v>0</v>
+        <v>2200</v>
       </c>
       <c r="I15" s="3">
-        <v>0</v>
+        <v>2500</v>
       </c>
       <c r="J15" s="3">
-        <v>0</v>
+        <v>2700</v>
       </c>
       <c r="K15" s="3">
         <v>0</v>
@@ -1309,8 +1332,11 @@
       <c r="Z15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:26" x14ac:dyDescent="0.2">
+      <c r="AA15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:27" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1334,67 +1360,68 @@
       <c r="X16" s="3"/>
       <c r="Y16" s="3"/>
       <c r="Z16" s="3"/>
-    </row>
-    <row r="17" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA16" s="3"/>
+    </row>
+    <row r="17" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>-38500</v>
+        <v>51000</v>
       </c>
       <c r="E17" s="3">
+        <v>29700</v>
+      </c>
+      <c r="F17" s="3">
         <v>47700</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>48800</v>
       </c>
-      <c r="G17" s="3">
-        <v>38500</v>
-      </c>
       <c r="H17" s="3">
-        <v>36700</v>
+        <v>37600</v>
       </c>
       <c r="I17" s="3">
-        <v>48700</v>
+        <v>29400</v>
       </c>
       <c r="J17" s="3">
+        <v>46300</v>
+      </c>
+      <c r="K17" s="3">
         <v>51300</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>70600</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>63300</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>55000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>40700</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>25700</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>49800</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>21800</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>37200</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>2000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>100</v>
       </c>
-      <c r="U17" s="3">
-        <v>0</v>
-      </c>
-      <c r="V17" s="3" t="s">
-        <v>3</v>
+      <c r="V17" s="3">
+        <v>0</v>
       </c>
       <c r="W17" s="3" t="s">
         <v>3</v>
@@ -1408,59 +1435,62 @@
       <c r="Z17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>39400</v>
+        <v>-50100</v>
       </c>
       <c r="E18" s="3">
+        <v>-28800</v>
+      </c>
+      <c r="F18" s="3">
         <v>-41100</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-42200</v>
       </c>
-      <c r="G18" s="3">
-        <v>-37800</v>
-      </c>
       <c r="H18" s="3">
-        <v>-36500</v>
+        <v>-36900</v>
       </c>
       <c r="I18" s="3">
-        <v>-39900</v>
+        <v>-29200</v>
       </c>
       <c r="J18" s="3">
+        <v>-37500</v>
+      </c>
+      <c r="K18" s="3">
         <v>-48600</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-64500</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-57400</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-51700</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-37600</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-25000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-49200</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-21600</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-37000</v>
       </c>
-      <c r="S18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1482,8 +1512,11 @@
       <c r="Z18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1510,59 +1543,60 @@
       <c r="X19" s="3"/>
       <c r="Y19" s="3"/>
       <c r="Z19" s="3"/>
-    </row>
-    <row r="20" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA19" s="3"/>
+    </row>
+    <row r="20" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>-59200</v>
+        <v>281100</v>
       </c>
       <c r="E20" s="3">
-        <v>3600</v>
+        <v>58900</v>
       </c>
       <c r="F20" s="3">
-        <v>9600</v>
+        <v>-3600</v>
       </c>
       <c r="G20" s="3">
-        <v>62200</v>
+        <v>-9600</v>
       </c>
       <c r="H20" s="3">
-        <v>-75500</v>
+        <v>-62200</v>
       </c>
       <c r="I20" s="3">
-        <v>-13100</v>
+        <v>75500</v>
       </c>
       <c r="J20" s="3">
-        <v>-400</v>
+        <v>13100</v>
       </c>
       <c r="K20" s="3">
         <v>-400</v>
       </c>
       <c r="L20" s="3">
+        <v>-400</v>
+      </c>
+      <c r="M20" s="3">
         <v>3600</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>8400</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>8300</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>10700</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-4700</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>200</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-5900</v>
       </c>
-      <c r="S20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T20" s="3" t="s">
         <v>3</v>
       </c>
@@ -1584,56 +1618,59 @@
       <c r="Z20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>-18400</v>
+        <v>-328600</v>
       </c>
       <c r="E21" s="3">
-        <v>-36400</v>
+        <v>-86300</v>
       </c>
       <c r="F21" s="3">
+        <v>-36300</v>
+      </c>
+      <c r="G21" s="3">
         <v>-30200</v>
       </c>
-      <c r="G21" s="3">
-        <v>26600</v>
-      </c>
       <c r="H21" s="3">
-        <v>-109500</v>
+        <v>27500</v>
       </c>
       <c r="I21" s="3">
-        <v>-50300</v>
+        <v>-102200</v>
       </c>
       <c r="J21" s="3">
+        <v>-47900</v>
+      </c>
+      <c r="K21" s="3">
         <v>-46000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-63300</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-52500</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-42300</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-28500</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-13700</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-53300</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-21000</v>
       </c>
-      <c r="R21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1658,59 +1695,62 @@
       <c r="Z21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>5400</v>
+      </c>
+      <c r="E22" s="3">
         <v>8400</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>9100</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>8600</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>9400</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>19600</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>18600</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>7600</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>5700</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>2900</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>2500</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>1300</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>3700</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>200</v>
       </c>
-      <c r="Q22" s="3">
-        <v>0</v>
-      </c>
       <c r="R22" s="3">
+        <v>0</v>
+      </c>
+      <c r="S22" s="3">
         <v>23800</v>
       </c>
-      <c r="S22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T22" s="3" t="s">
         <v>3</v>
       </c>
@@ -1726,73 +1766,76 @@
       <c r="X22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Y22" s="3">
-        <v>0</v>
+      <c r="Y22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Z22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-342900</v>
+      </c>
+      <c r="E23" s="3">
         <v>-28200</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-46700</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-41200</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>14900</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-131600</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-71600</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-56600</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-70600</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-56700</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-45800</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-30600</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-18100</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-54000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-21500</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-66700</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-2000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-100</v>
       </c>
-      <c r="U23" s="3">
-        <v>0</v>
-      </c>
-      <c r="V23" s="3" t="s">
-        <v>3</v>
+      <c r="V23" s="3">
+        <v>0</v>
       </c>
       <c r="W23" s="3" t="s">
         <v>3</v>
@@ -1806,8 +1849,11 @@
       <c r="Z23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1833,16 +1879,16 @@
         <v>0</v>
       </c>
       <c r="K24" s="3">
+        <v>0</v>
+      </c>
+      <c r="L24" s="3">
         <v>100</v>
       </c>
-      <c r="L24" s="3">
-        <v>0</v>
-      </c>
       <c r="M24" s="3">
         <v>0</v>
       </c>
-      <c r="N24" s="3" t="s">
-        <v>3</v>
+      <c r="N24" s="3">
+        <v>0</v>
       </c>
       <c r="O24" s="3" t="s">
         <v>3</v>
@@ -1859,8 +1905,8 @@
       <c r="S24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T24" s="3">
-        <v>0</v>
+      <c r="T24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="U24" s="3">
         <v>0</v>
@@ -1880,8 +1926,11 @@
       <c r="Z24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1954,67 +2003,70 @@
       <c r="Z25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-342900</v>
+      </c>
+      <c r="E26" s="3">
         <v>-28200</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-46700</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-41200</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>14900</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-131600</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-71600</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-56600</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-70700</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-56700</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-45800</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-30600</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-18100</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-54000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-21500</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-66700</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-2000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-100</v>
       </c>
-      <c r="U26" s="3">
-        <v>0</v>
-      </c>
-      <c r="V26" s="3" t="s">
-        <v>3</v>
+      <c r="V26" s="3">
+        <v>0</v>
       </c>
       <c r="W26" s="3" t="s">
         <v>3</v>
@@ -2028,67 +2080,70 @@
       <c r="Z26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-384100</v>
+      </c>
+      <c r="E27" s="3">
         <v>-51800</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-46700</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-41200</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>14900</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-131600</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-71600</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-56600</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-70700</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-56700</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-45800</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-30600</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-18100</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-54000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-21500</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-66700</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-2000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-100</v>
       </c>
-      <c r="U27" s="3">
-        <v>0</v>
-      </c>
-      <c r="V27" s="3" t="s">
-        <v>3</v>
+      <c r="V27" s="3">
+        <v>0</v>
       </c>
       <c r="W27" s="3" t="s">
         <v>3</v>
@@ -2102,8 +2157,11 @@
       <c r="Z27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2176,8 +2234,11 @@
       <c r="Z28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2250,8 +2311,11 @@
       <c r="Z29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2324,8 +2388,11 @@
       <c r="Z30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2398,59 +2465,62 @@
       <c r="Z31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>59200</v>
+        <v>-281100</v>
       </c>
       <c r="E32" s="3">
-        <v>-3600</v>
+        <v>-58900</v>
       </c>
       <c r="F32" s="3">
-        <v>-9600</v>
+        <v>3600</v>
       </c>
       <c r="G32" s="3">
-        <v>-62200</v>
+        <v>9600</v>
       </c>
       <c r="H32" s="3">
-        <v>75500</v>
+        <v>62200</v>
       </c>
       <c r="I32" s="3">
-        <v>13100</v>
+        <v>-75500</v>
       </c>
       <c r="J32" s="3">
-        <v>400</v>
+        <v>-13100</v>
       </c>
       <c r="K32" s="3">
         <v>400</v>
       </c>
       <c r="L32" s="3">
+        <v>400</v>
+      </c>
+      <c r="M32" s="3">
         <v>-3600</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-8400</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-8300</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-10700</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>4700</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-200</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>5900</v>
       </c>
-      <c r="S32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T32" s="3" t="s">
         <v>3</v>
       </c>
@@ -2472,67 +2542,70 @@
       <c r="Z32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>-51800</v>
+        <v>-342900</v>
       </c>
       <c r="E33" s="3">
+        <v>-28200</v>
+      </c>
+      <c r="F33" s="3">
         <v>-46700</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-41200</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>14900</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-131600</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-71600</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-56600</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-70700</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-56700</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-45800</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-30600</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-18100</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-54000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-21500</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-66700</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-2000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-100</v>
       </c>
-      <c r="U33" s="3">
-        <v>0</v>
-      </c>
-      <c r="V33" s="3" t="s">
-        <v>3</v>
+      <c r="V33" s="3">
+        <v>0</v>
       </c>
       <c r="W33" s="3" t="s">
         <v>3</v>
@@ -2546,8 +2619,11 @@
       <c r="Z33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2620,67 +2696,70 @@
       <c r="Z34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>-51800</v>
+        <v>-342900</v>
       </c>
       <c r="E35" s="3">
+        <v>-28200</v>
+      </c>
+      <c r="F35" s="3">
         <v>-46700</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-41200</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>14900</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-131600</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-71600</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-56600</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-70700</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-56700</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-45800</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-30600</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-18100</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-54000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-21500</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-66700</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-2000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-100</v>
       </c>
-      <c r="U35" s="3">
-        <v>0</v>
-      </c>
-      <c r="V35" s="3" t="s">
-        <v>3</v>
+      <c r="V35" s="3">
+        <v>0</v>
       </c>
       <c r="W35" s="3" t="s">
         <v>3</v>
@@ -2694,73 +2773,76 @@
       <c r="Z35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E38" s="2">
         <v>45473</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45382</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45291</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45199</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45107</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45016</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44926</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44834</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44742</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44651</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44561</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44469</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44377</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44286</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44196</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44104</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44012</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43921</v>
       </c>
-      <c r="V38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="W38" s="2" t="s">
         <v>3</v>
       </c>
@@ -2773,8 +2855,11 @@
       <c r="Z38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2801,8 +2886,9 @@
       <c r="X39" s="3"/>
       <c r="Y39" s="3"/>
       <c r="Z39" s="3"/>
-    </row>
-    <row r="40" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA39" s="3"/>
+    </row>
+    <row r="40" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2829,67 +2915,68 @@
       <c r="X40" s="3"/>
       <c r="Y40" s="3"/>
       <c r="Z40" s="3"/>
-    </row>
-    <row r="41" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA40" s="3"/>
+    </row>
+    <row r="41" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>23000</v>
+      </c>
+      <c r="E41" s="3">
         <v>52500</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>31800</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>69500</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>58000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>23200</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>16100</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>17100</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>38400</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>16300</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>55400</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>104800</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>144200</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>74700</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>100700</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>121900</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>300</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>500</v>
       </c>
-      <c r="U41" s="3">
-        <v>0</v>
-      </c>
-      <c r="V41" s="3" t="s">
-        <v>3</v>
+      <c r="V41" s="3">
+        <v>0</v>
       </c>
       <c r="W41" s="3" t="s">
         <v>3</v>
@@ -2903,8 +2990,11 @@
       <c r="Z41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2977,67 +3067,70 @@
       <c r="Z42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>82600</v>
+      </c>
+      <c r="E43" s="3">
         <v>100800</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>27300</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>20500</v>
       </c>
-      <c r="G43" s="3">
-        <v>4000</v>
-      </c>
       <c r="H43" s="3">
+        <v>4300</v>
+      </c>
+      <c r="I43" s="3">
+        <v>3900</v>
+      </c>
+      <c r="J43" s="3">
+        <v>7800</v>
+      </c>
+      <c r="K43" s="3">
         <v>3600</v>
       </c>
-      <c r="I43" s="3">
-        <v>7500</v>
-      </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
+        <v>6400</v>
+      </c>
+      <c r="M43" s="3">
         <v>3600</v>
       </c>
-      <c r="K43" s="3">
-        <v>6400</v>
-      </c>
-      <c r="L43" s="3">
-        <v>3600</v>
-      </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>3700</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>2000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>2400</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>400</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>300</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>100</v>
       </c>
-      <c r="S43" s="3">
-        <v>0</v>
-      </c>
       <c r="T43" s="3">
         <v>0</v>
       </c>
       <c r="U43" s="3">
         <v>0</v>
       </c>
-      <c r="V43" s="3" t="s">
-        <v>3</v>
+      <c r="V43" s="3">
+        <v>0</v>
       </c>
       <c r="W43" s="3" t="s">
         <v>3</v>
@@ -3051,59 +3144,62 @@
       <c r="Z43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>25900</v>
+      </c>
+      <c r="E44" s="3">
         <v>17800</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>14400</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>17100</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>20600</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>16600</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>14100</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>23300</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>23200</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>12900</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>10300</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>13000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>5000</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>4400</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>100</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>200</v>
       </c>
-      <c r="S44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T44" s="3" t="s">
         <v>3</v>
       </c>
@@ -3119,71 +3215,74 @@
       <c r="X44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Y44" s="3">
-        <v>0</v>
+      <c r="Y44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Z44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>12500</v>
+        <v>13900</v>
       </c>
       <c r="E45" s="3">
-        <v>13500</v>
+        <v>8600</v>
       </c>
       <c r="F45" s="3">
-        <v>15300</v>
+        <v>9600</v>
       </c>
       <c r="G45" s="3">
-        <v>25900</v>
+        <v>10700</v>
       </c>
       <c r="H45" s="3">
-        <v>20500</v>
+        <v>21400</v>
       </c>
       <c r="I45" s="3">
-        <v>12300</v>
+        <v>15500</v>
       </c>
       <c r="J45" s="3">
+        <v>7400</v>
+      </c>
+      <c r="K45" s="3">
         <v>11300</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>13600</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>27600</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>26800</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>22700</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>17400</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>12200</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>6200</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>5200</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>200</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>300</v>
       </c>
-      <c r="U45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V45" s="3" t="s">
         <v>3</v>
       </c>
@@ -3199,67 +3298,70 @@
       <c r="Z45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>149200</v>
+      </c>
+      <c r="E46" s="3">
         <v>183500</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>87000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>122300</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>108500</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>64000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>50000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>55100</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>81600</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>60500</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>96200</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>142600</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>169100</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>91700</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>107400</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>127400</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>600</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>800</v>
       </c>
-      <c r="U46" s="3">
-        <v>0</v>
-      </c>
-      <c r="V46" s="3" t="s">
-        <v>3</v>
+      <c r="V46" s="3">
+        <v>0</v>
       </c>
       <c r="W46" s="3" t="s">
         <v>3</v>
@@ -3273,8 +3375,11 @@
       <c r="Z46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3287,45 +3392,45 @@
       <c r="F47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G47" s="3">
+      <c r="G47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K47" s="3">
         <v>800</v>
-      </c>
-      <c r="H47" s="3">
-        <v>800</v>
-      </c>
-      <c r="I47" s="3">
-        <v>800</v>
-      </c>
-      <c r="J47" s="3">
-        <v>800</v>
-      </c>
-      <c r="K47" s="3">
-        <v>3700</v>
       </c>
       <c r="L47" s="3">
         <v>3700</v>
       </c>
       <c r="M47" s="3">
-        <v>3500</v>
+        <v>3700</v>
       </c>
       <c r="N47" s="3">
         <v>3500</v>
       </c>
       <c r="O47" s="3">
+        <v>3500</v>
+      </c>
+      <c r="P47" s="3">
         <v>4700</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>4100</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>11100</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>3700</v>
       </c>
-      <c r="S47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T47" s="3" t="s">
         <v>3</v>
       </c>
@@ -3341,65 +3446,68 @@
       <c r="X47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Y47" s="3">
-        <v>0</v>
+      <c r="Y47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Z47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>54600</v>
+      </c>
+      <c r="E48" s="3">
         <v>54000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>46500</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>41900</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>24300</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>23900</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>28700</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>31500</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>34400</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>25800</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>19500</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>16400</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>10300</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>8400</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>8000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>5700</v>
       </c>
-      <c r="S48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T48" s="3" t="s">
         <v>3</v>
       </c>
@@ -3415,14 +3523,17 @@
       <c r="X48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Y48" s="3">
-        <v>0</v>
+      <c r="Y48" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Z48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -3439,13 +3550,13 @@
         <v>4600</v>
       </c>
       <c r="H49" s="3">
-        <v>4700</v>
+        <v>4600</v>
       </c>
       <c r="I49" s="3">
         <v>4700</v>
       </c>
       <c r="J49" s="3">
-        <v>4600</v>
+        <v>4700</v>
       </c>
       <c r="K49" s="3">
         <v>4600</v>
@@ -3466,13 +3577,13 @@
         <v>4600</v>
       </c>
       <c r="Q49" s="3">
-        <v>300</v>
+        <v>4600</v>
       </c>
       <c r="R49" s="3">
         <v>300</v>
       </c>
-      <c r="S49" s="3" t="s">
-        <v>3</v>
+      <c r="S49" s="3">
+        <v>300</v>
       </c>
       <c r="T49" s="3" t="s">
         <v>3</v>
@@ -3489,14 +3600,17 @@
       <c r="X49" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Y49" s="3">
-        <v>0</v>
+      <c r="Y49" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Z49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3569,8 +3683,11 @@
       <c r="Z50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3643,68 +3760,71 @@
       <c r="Z51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>6600</v>
+        <v>7300</v>
       </c>
       <c r="E52" s="3">
-        <v>17600</v>
+        <v>4900</v>
       </c>
       <c r="F52" s="3">
         <v>17600</v>
       </c>
       <c r="G52" s="3">
+        <v>14200</v>
+      </c>
+      <c r="H52" s="3">
         <v>15900</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>15600</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>15500</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>14800</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>14200</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>3200</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>3100</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>2100</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>1400</v>
-      </c>
-      <c r="P52" s="3">
-        <v>1000</v>
       </c>
       <c r="Q52" s="3">
         <v>1000</v>
       </c>
       <c r="R52" s="3">
+        <v>1000</v>
+      </c>
+      <c r="S52" s="3">
         <v>1200</v>
-      </c>
-      <c r="S52" s="3">
-        <v>176800</v>
       </c>
       <c r="T52" s="3">
         <v>176800</v>
       </c>
       <c r="U52" s="3">
+        <v>176800</v>
+      </c>
+      <c r="V52" s="3">
         <v>100</v>
       </c>
-      <c r="V52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W52" s="3" t="s">
         <v>3</v>
       </c>
@@ -3717,8 +3837,11 @@
       <c r="Z52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3791,68 +3914,71 @@
       <c r="Z53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>216800</v>
+      </c>
+      <c r="E54" s="3">
         <v>248800</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>155700</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>186500</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>154100</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>109000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>99700</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>106800</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>138500</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>97700</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>126900</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>169200</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>190100</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>109900</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>127800</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>138300</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>177300</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>177500</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>100</v>
       </c>
-      <c r="V54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3865,8 +3991,11 @@
       <c r="Z54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3893,8 +4022,9 @@
       <c r="X55" s="3"/>
       <c r="Y55" s="3"/>
       <c r="Z55" s="3"/>
-    </row>
-    <row r="56" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA55" s="3"/>
+    </row>
+    <row r="56" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3921,67 +4051,68 @@
       <c r="X56" s="3"/>
       <c r="Y56" s="3"/>
       <c r="Z56" s="3"/>
-    </row>
-    <row r="57" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA56" s="3"/>
+    </row>
+    <row r="57" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>24300</v>
+      </c>
+      <c r="E57" s="3">
         <v>24100</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>18300</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>20500</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>13800</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>15400</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>32500</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>34700</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>35500</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>29100</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>11700</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>13700</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>13200</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>15200</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>20200</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>11400</v>
       </c>
-      <c r="S57" s="3">
-        <v>0</v>
-      </c>
       <c r="T57" s="3">
         <v>0</v>
       </c>
       <c r="U57" s="3">
         <v>0</v>
       </c>
-      <c r="V57" s="3" t="s">
-        <v>3</v>
+      <c r="V57" s="3">
+        <v>0</v>
       </c>
       <c r="W57" s="3" t="s">
         <v>3</v>
@@ -3995,68 +4126,71 @@
       <c r="Z57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>3000</v>
+        <v>4300</v>
       </c>
       <c r="E58" s="3">
-        <v>3500</v>
+        <v>5500</v>
       </c>
       <c r="F58" s="3">
-        <v>3400</v>
+        <v>5100</v>
       </c>
       <c r="G58" s="3">
-        <v>3200</v>
+        <v>4900</v>
       </c>
       <c r="H58" s="3">
-        <v>3100</v>
+        <v>4600</v>
       </c>
       <c r="I58" s="3">
-        <v>11200</v>
+        <v>4400</v>
       </c>
       <c r="J58" s="3">
+        <v>12400</v>
+      </c>
+      <c r="K58" s="3">
         <v>5600</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>2900</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>14000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>6700</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>6600</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>6500</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>6100</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>1200</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>1100</v>
       </c>
-      <c r="S58" s="3">
-        <v>0</v>
-      </c>
       <c r="T58" s="3">
         <v>0</v>
       </c>
       <c r="U58" s="3">
+        <v>0</v>
+      </c>
+      <c r="V58" s="3">
         <v>100</v>
       </c>
-      <c r="V58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W58" s="3" t="s">
         <v>3</v>
       </c>
@@ -4069,64 +4203,67 @@
       <c r="Z58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>41300</v>
+        <v>17100</v>
       </c>
       <c r="E59" s="3">
-        <v>43100</v>
+        <v>13500</v>
       </c>
       <c r="F59" s="3">
-        <v>36900</v>
+        <v>11500</v>
       </c>
       <c r="G59" s="3">
-        <v>29700</v>
+        <v>12600</v>
       </c>
       <c r="H59" s="3">
-        <v>24500</v>
+        <v>13000</v>
       </c>
       <c r="I59" s="3">
-        <v>21900</v>
+        <v>9000</v>
       </c>
       <c r="J59" s="3">
+        <v>6300</v>
+      </c>
+      <c r="K59" s="3">
         <v>20300</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>17500</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>16600</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>15500</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>9600</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>1200</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>3400</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>800</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>1700</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>1800</v>
       </c>
-      <c r="T59" s="3">
-        <v>0</v>
-      </c>
-      <c r="U59" s="3" t="s">
-        <v>3</v>
+      <c r="U59" s="3">
+        <v>0</v>
       </c>
       <c r="V59" s="3" t="s">
         <v>3</v>
@@ -4143,67 +4280,70 @@
       <c r="Z59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>75100</v>
+      </c>
+      <c r="E60" s="3">
         <v>68500</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>64900</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>60900</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>46800</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>43000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>65700</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>60600</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>55800</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>59600</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>33800</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>29900</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>20900</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>24600</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>22200</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>14100</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>1900</v>
-      </c>
-      <c r="T60" s="3">
-        <v>100</v>
       </c>
       <c r="U60" s="3">
         <v>100</v>
       </c>
-      <c r="V60" s="3" t="s">
-        <v>3</v>
+      <c r="V60" s="3">
+        <v>100</v>
       </c>
       <c r="W60" s="3" t="s">
         <v>3</v>
@@ -4217,59 +4357,62 @@
       <c r="Z60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>150200</v>
+        <v>187000</v>
       </c>
       <c r="E61" s="3">
-        <v>202200</v>
+        <v>152800</v>
       </c>
       <c r="F61" s="3">
-        <v>200600</v>
+        <v>206700</v>
       </c>
       <c r="G61" s="3">
-        <v>204100</v>
+        <v>204000</v>
       </c>
       <c r="H61" s="3">
-        <v>229500</v>
+        <v>207500</v>
       </c>
       <c r="I61" s="3">
-        <v>198600</v>
+        <v>233300</v>
       </c>
       <c r="J61" s="3">
+        <v>202400</v>
+      </c>
+      <c r="K61" s="3">
         <v>170400</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>160800</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>90300</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>95300</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>102700</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>106800</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>13500</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>100</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>300</v>
       </c>
-      <c r="S61" s="3">
-        <v>0</v>
-      </c>
       <c r="T61" s="3">
         <v>0</v>
       </c>
@@ -4291,59 +4434,62 @@
       <c r="Z61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>180800</v>
+        <v>369100</v>
       </c>
       <c r="E62" s="3">
-        <v>36300</v>
+        <v>173800</v>
       </c>
       <c r="F62" s="3">
-        <v>35800</v>
+        <v>27500</v>
       </c>
       <c r="G62" s="3">
-        <v>31600</v>
+        <v>28900</v>
       </c>
       <c r="H62" s="3">
-        <v>65900</v>
+        <v>27100</v>
       </c>
       <c r="I62" s="3">
-        <v>11100</v>
+        <v>61200</v>
       </c>
       <c r="J62" s="3">
+        <v>6300</v>
+      </c>
+      <c r="K62" s="3">
         <v>8500</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>10100</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>5700</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>8000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>4200</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>3900</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>3100</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>3700</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>800</v>
       </c>
-      <c r="S62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T62" s="3" t="s">
         <v>3</v>
       </c>
@@ -4359,14 +4505,17 @@
       <c r="X62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Y62" s="3">
-        <v>0</v>
+      <c r="Y62" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Z62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4439,8 +4588,11 @@
       <c r="Z63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4513,8 +4665,11 @@
       <c r="Z64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4587,67 +4742,70 @@
       <c r="Z65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>634500</v>
+      </c>
+      <c r="E66" s="3">
         <v>399500</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>303400</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>297300</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>282400</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>338500</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>275300</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>239500</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>226800</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>155600</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>137100</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>136700</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>131700</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>41300</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>26000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>15200</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>1900</v>
-      </c>
-      <c r="T66" s="3">
-        <v>100</v>
       </c>
       <c r="U66" s="3">
         <v>100</v>
       </c>
-      <c r="V66" s="3" t="s">
-        <v>3</v>
+      <c r="V66" s="3">
+        <v>100</v>
       </c>
       <c r="W66" s="3" t="s">
         <v>3</v>
@@ -4661,8 +4819,11 @@
       <c r="Z66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4689,8 +4850,9 @@
       <c r="X67" s="3"/>
       <c r="Y67" s="3"/>
       <c r="Z67" s="3"/>
-    </row>
-    <row r="68" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA67" s="3"/>
+    </row>
+    <row r="68" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4763,8 +4925,11 @@
       <c r="Z68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4837,17 +5002,20 @@
       <c r="Z69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
       <c r="D70" s="3">
+        <v>156100</v>
+      </c>
+      <c r="E70" s="3">
         <v>40100</v>
       </c>
-      <c r="E70" s="3">
-        <v>0</v>
-      </c>
       <c r="F70" s="3">
         <v>0</v>
       </c>
@@ -4911,8 +5079,11 @@
       <c r="Z70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4985,67 +5156,70 @@
       <c r="Z71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-1293600</v>
+      </c>
+      <c r="E72" s="3">
         <v>-950700</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-922600</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-875800</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-834600</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-849600</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-717900</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-646300</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-589700</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-519000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-462300</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-416500</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-385900</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-367800</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-313800</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-290800</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-2000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-100</v>
       </c>
-      <c r="U72" s="3">
-        <v>0</v>
-      </c>
-      <c r="V72" s="3" t="s">
-        <v>3</v>
+      <c r="V72" s="3">
+        <v>0</v>
       </c>
       <c r="W72" s="3" t="s">
         <v>3</v>
@@ -5059,8 +5233,11 @@
       <c r="Z72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5133,8 +5310,11 @@
       <c r="Z73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5207,8 +5387,11 @@
       <c r="Z74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5281,67 +5464,70 @@
       <c r="Z75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>-573800</v>
+      </c>
+      <c r="E76" s="3">
         <v>-190800</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>-147700</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>-110800</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>-128300</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>-229500</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>-175600</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>-132700</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>-88300</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>-57800</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>-10200</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>32400</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>58400</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>68600</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>101800</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>123100</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>175500</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>177400</v>
       </c>
-      <c r="U76" s="3">
-        <v>0</v>
-      </c>
-      <c r="V76" s="3" t="s">
-        <v>3</v>
+      <c r="V76" s="3">
+        <v>0</v>
       </c>
       <c r="W76" s="3" t="s">
         <v>3</v>
@@ -5355,8 +5541,11 @@
       <c r="Z76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5429,73 +5618,76 @@
       <c r="Z77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:26" x14ac:dyDescent="0.2">
+      <c r="AA77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:27" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:26" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:27" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E80" s="2">
         <v>45473</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45382</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45291</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45199</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45107</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45016</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44926</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44834</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44742</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44651</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44561</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44469</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44377</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44286</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44196</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44104</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44012</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43921</v>
       </c>
-      <c r="V80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="W80" s="2" t="s">
         <v>3</v>
       </c>
@@ -5508,67 +5700,70 @@
       <c r="Z80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>-51800</v>
+        <v>-342900</v>
       </c>
       <c r="E81" s="3">
+        <v>-28200</v>
+      </c>
+      <c r="F81" s="3">
         <v>-46700</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-41200</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>14900</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-131600</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-71600</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-56600</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-70700</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-56700</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-45800</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-30600</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-18100</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-54000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-21500</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-66700</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-2000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-100</v>
       </c>
-      <c r="U81" s="3">
-        <v>0</v>
-      </c>
-      <c r="V81" s="3" t="s">
-        <v>3</v>
+      <c r="V81" s="3">
+        <v>0</v>
       </c>
       <c r="W81" s="3" t="s">
         <v>3</v>
@@ -5582,8 +5777,11 @@
       <c r="Z81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5610,56 +5808,57 @@
       <c r="X82" s="3"/>
       <c r="Y82" s="3"/>
       <c r="Z82" s="3"/>
-    </row>
-    <row r="83" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA82" s="3"/>
+    </row>
+    <row r="83" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>1400</v>
+        <v>2400</v>
       </c>
       <c r="E83" s="3">
+        <v>2700</v>
+      </c>
+      <c r="F83" s="3">
+        <v>2900</v>
+      </c>
+      <c r="G83" s="3">
+        <v>3200</v>
+      </c>
+      <c r="H83" s="3">
+        <v>1800</v>
+      </c>
+      <c r="I83" s="3">
+        <v>1500</v>
+      </c>
+      <c r="J83" s="3">
         <v>1200</v>
       </c>
-      <c r="F83" s="3">
-        <v>2400</v>
-      </c>
-      <c r="G83" s="3">
-        <v>2200</v>
-      </c>
-      <c r="H83" s="3">
-        <v>2500</v>
-      </c>
-      <c r="I83" s="3">
-        <v>2700</v>
-      </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>3000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>1600</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>1300</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>1000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>800</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>700</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>600</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>500</v>
       </c>
-      <c r="R83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S83" s="3" t="s">
         <v>3</v>
       </c>
@@ -5675,8 +5874,8 @@
       <c r="W83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="X83" s="3">
-        <v>0</v>
+      <c r="X83" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Y83" s="3">
         <v>0</v>
@@ -5684,8 +5883,11 @@
       <c r="Z83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5758,8 +5960,11 @@
       <c r="Z84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5832,8 +6037,11 @@
       <c r="Z85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5906,8 +6114,11 @@
       <c r="Z86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5980,8 +6191,11 @@
       <c r="Z87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6054,67 +6268,70 @@
       <c r="Z88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-44400</v>
+      </c>
+      <c r="E89" s="3">
         <v>-26300</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-40500</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-37400</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-32000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-45100</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-30500</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-37700</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-72100</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-44300</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-42700</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-35500</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-31700</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-39200</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-9700</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-26100</v>
-      </c>
-      <c r="S89" s="3">
-        <v>-200</v>
       </c>
       <c r="T89" s="3">
         <v>-200</v>
       </c>
       <c r="U89" s="3">
-        <v>0</v>
-      </c>
-      <c r="V89" s="3" t="s">
-        <v>3</v>
+        <v>-200</v>
+      </c>
+      <c r="V89" s="3">
+        <v>0</v>
       </c>
       <c r="W89" s="3" t="s">
         <v>3</v>
@@ -6128,8 +6345,11 @@
       <c r="Z89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6156,56 +6376,57 @@
       <c r="X90" s="3"/>
       <c r="Y90" s="3"/>
       <c r="Z90" s="3"/>
-    </row>
-    <row r="91" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA90" s="3"/>
+    </row>
+    <row r="91" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-9800</v>
+      </c>
+      <c r="E91" s="3">
         <v>-6200</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-4000</v>
       </c>
-      <c r="F91" s="3">
-        <v>-8300</v>
-      </c>
       <c r="G91" s="3">
+        <v>-8100</v>
+      </c>
+      <c r="H91" s="3">
         <v>-11100</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-7200</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-2900</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-1300</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-7300</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-6400</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-5100</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-4200</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-3800</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-3100</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-4500</v>
       </c>
-      <c r="R91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S91" s="3" t="s">
         <v>3</v>
       </c>
@@ -6221,8 +6442,8 @@
       <c r="W91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="X91" s="3">
-        <v>0</v>
+      <c r="X91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Y91" s="3">
         <v>0</v>
@@ -6230,8 +6451,11 @@
       <c r="Z91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6304,8 +6528,11 @@
       <c r="Z92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6378,61 +6605,64 @@
       <c r="Z93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-9800</v>
+      </c>
+      <c r="E94" s="3">
         <v>-6300</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-4000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-8300</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-11100</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-7200</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-2900</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>1900</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-7300</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-6600</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-5100</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-3100</v>
-      </c>
-      <c r="O94" s="3">
-        <v>-4400</v>
       </c>
       <c r="P94" s="3">
         <v>-4400</v>
       </c>
       <c r="Q94" s="3">
+        <v>-4400</v>
+      </c>
+      <c r="R94" s="3">
         <v>-11400</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>170100</v>
       </c>
-      <c r="S94" s="3">
-        <v>0</v>
-      </c>
-      <c r="T94" s="3" t="s">
-        <v>3</v>
+      <c r="T94" s="3">
+        <v>0</v>
       </c>
       <c r="U94" s="3" t="s">
         <v>3</v>
@@ -6446,14 +6676,17 @@
       <c r="X94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Y94" s="3">
-        <v>0</v>
+      <c r="Y94" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Z94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6480,31 +6713,32 @@
       <c r="X95" s="3"/>
       <c r="Y95" s="3"/>
       <c r="Z95" s="3"/>
-    </row>
-    <row r="96" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA95" s="3"/>
+    </row>
+    <row r="96" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3">
-        <v>0</v>
-      </c>
-      <c r="E96" s="3">
-        <v>0</v>
-      </c>
-      <c r="F96" s="3">
-        <v>0</v>
-      </c>
-      <c r="G96" s="3">
-        <v>0</v>
-      </c>
-      <c r="H96" s="3">
-        <v>0</v>
-      </c>
-      <c r="I96" s="3">
-        <v>0</v>
-      </c>
-      <c r="J96" s="3">
-        <v>0</v>
+      <c r="D96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I96" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K96" s="3">
         <v>0</v>
@@ -6554,8 +6788,11 @@
       <c r="Z96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6628,8 +6865,11 @@
       <c r="Z97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6702,8 +6942,11 @@
       <c r="Z98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6776,68 +7019,71 @@
       <c r="Z99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>27300</v>
+      </c>
+      <c r="E100" s="3">
         <v>43900</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>6100</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>57300</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>78000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>60200</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>32500</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>16000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>112900</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>11800</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-1200</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-400</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>106200</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>17600</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-100</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-23300</v>
       </c>
-      <c r="S100" s="3">
-        <v>0</v>
-      </c>
       <c r="T100" s="3">
+        <v>0</v>
+      </c>
+      <c r="U100" s="3">
         <v>177500</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>100</v>
       </c>
-      <c r="V100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W100" s="3" t="s">
         <v>3</v>
       </c>
@@ -6850,8 +7096,11 @@
       <c r="Z100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -6873,14 +7122,14 @@
       <c r="I101" s="3">
         <v>0</v>
       </c>
-      <c r="J101" s="3">
-        <v>0</v>
+      <c r="J101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K101" s="3">
         <v>0</v>
       </c>
-      <c r="L101" s="3" t="s">
-        <v>3</v>
+      <c r="L101" s="3">
+        <v>0</v>
       </c>
       <c r="M101" s="3" t="s">
         <v>3</v>
@@ -6897,8 +7146,8 @@
       <c r="Q101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R101" s="3">
-        <v>0</v>
+      <c r="R101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="S101" s="3">
         <v>0</v>
@@ -6924,67 +7173,70 @@
       <c r="Z101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:26" x14ac:dyDescent="0.2">
+      <c r="AA101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:27" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-26900</v>
+      </c>
+      <c r="E102" s="3">
         <v>11300</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-38400</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>11600</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>34900</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>7900</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-900</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-19800</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>33500</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-39100</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-49100</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-39000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>70000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-26000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-21100</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>120700</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-200</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>500</v>
       </c>
-      <c r="U102" s="3">
-        <v>0</v>
-      </c>
-      <c r="V102" s="3" t="s">
-        <v>3</v>
+      <c r="V102" s="3">
+        <v>0</v>
       </c>
       <c r="W102" s="3" t="s">
         <v>3</v>
@@ -6996,6 +7248,9 @@
         <v>3</v>
       </c>
       <c r="Z102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/EOSE_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/EOSE_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="376" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="378" uniqueCount="92">
   <si>
     <t>EOSE</t>
   </si>
@@ -656,105 +656,105 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AA102"/>
+  <dimension ref="A5:AB102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="27" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="28" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:28" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:28" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
         <v>45565</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45473</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45382</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45291</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45199</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45107</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45016</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44926</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44834</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44742</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44651</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44561</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44469</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44377</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44286</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44196</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44104</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44012</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43921</v>
       </c>
-      <c r="W7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="X7" s="2" t="s">
         <v>3</v>
       </c>
@@ -767,61 +767,64 @@
       <c r="AA7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
-        <v>900</v>
+        <v>7300</v>
       </c>
       <c r="E8" s="3">
         <v>900</v>
       </c>
       <c r="F8" s="3">
-        <v>6600</v>
+        <v>900</v>
       </c>
       <c r="G8" s="3">
         <v>6600</v>
       </c>
       <c r="H8" s="3">
+        <v>6600</v>
+      </c>
+      <c r="I8" s="3">
         <v>700</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>200</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>8800</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>2700</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>6100</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>5900</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>3300</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>3100</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>700</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>600</v>
-      </c>
-      <c r="R8" s="3">
-        <v>200</v>
       </c>
       <c r="S8" s="3">
         <v>200</v>
       </c>
-      <c r="T8" s="3" t="s">
-        <v>3</v>
+      <c r="T8" s="3">
+        <v>200</v>
       </c>
       <c r="U8" s="3" t="s">
         <v>3</v>
@@ -838,68 +841,71 @@
       <c r="Y8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Z8" s="3">
-        <v>0</v>
+      <c r="Z8" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AA8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>30800</v>
+      </c>
+      <c r="E9" s="3">
         <v>25800</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>14100</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>28200</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>30400</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>21300</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>11200</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>26900</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>30800</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>50000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>36900</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>35600</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>21100</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>12900</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>12400</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>100</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>5500</v>
       </c>
-      <c r="T9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U9" s="3" t="s">
         <v>3</v>
       </c>
@@ -921,62 +927,65 @@
       <c r="AA9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>-23500</v>
+      </c>
+      <c r="E10" s="3">
         <v>-24900</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>-13200</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>-21600</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>-23700</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>-20600</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>-11000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>-18100</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>-28100</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>-43900</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>-31000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>-32300</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>-18000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>-12200</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>-11800</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>100</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>-5300</v>
       </c>
-      <c r="T10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U10" s="3" t="s">
         <v>3</v>
       </c>
@@ -998,8 +1007,11 @@
       <c r="AA10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1027,62 +1039,63 @@
       <c r="Y11" s="3"/>
       <c r="Z11" s="3"/>
       <c r="AA11" s="3"/>
-    </row>
-    <row r="12" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB11" s="3"/>
+    </row>
+    <row r="12" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>5900</v>
+      </c>
+      <c r="E12" s="3">
         <v>7400</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>4300</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>5200</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>5000</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>3200</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>5000</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>5400</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>3600</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>4500</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>5500</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>5000</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>5400</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>5100</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>3600</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>5000</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>14000</v>
       </c>
-      <c r="T12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U12" s="3" t="s">
         <v>3</v>
       </c>
@@ -1104,8 +1117,11 @@
       <c r="AA12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1181,61 +1197,64 @@
       <c r="AA13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>-31500</v>
+      </c>
+      <c r="E14" s="3">
         <v>6200</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>-68000</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>100</v>
       </c>
-      <c r="G14" s="3">
-        <v>0</v>
-      </c>
       <c r="H14" s="3">
+        <v>0</v>
+      </c>
+      <c r="I14" s="3">
         <v>1000</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>7300</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>2400</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>4300</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>1400</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>2000</v>
       </c>
-      <c r="N14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O14" s="3">
-        <v>0</v>
+      <c r="O14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="3">
         <v>-1300</v>
       </c>
-      <c r="Q14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="R14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S14" s="3">
-        <v>0</v>
-      </c>
-      <c r="T14" s="3" t="s">
-        <v>3</v>
+      <c r="S14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="T14" s="3">
+        <v>0</v>
       </c>
       <c r="U14" s="3" t="s">
         <v>3</v>
@@ -1243,8 +1262,8 @@
       <c r="V14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="W14" s="3">
-        <v>0</v>
+      <c r="W14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="X14" s="3">
         <v>0</v>
@@ -1258,35 +1277,38 @@
       <c r="AA14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:28" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>2600</v>
+      </c>
+      <c r="E15" s="3">
         <v>2700</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>1400</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>1200</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>2400</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>2200</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>2500</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>2700</v>
       </c>
-      <c r="K15" s="3">
-        <v>0</v>
-      </c>
       <c r="L15" s="3">
         <v>0</v>
       </c>
@@ -1335,8 +1357,11 @@
       <c r="AA15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:28" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1361,70 +1386,71 @@
       <c r="Y16" s="3"/>
       <c r="Z16" s="3"/>
       <c r="AA16" s="3"/>
-    </row>
-    <row r="17" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB16" s="3"/>
+    </row>
+    <row r="17" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>53300</v>
+      </c>
+      <c r="E17" s="3">
         <v>51000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>29700</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>47700</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>48800</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>37600</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>29400</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>46300</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>51300</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>70600</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>63300</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>55000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>40700</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>25700</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>49800</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>21800</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>37200</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>2000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>100</v>
       </c>
-      <c r="V17" s="3">
-        <v>0</v>
-      </c>
-      <c r="W17" s="3" t="s">
-        <v>3</v>
+      <c r="W17" s="3">
+        <v>0</v>
       </c>
       <c r="X17" s="3" t="s">
         <v>3</v>
@@ -1438,62 +1464,65 @@
       <c r="AA17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-46100</v>
+      </c>
+      <c r="E18" s="3">
         <v>-50100</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-28800</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-41100</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-42200</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-36900</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-29200</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-37500</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-48600</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-64500</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-57400</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-51700</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-37600</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-25000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-49200</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-21600</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-37000</v>
       </c>
-      <c r="T18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1515,8 +1544,11 @@
       <c r="AA18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1544,62 +1576,63 @@
       <c r="Y19" s="3"/>
       <c r="Z19" s="3"/>
       <c r="AA19" s="3"/>
-    </row>
-    <row r="20" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB19" s="3"/>
+    </row>
+    <row r="20" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>248300</v>
+      </c>
+      <c r="E20" s="3">
         <v>281100</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>58900</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-3600</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-9600</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-62200</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>75500</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>13100</v>
-      </c>
-      <c r="K20" s="3">
-        <v>-400</v>
       </c>
       <c r="L20" s="3">
         <v>-400</v>
       </c>
       <c r="M20" s="3">
+        <v>-400</v>
+      </c>
+      <c r="N20" s="3">
         <v>3600</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>8400</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>8300</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>10700</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-4700</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>200</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-5900</v>
       </c>
-      <c r="T20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U20" s="3" t="s">
         <v>3</v>
       </c>
@@ -1621,59 +1654,62 @@
       <c r="AA20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-291700</v>
+      </c>
+      <c r="E21" s="3">
         <v>-328600</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-86300</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-36300</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-30200</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>27500</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-102200</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-47900</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-46000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-63300</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-52500</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-42300</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-28500</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-13700</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-53300</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-21000</v>
       </c>
-      <c r="S21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1698,62 +1734,65 @@
       <c r="AA21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>5200</v>
+      </c>
+      <c r="E22" s="3">
         <v>5400</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>8400</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>9100</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>8600</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>9400</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>19600</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>18600</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>7600</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>5700</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>2900</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>2500</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>1300</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>3700</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>200</v>
       </c>
-      <c r="R22" s="3">
-        <v>0</v>
-      </c>
       <c r="S22" s="3">
+        <v>0</v>
+      </c>
+      <c r="T22" s="3">
         <v>23800</v>
       </c>
-      <c r="T22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U22" s="3" t="s">
         <v>3</v>
       </c>
@@ -1769,76 +1808,79 @@
       <c r="Y22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Z22" s="3">
-        <v>0</v>
+      <c r="Z22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AA22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-268100</v>
+      </c>
+      <c r="E23" s="3">
         <v>-342900</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-28200</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-46700</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-41200</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>14900</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-131600</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-71600</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-56600</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-70600</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-56700</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-45800</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-30600</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-18100</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-54000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-21500</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-66700</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-2000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-100</v>
       </c>
-      <c r="V23" s="3">
-        <v>0</v>
-      </c>
-      <c r="W23" s="3" t="s">
-        <v>3</v>
+      <c r="W23" s="3">
+        <v>0</v>
       </c>
       <c r="X23" s="3" t="s">
         <v>3</v>
@@ -1852,8 +1894,11 @@
       <c r="AA23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1882,16 +1927,16 @@
         <v>0</v>
       </c>
       <c r="L24" s="3">
+        <v>0</v>
+      </c>
+      <c r="M24" s="3">
         <v>100</v>
       </c>
-      <c r="M24" s="3">
-        <v>0</v>
-      </c>
       <c r="N24" s="3">
         <v>0</v>
       </c>
-      <c r="O24" s="3" t="s">
-        <v>3</v>
+      <c r="O24" s="3">
+        <v>0</v>
       </c>
       <c r="P24" s="3" t="s">
         <v>3</v>
@@ -1908,8 +1953,8 @@
       <c r="T24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U24" s="3">
-        <v>0</v>
+      <c r="U24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="V24" s="3">
         <v>0</v>
@@ -1929,8 +1974,11 @@
       <c r="AA24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2006,70 +2054,73 @@
       <c r="AA25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-268100</v>
+      </c>
+      <c r="E26" s="3">
         <v>-342900</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-28200</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-46700</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-41200</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>14900</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-131600</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-71600</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-56600</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-70700</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-56700</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-45800</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-30600</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-18100</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-54000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-21500</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-66700</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-2000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-100</v>
       </c>
-      <c r="V26" s="3">
-        <v>0</v>
-      </c>
-      <c r="W26" s="3" t="s">
-        <v>3</v>
+      <c r="W26" s="3">
+        <v>0</v>
       </c>
       <c r="X26" s="3" t="s">
         <v>3</v>
@@ -2083,70 +2134,73 @@
       <c r="AA26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-481500</v>
+      </c>
+      <c r="E27" s="3">
         <v>-384100</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-51800</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-46700</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-41200</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>14900</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-131600</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-71600</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-56600</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-70700</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-56700</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-45800</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-30600</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-18100</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-54000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-21500</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-66700</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-2000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-100</v>
       </c>
-      <c r="V27" s="3">
-        <v>0</v>
-      </c>
-      <c r="W27" s="3" t="s">
-        <v>3</v>
+      <c r="W27" s="3">
+        <v>0</v>
       </c>
       <c r="X27" s="3" t="s">
         <v>3</v>
@@ -2160,8 +2214,11 @@
       <c r="AA27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2237,8 +2294,11 @@
       <c r="AA28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2314,8 +2374,11 @@
       <c r="AA29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2391,8 +2454,11 @@
       <c r="AA30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2468,62 +2534,65 @@
       <c r="AA31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-248300</v>
+      </c>
+      <c r="E32" s="3">
         <v>-281100</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-58900</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>3600</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>9600</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>62200</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-75500</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-13100</v>
-      </c>
-      <c r="K32" s="3">
-        <v>400</v>
       </c>
       <c r="L32" s="3">
         <v>400</v>
       </c>
       <c r="M32" s="3">
+        <v>400</v>
+      </c>
+      <c r="N32" s="3">
         <v>-3600</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-8400</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-8300</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-10700</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>4700</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-200</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>5900</v>
       </c>
-      <c r="T32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U32" s="3" t="s">
         <v>3</v>
       </c>
@@ -2545,70 +2614,73 @@
       <c r="AA32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-268100</v>
+      </c>
+      <c r="E33" s="3">
         <v>-342900</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-28200</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-46700</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-41200</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>14900</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-131600</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-71600</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-56600</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-70700</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-56700</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-45800</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-30600</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-18100</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-54000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-21500</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-66700</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-2000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-100</v>
       </c>
-      <c r="V33" s="3">
-        <v>0</v>
-      </c>
-      <c r="W33" s="3" t="s">
-        <v>3</v>
+      <c r="W33" s="3">
+        <v>0</v>
       </c>
       <c r="X33" s="3" t="s">
         <v>3</v>
@@ -2622,8 +2694,11 @@
       <c r="AA33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2699,70 +2774,73 @@
       <c r="AA34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-268100</v>
+      </c>
+      <c r="E35" s="3">
         <v>-342900</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-28200</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-46700</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-41200</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>14900</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-131600</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-71600</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-56600</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-70700</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-56700</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-45800</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-30600</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-18100</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-54000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-21500</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-66700</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-2000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-100</v>
       </c>
-      <c r="V35" s="3">
-        <v>0</v>
-      </c>
-      <c r="W35" s="3" t="s">
-        <v>3</v>
+      <c r="W35" s="3">
+        <v>0</v>
       </c>
       <c r="X35" s="3" t="s">
         <v>3</v>
@@ -2776,76 +2854,79 @@
       <c r="AA35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:28" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
         <v>45565</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45473</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45382</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45291</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45199</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45107</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45016</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44926</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44834</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44742</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44651</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44561</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44469</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44377</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44286</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44196</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44104</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44012</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43921</v>
       </c>
-      <c r="W38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="X38" s="2" t="s">
         <v>3</v>
       </c>
@@ -2858,8 +2939,11 @@
       <c r="AA38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2887,8 +2971,9 @@
       <c r="Y39" s="3"/>
       <c r="Z39" s="3"/>
       <c r="AA39" s="3"/>
-    </row>
-    <row r="40" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB39" s="3"/>
+    </row>
+    <row r="40" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2916,70 +3001,71 @@
       <c r="Y40" s="3"/>
       <c r="Z40" s="3"/>
       <c r="AA40" s="3"/>
-    </row>
-    <row r="41" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB40" s="3"/>
+    </row>
+    <row r="41" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>74300</v>
+      </c>
+      <c r="E41" s="3">
         <v>23000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>52500</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>31800</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>69500</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>58000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>23200</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>16100</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>17100</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>38400</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>16300</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>55400</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>104800</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>144200</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>74700</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>100700</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>121900</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>300</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>500</v>
       </c>
-      <c r="V41" s="3">
-        <v>0</v>
-      </c>
-      <c r="W41" s="3" t="s">
-        <v>3</v>
+      <c r="W41" s="3">
+        <v>0</v>
       </c>
       <c r="X41" s="3" t="s">
         <v>3</v>
@@ -2993,8 +3079,11 @@
       <c r="AA41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3070,70 +3159,73 @@
       <c r="AA42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>40100</v>
+      </c>
+      <c r="E43" s="3">
         <v>82600</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>100800</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>27300</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>20500</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>4300</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>3900</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>7800</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>3600</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>6400</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>3600</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>3700</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>2000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>2400</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>400</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>300</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>100</v>
       </c>
-      <c r="T43" s="3">
-        <v>0</v>
-      </c>
       <c r="U43" s="3">
         <v>0</v>
       </c>
       <c r="V43" s="3">
         <v>0</v>
       </c>
-      <c r="W43" s="3" t="s">
-        <v>3</v>
+      <c r="W43" s="3">
+        <v>0</v>
       </c>
       <c r="X43" s="3" t="s">
         <v>3</v>
@@ -3147,62 +3239,65 @@
       <c r="AA43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>32800</v>
+      </c>
+      <c r="E44" s="3">
         <v>25900</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>17800</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>14400</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>17100</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>20600</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>16600</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>14100</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>23300</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>23200</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>12900</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>10300</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>13000</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>5000</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>4400</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>100</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>200</v>
       </c>
-      <c r="T44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U44" s="3" t="s">
         <v>3</v>
       </c>
@@ -3218,74 +3313,77 @@
       <c r="Y44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Z44" s="3">
-        <v>0</v>
+      <c r="Z44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AA44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>17600</v>
+      </c>
+      <c r="E45" s="3">
         <v>13900</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>8600</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>9600</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>10700</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>21400</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>15500</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>7400</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>11300</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>13600</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>27600</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>26800</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>22700</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>17400</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>12200</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>6200</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>5200</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>200</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>300</v>
       </c>
-      <c r="V45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W45" s="3" t="s">
         <v>3</v>
       </c>
@@ -3301,70 +3399,73 @@
       <c r="AA45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>179900</v>
+      </c>
+      <c r="E46" s="3">
         <v>149200</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>183500</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>87000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>122300</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>108500</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>64000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>50000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>55100</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>81600</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>60500</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>96200</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>142600</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>169100</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>91700</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>107400</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>127400</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>600</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>800</v>
       </c>
-      <c r="V46" s="3">
-        <v>0</v>
-      </c>
-      <c r="W46" s="3" t="s">
-        <v>3</v>
+      <c r="W46" s="3">
+        <v>0</v>
       </c>
       <c r="X46" s="3" t="s">
         <v>3</v>
@@ -3378,8 +3479,11 @@
       <c r="AA46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3404,36 +3508,36 @@
       <c r="J47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K47" s="3">
+      <c r="K47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L47" s="3">
         <v>800</v>
-      </c>
-      <c r="L47" s="3">
-        <v>3700</v>
       </c>
       <c r="M47" s="3">
         <v>3700</v>
       </c>
       <c r="N47" s="3">
-        <v>3500</v>
+        <v>3700</v>
       </c>
       <c r="O47" s="3">
         <v>3500</v>
       </c>
       <c r="P47" s="3">
+        <v>3500</v>
+      </c>
+      <c r="Q47" s="3">
         <v>4700</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>4100</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>11100</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>3700</v>
       </c>
-      <c r="T47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U47" s="3" t="s">
         <v>3</v>
       </c>
@@ -3449,68 +3553,71 @@
       <c r="Y47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Z47" s="3">
-        <v>0</v>
+      <c r="Z47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AA47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>48600</v>
+      </c>
+      <c r="E48" s="3">
         <v>54600</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>54000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>46500</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>41900</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>24300</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>23900</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>28700</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>31500</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>34400</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>25800</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>19500</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>16400</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>10300</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>8400</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>8000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>5700</v>
       </c>
-      <c r="T48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U48" s="3" t="s">
         <v>3</v>
       </c>
@@ -3526,14 +3633,17 @@
       <c r="Y48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Z48" s="3">
-        <v>0</v>
+      <c r="Z48" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AA48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -3553,13 +3663,13 @@
         <v>4600</v>
       </c>
       <c r="I49" s="3">
-        <v>4700</v>
+        <v>4600</v>
       </c>
       <c r="J49" s="3">
         <v>4700</v>
       </c>
       <c r="K49" s="3">
-        <v>4600</v>
+        <v>4700</v>
       </c>
       <c r="L49" s="3">
         <v>4600</v>
@@ -3580,13 +3690,13 @@
         <v>4600</v>
       </c>
       <c r="R49" s="3">
-        <v>300</v>
+        <v>4600</v>
       </c>
       <c r="S49" s="3">
         <v>300</v>
       </c>
-      <c r="T49" s="3" t="s">
-        <v>3</v>
+      <c r="T49" s="3">
+        <v>300</v>
       </c>
       <c r="U49" s="3" t="s">
         <v>3</v>
@@ -3603,14 +3713,17 @@
       <c r="Y49" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Z49" s="3">
-        <v>0</v>
+      <c r="Z49" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AA49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3686,8 +3799,11 @@
       <c r="AA50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3763,71 +3879,74 @@
       <c r="AA51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>26300</v>
+      </c>
+      <c r="E52" s="3">
         <v>7300</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>4900</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>17600</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
+        <v>15700</v>
+      </c>
+      <c r="I52" s="3">
+        <v>15900</v>
+      </c>
+      <c r="J52" s="3">
+        <v>15600</v>
+      </c>
+      <c r="K52" s="3">
+        <v>15500</v>
+      </c>
+      <c r="L52" s="3">
+        <v>14800</v>
+      </c>
+      <c r="M52" s="3">
         <v>14200</v>
       </c>
-      <c r="H52" s="3">
-        <v>15900</v>
-      </c>
-      <c r="I52" s="3">
-        <v>15600</v>
-      </c>
-      <c r="J52" s="3">
-        <v>15500</v>
-      </c>
-      <c r="K52" s="3">
-        <v>14800</v>
-      </c>
-      <c r="L52" s="3">
-        <v>14200</v>
-      </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>3200</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>3100</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>2100</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>1400</v>
-      </c>
-      <c r="Q52" s="3">
-        <v>1000</v>
       </c>
       <c r="R52" s="3">
         <v>1000</v>
       </c>
       <c r="S52" s="3">
+        <v>1000</v>
+      </c>
+      <c r="T52" s="3">
         <v>1200</v>
-      </c>
-      <c r="T52" s="3">
-        <v>176800</v>
       </c>
       <c r="U52" s="3">
         <v>176800</v>
       </c>
       <c r="V52" s="3">
+        <v>176800</v>
+      </c>
+      <c r="W52" s="3">
         <v>100</v>
       </c>
-      <c r="W52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X52" s="3" t="s">
         <v>3</v>
       </c>
@@ -3840,8 +3959,11 @@
       <c r="AA52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3917,71 +4039,74 @@
       <c r="AA53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>260300</v>
+      </c>
+      <c r="E54" s="3">
         <v>216800</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>248800</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>155700</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>186500</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>154100</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>109000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>99700</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>106800</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>138500</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>97700</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>126900</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>169200</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>190100</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>109900</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>127800</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>138300</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>177300</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>177500</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>100</v>
       </c>
-      <c r="W54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X54" s="3" t="s">
         <v>3</v>
       </c>
@@ -3994,8 +4119,11 @@
       <c r="AA54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4023,8 +4151,9 @@
       <c r="Y55" s="3"/>
       <c r="Z55" s="3"/>
       <c r="AA55" s="3"/>
-    </row>
-    <row r="56" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB55" s="3"/>
+    </row>
+    <row r="56" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4052,70 +4181,71 @@
       <c r="Y56" s="3"/>
       <c r="Z56" s="3"/>
       <c r="AA56" s="3"/>
-    </row>
-    <row r="57" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB56" s="3"/>
+    </row>
+    <row r="57" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>16700</v>
+      </c>
+      <c r="E57" s="3">
         <v>24300</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>24100</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>18300</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>20500</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>13800</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>15400</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>32500</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>34700</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>35500</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>29100</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>11700</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>13700</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>13200</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>15200</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>20200</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>11400</v>
       </c>
-      <c r="T57" s="3">
-        <v>0</v>
-      </c>
       <c r="U57" s="3">
         <v>0</v>
       </c>
       <c r="V57" s="3">
         <v>0</v>
       </c>
-      <c r="W57" s="3" t="s">
-        <v>3</v>
+      <c r="W57" s="3">
+        <v>0</v>
       </c>
       <c r="X57" s="3" t="s">
         <v>3</v>
@@ -4129,71 +4259,74 @@
       <c r="AA57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>3900</v>
+      </c>
+      <c r="E58" s="3">
         <v>4300</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>5500</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>5100</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>4900</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>4600</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>4400</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>12400</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>5600</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>2900</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>14000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>6700</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>6600</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>6500</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>6100</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>1200</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>1100</v>
       </c>
-      <c r="T58" s="3">
-        <v>0</v>
-      </c>
       <c r="U58" s="3">
         <v>0</v>
       </c>
       <c r="V58" s="3">
+        <v>0</v>
+      </c>
+      <c r="W58" s="3">
         <v>100</v>
       </c>
-      <c r="W58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X58" s="3" t="s">
         <v>3</v>
       </c>
@@ -4206,67 +4339,70 @@
       <c r="AA58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>32100</v>
+      </c>
+      <c r="E59" s="3">
         <v>17100</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>13500</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>11500</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>12600</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>13000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>9000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>6300</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>20300</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>17500</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>16600</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>15500</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>9600</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>1200</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>3400</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>800</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>1700</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>1800</v>
       </c>
-      <c r="U59" s="3">
-        <v>0</v>
-      </c>
-      <c r="V59" s="3" t="s">
-        <v>3</v>
+      <c r="V59" s="3">
+        <v>0</v>
       </c>
       <c r="W59" s="3" t="s">
         <v>3</v>
@@ -4283,70 +4419,73 @@
       <c r="AA59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>65000</v>
+      </c>
+      <c r="E60" s="3">
         <v>75100</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>68500</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>64900</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>60900</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>46800</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>43000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>65700</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>60600</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>55800</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>59600</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>33800</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>29900</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>20900</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>24600</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>22200</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>14100</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>1900</v>
-      </c>
-      <c r="U60" s="3">
-        <v>100</v>
       </c>
       <c r="V60" s="3">
         <v>100</v>
       </c>
-      <c r="W60" s="3" t="s">
-        <v>3</v>
+      <c r="W60" s="3">
+        <v>100</v>
       </c>
       <c r="X60" s="3" t="s">
         <v>3</v>
@@ -4360,62 +4499,65 @@
       <c r="AA60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>316600</v>
+      </c>
+      <c r="E61" s="3">
         <v>187000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>152800</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>206700</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>204000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>207500</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>233300</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>202400</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>170400</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>160800</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>90300</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>95300</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>102700</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>106800</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>13500</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>100</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>300</v>
       </c>
-      <c r="T61" s="3">
-        <v>0</v>
-      </c>
       <c r="U61" s="3">
         <v>0</v>
       </c>
@@ -4437,62 +4579,65 @@
       <c r="AA61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>456200</v>
+      </c>
+      <c r="E62" s="3">
         <v>369100</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>173800</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>27500</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>28900</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>27100</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>61200</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>6300</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>8500</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>10100</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>5700</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>8000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>4200</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>3900</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>3100</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>3700</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>800</v>
       </c>
-      <c r="T62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U62" s="3" t="s">
         <v>3</v>
       </c>
@@ -4508,14 +4653,17 @@
       <c r="Y62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Z62" s="3">
-        <v>0</v>
+      <c r="Z62" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AA62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4591,8 +4739,11 @@
       <c r="AA63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4668,8 +4819,11 @@
       <c r="AA64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4745,70 +4899,73 @@
       <c r="AA65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>842100</v>
+      </c>
+      <c r="E66" s="3">
         <v>634500</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>399500</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>303400</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>297300</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>282400</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>338500</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>275300</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>239500</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>226800</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>155600</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>137100</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>136700</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>131700</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>41300</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>26000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>15200</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>1900</v>
-      </c>
-      <c r="U66" s="3">
-        <v>100</v>
       </c>
       <c r="V66" s="3">
         <v>100</v>
       </c>
-      <c r="W66" s="3" t="s">
-        <v>3</v>
+      <c r="W66" s="3">
+        <v>100</v>
       </c>
       <c r="X66" s="3" t="s">
         <v>3</v>
@@ -4822,8 +4979,11 @@
       <c r="AA66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4851,8 +5011,9 @@
       <c r="Y67" s="3"/>
       <c r="Z67" s="3"/>
       <c r="AA67" s="3"/>
-    </row>
-    <row r="68" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB67" s="3"/>
+    </row>
+    <row r="68" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4928,8 +5089,11 @@
       <c r="AA68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5005,20 +5169,23 @@
       <c r="AA69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
       <c r="D70" s="3">
+        <v>488700</v>
+      </c>
+      <c r="E70" s="3">
         <v>156100</v>
       </c>
-      <c r="E70" s="3">
+      <c r="F70" s="3">
         <v>40100</v>
       </c>
-      <c r="F70" s="3">
-        <v>0</v>
-      </c>
       <c r="G70" s="3">
         <v>0</v>
       </c>
@@ -5082,8 +5249,11 @@
       <c r="AA70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5159,70 +5329,73 @@
       <c r="AA71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-1561700</v>
+      </c>
+      <c r="E72" s="3">
         <v>-1293600</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-950700</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-922600</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-875800</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-834600</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-849600</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-717900</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-646300</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-589700</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-519000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-462300</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-416500</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-385900</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-367800</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-313800</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-290800</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-2000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-100</v>
       </c>
-      <c r="V72" s="3">
-        <v>0</v>
-      </c>
-      <c r="W72" s="3" t="s">
-        <v>3</v>
+      <c r="W72" s="3">
+        <v>0</v>
       </c>
       <c r="X72" s="3" t="s">
         <v>3</v>
@@ -5236,8 +5409,11 @@
       <c r="AA72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5313,8 +5489,11 @@
       <c r="AA73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5390,8 +5569,11 @@
       <c r="AA74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5467,70 +5649,73 @@
       <c r="AA75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>-1070500</v>
+      </c>
+      <c r="E76" s="3">
         <v>-573800</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>-190800</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>-147700</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>-110800</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>-128300</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>-229500</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>-175600</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>-132700</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>-88300</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>-57800</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>-10200</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>32400</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>58400</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>68600</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>101800</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>123100</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>175500</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>177400</v>
       </c>
-      <c r="V76" s="3">
-        <v>0</v>
-      </c>
-      <c r="W76" s="3" t="s">
-        <v>3</v>
+      <c r="W76" s="3">
+        <v>0</v>
       </c>
       <c r="X76" s="3" t="s">
         <v>3</v>
@@ -5544,8 +5729,11 @@
       <c r="AA76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5621,76 +5809,79 @@
       <c r="AA77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:28" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:28" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
         <v>45565</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45473</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45382</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45291</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45199</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45107</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45016</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44926</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44834</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44742</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44651</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44561</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44469</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44377</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44286</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44196</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44104</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44012</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43921</v>
       </c>
-      <c r="W80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="X80" s="2" t="s">
         <v>3</v>
       </c>
@@ -5703,70 +5894,73 @@
       <c r="AA80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-268100</v>
+      </c>
+      <c r="E81" s="3">
         <v>-342900</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-28200</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-46700</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-41200</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>14900</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-131600</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-71600</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-56600</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-70700</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-56700</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-45800</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-30600</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-18100</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-54000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-21500</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-66700</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-2000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-100</v>
       </c>
-      <c r="V81" s="3">
-        <v>0</v>
-      </c>
-      <c r="W81" s="3" t="s">
-        <v>3</v>
+      <c r="W81" s="3">
+        <v>0</v>
       </c>
       <c r="X81" s="3" t="s">
         <v>3</v>
@@ -5780,8 +5974,11 @@
       <c r="AA81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5809,59 +6006,60 @@
       <c r="Y82" s="3"/>
       <c r="Z82" s="3"/>
       <c r="AA82" s="3"/>
-    </row>
-    <row r="83" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB82" s="3"/>
+    </row>
+    <row r="83" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>2700</v>
+      </c>
+      <c r="E83" s="3">
         <v>2400</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>2700</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>2900</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>3200</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>1800</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>1500</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>1200</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>3000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>1600</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>1300</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>1000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>800</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>700</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>600</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>500</v>
       </c>
-      <c r="S83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T83" s="3" t="s">
         <v>3</v>
       </c>
@@ -5877,8 +6075,8 @@
       <c r="X83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Y83" s="3">
-        <v>0</v>
+      <c r="Y83" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Z83" s="3">
         <v>0</v>
@@ -5886,8 +6084,11 @@
       <c r="AA83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5963,8 +6164,11 @@
       <c r="AA84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6040,8 +6244,11 @@
       <c r="AA85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6117,8 +6324,11 @@
       <c r="AA86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6194,8 +6404,11 @@
       <c r="AA87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6271,70 +6484,73 @@
       <c r="AA88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-42700</v>
+      </c>
+      <c r="E89" s="3">
         <v>-44400</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-26300</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-40500</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-37400</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-32000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-45100</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-30500</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-37700</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-72100</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-44300</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-42700</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-35500</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-31700</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-39200</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-9700</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-26100</v>
-      </c>
-      <c r="T89" s="3">
-        <v>-200</v>
       </c>
       <c r="U89" s="3">
         <v>-200</v>
       </c>
       <c r="V89" s="3">
-        <v>0</v>
-      </c>
-      <c r="W89" s="3" t="s">
-        <v>3</v>
+        <v>-200</v>
+      </c>
+      <c r="W89" s="3">
+        <v>0</v>
       </c>
       <c r="X89" s="3" t="s">
         <v>3</v>
@@ -6348,8 +6564,11 @@
       <c r="AA89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6377,59 +6596,60 @@
       <c r="Y90" s="3"/>
       <c r="Z90" s="3"/>
       <c r="AA90" s="3"/>
-    </row>
-    <row r="91" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB90" s="3"/>
+    </row>
+    <row r="91" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-13100</v>
+      </c>
+      <c r="E91" s="3">
         <v>-9800</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-6200</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-4000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-8100</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-11100</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-7200</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-2900</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-1300</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-7300</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-6400</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-5100</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-4200</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-3800</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-3100</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-4500</v>
       </c>
-      <c r="S91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T91" s="3" t="s">
         <v>3</v>
       </c>
@@ -6445,8 +6665,8 @@
       <c r="X91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Y91" s="3">
-        <v>0</v>
+      <c r="Y91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Z91" s="3">
         <v>0</v>
@@ -6454,8 +6674,11 @@
       <c r="AA91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6531,8 +6754,11 @@
       <c r="AA92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6608,64 +6834,67 @@
       <c r="AA93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-13100</v>
+      </c>
+      <c r="E94" s="3">
         <v>-9800</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-6300</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-4000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-8300</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-11100</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-7200</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-2900</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>1900</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-7300</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-6600</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-5100</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-3100</v>
-      </c>
-      <c r="P94" s="3">
-        <v>-4400</v>
       </c>
       <c r="Q94" s="3">
         <v>-4400</v>
       </c>
       <c r="R94" s="3">
+        <v>-4400</v>
+      </c>
+      <c r="S94" s="3">
         <v>-11400</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>170100</v>
       </c>
-      <c r="T94" s="3">
-        <v>0</v>
-      </c>
-      <c r="U94" s="3" t="s">
-        <v>3</v>
+      <c r="U94" s="3">
+        <v>0</v>
       </c>
       <c r="V94" s="3" t="s">
         <v>3</v>
@@ -6679,14 +6908,17 @@
       <c r="Y94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Z94" s="3">
-        <v>0</v>
+      <c r="Z94" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AA94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6714,8 +6946,9 @@
       <c r="Y95" s="3"/>
       <c r="Z95" s="3"/>
       <c r="AA95" s="3"/>
-    </row>
-    <row r="96" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB95" s="3"/>
+    </row>
+    <row r="96" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -6740,8 +6973,8 @@
       <c r="J96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K96" s="3">
-        <v>0</v>
+      <c r="K96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L96" s="3">
         <v>0</v>
@@ -6791,8 +7024,11 @@
       <c r="AA96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6868,8 +7104,11 @@
       <c r="AA97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6945,8 +7184,11 @@
       <c r="AA98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7022,71 +7264,74 @@
       <c r="AA99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>128500</v>
+      </c>
+      <c r="E100" s="3">
         <v>27300</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>43900</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>6100</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>57300</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>78000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>60200</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>32500</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>16000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>112900</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>11800</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-1200</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-400</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>106200</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>17600</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-100</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-23300</v>
       </c>
-      <c r="T100" s="3">
-        <v>0</v>
-      </c>
       <c r="U100" s="3">
+        <v>0</v>
+      </c>
+      <c r="V100" s="3">
         <v>177500</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>100</v>
       </c>
-      <c r="W100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X100" s="3" t="s">
         <v>3</v>
       </c>
@@ -7099,8 +7344,11 @@
       <c r="AA100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -7122,17 +7370,17 @@
       <c r="I101" s="3">
         <v>0</v>
       </c>
-      <c r="J101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K101" s="3">
-        <v>0</v>
+      <c r="J101" s="3">
+        <v>0</v>
+      </c>
+      <c r="K101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L101" s="3">
         <v>0</v>
       </c>
-      <c r="M101" s="3" t="s">
-        <v>3</v>
+      <c r="M101" s="3">
+        <v>0</v>
       </c>
       <c r="N101" s="3" t="s">
         <v>3</v>
@@ -7149,8 +7397,8 @@
       <c r="R101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="S101" s="3">
-        <v>0</v>
+      <c r="S101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="T101" s="3">
         <v>0</v>
@@ -7176,70 +7424,73 @@
       <c r="AA101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:28" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>72700</v>
+      </c>
+      <c r="E102" s="3">
         <v>-26900</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>11300</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-38400</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>11600</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>34900</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>7900</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-900</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-19800</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>33500</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-39100</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-49100</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-39000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>70000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-26000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-21100</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>120700</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-200</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>500</v>
       </c>
-      <c r="V102" s="3">
-        <v>0</v>
-      </c>
-      <c r="W102" s="3" t="s">
-        <v>3</v>
+      <c r="W102" s="3">
+        <v>0</v>
       </c>
       <c r="X102" s="3" t="s">
         <v>3</v>
@@ -7251,6 +7502,9 @@
         <v>3</v>
       </c>
       <c r="AA102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/EOSE_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/EOSE_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="378" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="380" uniqueCount="92">
   <si>
     <t>EOSE</t>
   </si>
@@ -656,108 +656,109 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AB102"/>
+  <dimension ref="A5:AC102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="28" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="29" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:29" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:28" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45565</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45473</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45382</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45291</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45199</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45107</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45016</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44926</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44834</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44742</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44651</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44561</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44469</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44377</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44286</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44196</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44104</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44012</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43921</v>
       </c>
-      <c r="X7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="Y7" s="2" t="s">
         <v>3</v>
       </c>
@@ -770,64 +771,67 @@
       <c r="AB7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>10500</v>
+      </c>
+      <c r="E8" s="3">
         <v>7300</v>
-      </c>
-      <c r="E8" s="3">
-        <v>900</v>
       </c>
       <c r="F8" s="3">
         <v>900</v>
       </c>
       <c r="G8" s="3">
-        <v>6600</v>
+        <v>900</v>
       </c>
       <c r="H8" s="3">
         <v>6600</v>
       </c>
       <c r="I8" s="3">
+        <v>6600</v>
+      </c>
+      <c r="J8" s="3">
         <v>700</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>200</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>8800</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>2700</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>6100</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>5900</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>3300</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>3100</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>700</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>600</v>
-      </c>
-      <c r="S8" s="3">
-        <v>200</v>
       </c>
       <c r="T8" s="3">
         <v>200</v>
       </c>
-      <c r="U8" s="3" t="s">
-        <v>3</v>
+      <c r="U8" s="3">
+        <v>200</v>
       </c>
       <c r="V8" s="3" t="s">
         <v>3</v>
@@ -844,71 +848,74 @@
       <c r="Z8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AA8" s="3">
-        <v>0</v>
+      <c r="AA8" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AB8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>35000</v>
+      </c>
+      <c r="E9" s="3">
         <v>30800</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>25800</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>14100</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>28200</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>30400</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>21300</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>11200</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>26900</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>30800</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>50000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>36900</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>35600</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>21100</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>12900</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>12400</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>100</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>5500</v>
       </c>
-      <c r="U9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V9" s="3" t="s">
         <v>3</v>
       </c>
@@ -930,65 +937,68 @@
       <c r="AB9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>-24500</v>
+      </c>
+      <c r="E10" s="3">
         <v>-23500</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>-24900</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>-13200</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>-21600</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>-23700</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>-20600</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>-11000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>-18100</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>-28100</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>-43900</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>-31000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>-32300</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>-18000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>-12200</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>-11800</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>100</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>-5300</v>
       </c>
-      <c r="U10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V10" s="3" t="s">
         <v>3</v>
       </c>
@@ -1010,8 +1020,11 @@
       <c r="AB10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1040,65 +1053,66 @@
       <c r="Z11" s="3"/>
       <c r="AA11" s="3"/>
       <c r="AB11" s="3"/>
-    </row>
-    <row r="12" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC11" s="3"/>
+    </row>
+    <row r="12" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>6800</v>
+      </c>
+      <c r="E12" s="3">
         <v>5900</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>7400</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>4300</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>5200</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>5000</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>3200</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>5000</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>5400</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>3600</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>4500</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>5500</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>5000</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>5400</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>5100</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>3600</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>5000</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>14000</v>
       </c>
-      <c r="U12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V12" s="3" t="s">
         <v>3</v>
       </c>
@@ -1120,8 +1134,11 @@
       <c r="AB12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1200,64 +1217,67 @@
       <c r="AB13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>6500</v>
+      </c>
+      <c r="E14" s="3">
         <v>-31500</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>6200</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>-68000</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>100</v>
       </c>
-      <c r="H14" s="3">
-        <v>0</v>
-      </c>
       <c r="I14" s="3">
+        <v>0</v>
+      </c>
+      <c r="J14" s="3">
         <v>1000</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>7300</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>2400</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>4300</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>1400</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>2000</v>
       </c>
-      <c r="O14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P14" s="3">
-        <v>0</v>
+      <c r="P14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q14" s="3">
+        <v>0</v>
+      </c>
+      <c r="R14" s="3">
         <v>-1300</v>
       </c>
-      <c r="R14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="S14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T14" s="3">
-        <v>0</v>
-      </c>
-      <c r="U14" s="3" t="s">
-        <v>3</v>
+      <c r="T14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="U14" s="3">
+        <v>0</v>
       </c>
       <c r="V14" s="3" t="s">
         <v>3</v>
@@ -1265,8 +1285,8 @@
       <c r="W14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="X14" s="3">
-        <v>0</v>
+      <c r="X14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Y14" s="3">
         <v>0</v>
@@ -1280,38 +1300,41 @@
       <c r="AB14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>2700</v>
+      </c>
+      <c r="E15" s="3">
         <v>2600</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>2700</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>1400</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>1200</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>2400</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>2200</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>2500</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>2700</v>
       </c>
-      <c r="L15" s="3">
-        <v>0</v>
-      </c>
       <c r="M15" s="3">
         <v>0</v>
       </c>
@@ -1360,8 +1383,11 @@
       <c r="AB15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:28" x14ac:dyDescent="0.2">
+      <c r="AC15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:29" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1387,73 +1413,74 @@
       <c r="Z16" s="3"/>
       <c r="AA16" s="3"/>
       <c r="AB16" s="3"/>
-    </row>
-    <row r="17" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC16" s="3"/>
+    </row>
+    <row r="17" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>62800</v>
+      </c>
+      <c r="E17" s="3">
         <v>53300</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>51000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>29700</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>47700</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>48800</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>37600</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>29400</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>46300</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>51300</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>70600</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>63300</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>55000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>40700</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>25700</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>49800</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>21800</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>37200</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>2000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>100</v>
       </c>
-      <c r="W17" s="3">
-        <v>0</v>
-      </c>
-      <c r="X17" s="3" t="s">
-        <v>3</v>
+      <c r="X17" s="3">
+        <v>0</v>
       </c>
       <c r="Y17" s="3" t="s">
         <v>3</v>
@@ -1467,65 +1494,68 @@
       <c r="AB17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-52400</v>
+      </c>
+      <c r="E18" s="3">
         <v>-46100</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-50100</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-28800</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-41100</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-42200</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-36900</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-29200</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-37500</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-48600</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-64500</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-57400</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-51700</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-37600</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-25000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-49200</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-21600</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-37000</v>
       </c>
-      <c r="U18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1547,8 +1577,11 @@
       <c r="AB18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1577,65 +1610,66 @@
       <c r="Z19" s="3"/>
       <c r="AA19" s="3"/>
       <c r="AB19" s="3"/>
-    </row>
-    <row r="20" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC19" s="3"/>
+    </row>
+    <row r="20" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-80000</v>
+      </c>
+      <c r="E20" s="3">
         <v>248300</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>281100</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>58900</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-3600</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-9600</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-62200</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>75500</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>13100</v>
-      </c>
-      <c r="L20" s="3">
-        <v>-400</v>
       </c>
       <c r="M20" s="3">
         <v>-400</v>
       </c>
       <c r="N20" s="3">
+        <v>-400</v>
+      </c>
+      <c r="O20" s="3">
         <v>3600</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>8400</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>8300</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>10700</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-4700</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>200</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-5900</v>
       </c>
-      <c r="U20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V20" s="3" t="s">
         <v>3</v>
       </c>
@@ -1657,62 +1691,65 @@
       <c r="AB20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>30200</v>
+      </c>
+      <c r="E21" s="3">
         <v>-291700</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-328600</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-86300</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-36300</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-30200</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>27500</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-102200</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-47900</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-46000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-63300</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-52500</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-42300</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-28500</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-13700</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-53300</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-21000</v>
       </c>
-      <c r="T21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1737,65 +1774,68 @@
       <c r="AB21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>5900</v>
+      </c>
+      <c r="E22" s="3">
         <v>5200</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>5400</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>8400</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>9100</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>8600</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>9400</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>19600</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>18600</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>7600</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>5700</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>2900</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>2500</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>1300</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>3700</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>200</v>
       </c>
-      <c r="S22" s="3">
-        <v>0</v>
-      </c>
       <c r="T22" s="3">
+        <v>0</v>
+      </c>
+      <c r="U22" s="3">
         <v>23800</v>
       </c>
-      <c r="U22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V22" s="3" t="s">
         <v>3</v>
       </c>
@@ -1811,79 +1851,82 @@
       <c r="Z22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AA22" s="3">
-        <v>0</v>
+      <c r="AA22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AB22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>15100</v>
+      </c>
+      <c r="E23" s="3">
         <v>-268100</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-342900</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-28200</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-46700</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-41200</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>14900</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-131600</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-71600</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-56600</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-70600</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-56700</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-45800</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-30600</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-18100</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-54000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-21500</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-66700</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-2000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-100</v>
       </c>
-      <c r="W23" s="3">
-        <v>0</v>
-      </c>
-      <c r="X23" s="3" t="s">
-        <v>3</v>
+      <c r="X23" s="3">
+        <v>0</v>
       </c>
       <c r="Y23" s="3" t="s">
         <v>3</v>
@@ -1897,8 +1940,11 @@
       <c r="AB23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1930,16 +1976,16 @@
         <v>0</v>
       </c>
       <c r="M24" s="3">
+        <v>0</v>
+      </c>
+      <c r="N24" s="3">
         <v>100</v>
       </c>
-      <c r="N24" s="3">
-        <v>0</v>
-      </c>
       <c r="O24" s="3">
         <v>0</v>
       </c>
-      <c r="P24" s="3" t="s">
-        <v>3</v>
+      <c r="P24" s="3">
+        <v>0</v>
       </c>
       <c r="Q24" s="3" t="s">
         <v>3</v>
@@ -1956,8 +2002,8 @@
       <c r="U24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="V24" s="3">
-        <v>0</v>
+      <c r="V24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="W24" s="3">
         <v>0</v>
@@ -1977,8 +2023,11 @@
       <c r="AB24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2057,73 +2106,76 @@
       <c r="AB25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>15100</v>
+      </c>
+      <c r="E26" s="3">
         <v>-268100</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-342900</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-28200</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-46700</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-41200</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>14900</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-131600</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-71600</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-56600</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-70700</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-56700</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-45800</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-30600</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-18100</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-54000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-21500</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-66700</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-2000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-100</v>
       </c>
-      <c r="W26" s="3">
-        <v>0</v>
-      </c>
-      <c r="X26" s="3" t="s">
-        <v>3</v>
+      <c r="X26" s="3">
+        <v>0</v>
       </c>
       <c r="Y26" s="3" t="s">
         <v>3</v>
@@ -2137,73 +2189,76 @@
       <c r="AB26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>95100</v>
+      </c>
+      <c r="E27" s="3">
         <v>-481500</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-384100</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-51800</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-46700</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-41200</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>14900</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-131600</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-71600</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-56600</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-70700</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-56700</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-45800</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-30600</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-18100</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-54000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-21500</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-66700</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-2000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-100</v>
       </c>
-      <c r="W27" s="3">
-        <v>0</v>
-      </c>
-      <c r="X27" s="3" t="s">
-        <v>3</v>
+      <c r="X27" s="3">
+        <v>0</v>
       </c>
       <c r="Y27" s="3" t="s">
         <v>3</v>
@@ -2217,8 +2272,11 @@
       <c r="AB27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2297,8 +2355,11 @@
       <c r="AB28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2377,8 +2438,11 @@
       <c r="AB29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2457,8 +2521,11 @@
       <c r="AB30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2537,65 +2604,68 @@
       <c r="AB31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>80000</v>
+      </c>
+      <c r="E32" s="3">
         <v>-248300</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-281100</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-58900</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>3600</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>9600</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>62200</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-75500</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-13100</v>
-      </c>
-      <c r="L32" s="3">
-        <v>400</v>
       </c>
       <c r="M32" s="3">
         <v>400</v>
       </c>
       <c r="N32" s="3">
+        <v>400</v>
+      </c>
+      <c r="O32" s="3">
         <v>-3600</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-8400</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-8300</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-10700</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>4700</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-200</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>5900</v>
       </c>
-      <c r="U32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V32" s="3" t="s">
         <v>3</v>
       </c>
@@ -2617,73 +2687,76 @@
       <c r="AB32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>15100</v>
+      </c>
+      <c r="E33" s="3">
         <v>-268100</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-342900</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-28200</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-46700</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-41200</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>14900</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-131600</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-71600</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-56600</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-70700</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-56700</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-45800</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-30600</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-18100</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-54000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-21500</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-66700</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-2000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-100</v>
       </c>
-      <c r="W33" s="3">
-        <v>0</v>
-      </c>
-      <c r="X33" s="3" t="s">
-        <v>3</v>
+      <c r="X33" s="3">
+        <v>0</v>
       </c>
       <c r="Y33" s="3" t="s">
         <v>3</v>
@@ -2697,8 +2770,11 @@
       <c r="AB33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2777,73 +2853,76 @@
       <c r="AB34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>15100</v>
+      </c>
+      <c r="E35" s="3">
         <v>-268100</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-342900</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-28200</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-46700</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-41200</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>14900</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-131600</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-71600</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-56600</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-70700</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-56700</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-45800</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-30600</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-18100</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-54000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-21500</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-66700</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-2000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-100</v>
       </c>
-      <c r="W35" s="3">
-        <v>0</v>
-      </c>
-      <c r="X35" s="3" t="s">
-        <v>3</v>
+      <c r="X35" s="3">
+        <v>0</v>
       </c>
       <c r="Y35" s="3" t="s">
         <v>3</v>
@@ -2857,79 +2936,82 @@
       <c r="AB35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45565</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45473</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45382</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45291</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45199</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45107</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45016</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44926</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44834</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44742</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44651</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44561</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44469</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44377</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44286</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44196</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44104</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44012</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43921</v>
       </c>
-      <c r="X38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="Y38" s="2" t="s">
         <v>3</v>
       </c>
@@ -2942,8 +3024,11 @@
       <c r="AB38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2972,8 +3057,9 @@
       <c r="Z39" s="3"/>
       <c r="AA39" s="3"/>
       <c r="AB39" s="3"/>
-    </row>
-    <row r="40" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC39" s="3"/>
+    </row>
+    <row r="40" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3002,73 +3088,74 @@
       <c r="Z40" s="3"/>
       <c r="AA40" s="3"/>
       <c r="AB40" s="3"/>
-    </row>
-    <row r="41" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC40" s="3"/>
+    </row>
+    <row r="41" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>82600</v>
+      </c>
+      <c r="E41" s="3">
         <v>74300</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>23000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>52500</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>31800</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>69500</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>58000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>23200</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>16100</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>17100</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>38400</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>16300</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>55400</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>104800</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>144200</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>74700</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>100700</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>121900</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>300</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>500</v>
       </c>
-      <c r="W41" s="3">
-        <v>0</v>
-      </c>
-      <c r="X41" s="3" t="s">
-        <v>3</v>
+      <c r="X41" s="3">
+        <v>0</v>
       </c>
       <c r="Y41" s="3" t="s">
         <v>3</v>
@@ -3082,8 +3169,11 @@
       <c r="AB41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3162,73 +3252,76 @@
       <c r="AB42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>24300</v>
+      </c>
+      <c r="E43" s="3">
         <v>40100</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>82600</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>100800</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>27300</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>20500</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>4300</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>3900</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>7800</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>3600</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>6400</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>3600</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>3700</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>2000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>2400</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>400</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>300</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>100</v>
       </c>
-      <c r="U43" s="3">
-        <v>0</v>
-      </c>
       <c r="V43" s="3">
         <v>0</v>
       </c>
       <c r="W43" s="3">
         <v>0</v>
       </c>
-      <c r="X43" s="3" t="s">
-        <v>3</v>
+      <c r="X43" s="3">
+        <v>0</v>
       </c>
       <c r="Y43" s="3" t="s">
         <v>3</v>
@@ -3242,65 +3335,68 @@
       <c r="AB43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>40300</v>
+      </c>
+      <c r="E44" s="3">
         <v>32800</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>25900</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>17800</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>14400</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>17100</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>20600</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>16600</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>14100</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>23300</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>23200</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>12900</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>10300</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>13000</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>5000</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>4400</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>100</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>200</v>
       </c>
-      <c r="U44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V44" s="3" t="s">
         <v>3</v>
       </c>
@@ -3316,77 +3412,80 @@
       <c r="Z44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AA44" s="3">
-        <v>0</v>
+      <c r="AA44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AB44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>22900</v>
+      </c>
+      <c r="E45" s="3">
         <v>17600</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>13900</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>8600</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>9600</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>10700</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>21400</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>15500</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>7400</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>11300</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>13600</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>27600</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>26800</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>22700</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>17400</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>12200</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>6200</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>5200</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>200</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>300</v>
       </c>
-      <c r="W45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X45" s="3" t="s">
         <v>3</v>
       </c>
@@ -3402,73 +3501,76 @@
       <c r="AB45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>185500</v>
+      </c>
+      <c r="E46" s="3">
         <v>179900</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>149200</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>183500</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>87000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>122300</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>108500</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>64000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>50000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>55100</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>81600</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>60500</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>96200</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>142600</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>169100</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>91700</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>107400</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>127400</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>600</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>800</v>
       </c>
-      <c r="W46" s="3">
-        <v>0</v>
-      </c>
-      <c r="X46" s="3" t="s">
-        <v>3</v>
+      <c r="X46" s="3">
+        <v>0</v>
       </c>
       <c r="Y46" s="3" t="s">
         <v>3</v>
@@ -3482,8 +3584,11 @@
       <c r="AB46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3511,36 +3616,36 @@
       <c r="K47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L47" s="3">
+      <c r="L47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="M47" s="3">
         <v>800</v>
-      </c>
-      <c r="M47" s="3">
-        <v>3700</v>
       </c>
       <c r="N47" s="3">
         <v>3700</v>
       </c>
       <c r="O47" s="3">
-        <v>3500</v>
+        <v>3700</v>
       </c>
       <c r="P47" s="3">
         <v>3500</v>
       </c>
       <c r="Q47" s="3">
+        <v>3500</v>
+      </c>
+      <c r="R47" s="3">
         <v>4700</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>4100</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>11100</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>3700</v>
       </c>
-      <c r="U47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V47" s="3" t="s">
         <v>3</v>
       </c>
@@ -3556,71 +3661,74 @@
       <c r="Z47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AA47" s="3">
-        <v>0</v>
+      <c r="AA47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AB47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>46500</v>
+      </c>
+      <c r="E48" s="3">
         <v>48600</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>54600</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>54000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>46500</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>41900</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>24300</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>23900</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>28700</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>31500</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>34400</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>25800</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>19500</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>16400</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>10300</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>8400</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>8000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>5700</v>
       </c>
-      <c r="U48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V48" s="3" t="s">
         <v>3</v>
       </c>
@@ -3636,19 +3744,22 @@
       <c r="Z48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AA48" s="3">
-        <v>0</v>
+      <c r="AA48" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AB48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>4600</v>
+        <v>4500</v>
       </c>
       <c r="E49" s="3">
         <v>4600</v>
@@ -3666,13 +3777,13 @@
         <v>4600</v>
       </c>
       <c r="J49" s="3">
-        <v>4700</v>
+        <v>4600</v>
       </c>
       <c r="K49" s="3">
         <v>4700</v>
       </c>
       <c r="L49" s="3">
-        <v>4600</v>
+        <v>4700</v>
       </c>
       <c r="M49" s="3">
         <v>4600</v>
@@ -3693,13 +3804,13 @@
         <v>4600</v>
       </c>
       <c r="S49" s="3">
-        <v>300</v>
+        <v>4600</v>
       </c>
       <c r="T49" s="3">
         <v>300</v>
       </c>
-      <c r="U49" s="3" t="s">
-        <v>3</v>
+      <c r="U49" s="3">
+        <v>300</v>
       </c>
       <c r="V49" s="3" t="s">
         <v>3</v>
@@ -3716,14 +3827,17 @@
       <c r="Z49" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AA49" s="3">
-        <v>0</v>
+      <c r="AA49" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AB49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3802,8 +3916,11 @@
       <c r="AB50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3882,74 +3999,77 @@
       <c r="AB51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>26700</v>
+      </c>
+      <c r="E52" s="3">
         <v>26300</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>7300</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>4900</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>17600</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>15700</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>15900</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>15600</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>15500</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>14800</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>14200</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>3200</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>3100</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>2100</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>1400</v>
-      </c>
-      <c r="R52" s="3">
-        <v>1000</v>
       </c>
       <c r="S52" s="3">
         <v>1000</v>
       </c>
       <c r="T52" s="3">
+        <v>1000</v>
+      </c>
+      <c r="U52" s="3">
         <v>1200</v>
-      </c>
-      <c r="U52" s="3">
-        <v>176800</v>
       </c>
       <c r="V52" s="3">
         <v>176800</v>
       </c>
       <c r="W52" s="3">
+        <v>176800</v>
+      </c>
+      <c r="X52" s="3">
         <v>100</v>
       </c>
-      <c r="X52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y52" s="3" t="s">
         <v>3</v>
       </c>
@@ -3962,8 +4082,11 @@
       <c r="AB52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4042,74 +4165,77 @@
       <c r="AB53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>263300</v>
+      </c>
+      <c r="E54" s="3">
         <v>260300</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>216800</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>248800</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>155700</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>186500</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>154100</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>109000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>99700</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>106800</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>138500</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>97700</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>126900</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>169200</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>190100</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>109900</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>127800</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>138300</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>177300</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>177500</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>100</v>
       </c>
-      <c r="X54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y54" s="3" t="s">
         <v>3</v>
       </c>
@@ -4122,8 +4248,11 @@
       <c r="AB54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4152,8 +4281,9 @@
       <c r="Z55" s="3"/>
       <c r="AA55" s="3"/>
       <c r="AB55" s="3"/>
-    </row>
-    <row r="56" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC55" s="3"/>
+    </row>
+    <row r="56" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4182,73 +4312,74 @@
       <c r="Z56" s="3"/>
       <c r="AA56" s="3"/>
       <c r="AB56" s="3"/>
-    </row>
-    <row r="57" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC56" s="3"/>
+    </row>
+    <row r="57" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>24300</v>
+      </c>
+      <c r="E57" s="3">
         <v>16700</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>24300</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>24100</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>18300</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>20500</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>13800</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>15400</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>32500</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>34700</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>35500</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>29100</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>11700</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>13700</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>13200</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>15200</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>20200</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>11400</v>
       </c>
-      <c r="U57" s="3">
-        <v>0</v>
-      </c>
       <c r="V57" s="3">
         <v>0</v>
       </c>
       <c r="W57" s="3">
         <v>0</v>
       </c>
-      <c r="X57" s="3" t="s">
-        <v>3</v>
+      <c r="X57" s="3">
+        <v>0</v>
       </c>
       <c r="Y57" s="3" t="s">
         <v>3</v>
@@ -4262,74 +4393,77 @@
       <c r="AB57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>5100</v>
+      </c>
+      <c r="E58" s="3">
         <v>3900</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>4300</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>5500</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>5100</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>4900</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>4600</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>4400</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>12400</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>5600</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>2900</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>14000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>6700</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>6600</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>6500</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>6100</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>1200</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>1100</v>
       </c>
-      <c r="U58" s="3">
-        <v>0</v>
-      </c>
       <c r="V58" s="3">
         <v>0</v>
       </c>
       <c r="W58" s="3">
+        <v>0</v>
+      </c>
+      <c r="X58" s="3">
         <v>100</v>
       </c>
-      <c r="X58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y58" s="3" t="s">
         <v>3</v>
       </c>
@@ -4342,70 +4476,73 @@
       <c r="AB58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>48800</v>
+      </c>
+      <c r="E59" s="3">
         <v>32100</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>17100</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>13500</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>11500</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>12600</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>13000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>9000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>6300</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>20300</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>17500</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>16600</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>15500</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>9600</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>1200</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>3400</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>800</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>1700</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>1800</v>
       </c>
-      <c r="V59" s="3">
-        <v>0</v>
-      </c>
-      <c r="W59" s="3" t="s">
-        <v>3</v>
+      <c r="W59" s="3">
+        <v>0</v>
       </c>
       <c r="X59" s="3" t="s">
         <v>3</v>
@@ -4422,73 +4559,76 @@
       <c r="AB59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>90700</v>
+      </c>
+      <c r="E60" s="3">
         <v>65000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>75100</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>68500</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>64900</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>60900</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>46800</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>43000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>65700</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>60600</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>55800</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>59600</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>33800</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>29900</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>20900</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>24600</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>22200</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>14100</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>1900</v>
-      </c>
-      <c r="V60" s="3">
-        <v>100</v>
       </c>
       <c r="W60" s="3">
         <v>100</v>
       </c>
-      <c r="X60" s="3" t="s">
-        <v>3</v>
+      <c r="X60" s="3">
+        <v>100</v>
       </c>
       <c r="Y60" s="3" t="s">
         <v>3</v>
@@ -4502,65 +4642,68 @@
       <c r="AB60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>325300</v>
+      </c>
+      <c r="E61" s="3">
         <v>316600</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>187000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>152800</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>206700</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>204000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>207500</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>233300</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>202400</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>170400</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>160800</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>90300</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>95300</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>102700</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>106800</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>13500</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>100</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>300</v>
       </c>
-      <c r="U61" s="3">
-        <v>0</v>
-      </c>
       <c r="V61" s="3">
         <v>0</v>
       </c>
@@ -4582,65 +4725,68 @@
       <c r="AB61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>274900</v>
+      </c>
+      <c r="E62" s="3">
         <v>456200</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>369100</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>173800</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>27500</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>28900</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>27100</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>61200</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>6300</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>8500</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>10100</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>5700</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>8000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>4200</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>3900</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>3100</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>3700</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>800</v>
       </c>
-      <c r="U62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V62" s="3" t="s">
         <v>3</v>
       </c>
@@ -4656,14 +4802,17 @@
       <c r="Z62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AA62" s="3">
-        <v>0</v>
+      <c r="AA62" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AB62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4742,8 +4891,11 @@
       <c r="AB63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4822,8 +4974,11 @@
       <c r="AB64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4902,73 +5057,76 @@
       <c r="AB65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>694600</v>
+      </c>
+      <c r="E66" s="3">
         <v>842100</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>634500</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>399500</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>303400</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>297300</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>282400</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>338500</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>275300</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>239500</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>226800</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>155600</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>137100</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>136700</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>131700</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>41300</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>26000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>15200</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>1900</v>
-      </c>
-      <c r="V66" s="3">
-        <v>100</v>
       </c>
       <c r="W66" s="3">
         <v>100</v>
       </c>
-      <c r="X66" s="3" t="s">
-        <v>3</v>
+      <c r="X66" s="3">
+        <v>100</v>
       </c>
       <c r="Y66" s="3" t="s">
         <v>3</v>
@@ -4982,8 +5140,11 @@
       <c r="AB66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5012,8 +5173,9 @@
       <c r="Z67" s="3"/>
       <c r="AA67" s="3"/>
       <c r="AB67" s="3"/>
-    </row>
-    <row r="68" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC67" s="3"/>
+    </row>
+    <row r="68" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5092,8 +5254,11 @@
       <c r="AB68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5172,23 +5337,26 @@
       <c r="AB69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
       <c r="D70" s="3">
+        <v>510900</v>
+      </c>
+      <c r="E70" s="3">
         <v>488700</v>
       </c>
-      <c r="E70" s="3">
+      <c r="F70" s="3">
         <v>156100</v>
       </c>
-      <c r="F70" s="3">
+      <c r="G70" s="3">
         <v>40100</v>
       </c>
-      <c r="G70" s="3">
-        <v>0</v>
-      </c>
       <c r="H70" s="3">
         <v>0</v>
       </c>
@@ -5252,8 +5420,11 @@
       <c r="AB70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5332,73 +5503,76 @@
       <c r="AB71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-1546600</v>
+      </c>
+      <c r="E72" s="3">
         <v>-1561700</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-1293600</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-950700</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-922600</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-875800</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-834600</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-849600</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-717900</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-646300</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-589700</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-519000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-462300</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-416500</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-385900</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-367800</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-313800</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-290800</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-2000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-100</v>
       </c>
-      <c r="W72" s="3">
-        <v>0</v>
-      </c>
-      <c r="X72" s="3" t="s">
-        <v>3</v>
+      <c r="X72" s="3">
+        <v>0</v>
       </c>
       <c r="Y72" s="3" t="s">
         <v>3</v>
@@ -5412,8 +5586,11 @@
       <c r="AB72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5492,8 +5669,11 @@
       <c r="AB73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5572,8 +5752,11 @@
       <c r="AB74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5652,73 +5835,76 @@
       <c r="AB75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>-942200</v>
+      </c>
+      <c r="E76" s="3">
         <v>-1070500</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>-573800</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>-190800</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>-147700</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>-110800</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>-128300</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>-229500</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>-175600</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>-132700</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>-88300</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>-57800</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>-10200</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>32400</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>58400</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>68600</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>101800</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>123100</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>175500</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>177400</v>
       </c>
-      <c r="W76" s="3">
-        <v>0</v>
-      </c>
-      <c r="X76" s="3" t="s">
-        <v>3</v>
+      <c r="X76" s="3">
+        <v>0</v>
       </c>
       <c r="Y76" s="3" t="s">
         <v>3</v>
@@ -5732,8 +5918,11 @@
       <c r="AB76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5812,79 +6001,82 @@
       <c r="AB77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:28" x14ac:dyDescent="0.2">
+      <c r="AC77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:28" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45565</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45473</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45382</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45291</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45199</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45107</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45016</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44926</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44834</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44742</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44651</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44561</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44469</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44377</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44286</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44196</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44104</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44012</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43921</v>
       </c>
-      <c r="X80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="Y80" s="2" t="s">
         <v>3</v>
       </c>
@@ -5897,73 +6089,76 @@
       <c r="AB80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>15100</v>
+      </c>
+      <c r="E81" s="3">
         <v>-268100</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-342900</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-28200</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-46700</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-41200</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>14900</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-131600</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-71600</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-56600</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-70700</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-56700</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-45800</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-30600</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-18100</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-54000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-21500</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-66700</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-2000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-100</v>
       </c>
-      <c r="W81" s="3">
-        <v>0</v>
-      </c>
-      <c r="X81" s="3" t="s">
-        <v>3</v>
+      <c r="X81" s="3">
+        <v>0</v>
       </c>
       <c r="Y81" s="3" t="s">
         <v>3</v>
@@ -5977,8 +6172,11 @@
       <c r="AB81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6007,62 +6205,63 @@
       <c r="Z82" s="3"/>
       <c r="AA82" s="3"/>
       <c r="AB82" s="3"/>
-    </row>
-    <row r="83" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC82" s="3"/>
+    </row>
+    <row r="83" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>1500</v>
+      </c>
+      <c r="E83" s="3">
         <v>2700</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>2400</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>2700</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>2900</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>3200</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>1800</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>1500</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>1200</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>3000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>1600</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>1300</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>1000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>800</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>700</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>600</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>500</v>
       </c>
-      <c r="T83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U83" s="3" t="s">
         <v>3</v>
       </c>
@@ -6078,8 +6277,8 @@
       <c r="Y83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Z83" s="3">
-        <v>0</v>
+      <c r="Z83" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AA83" s="3">
         <v>0</v>
@@ -6087,8 +6286,11 @@
       <c r="AB83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6167,8 +6369,11 @@
       <c r="AB84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6247,8 +6452,11 @@
       <c r="AB85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6327,8 +6535,11 @@
       <c r="AB86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6407,8 +6618,11 @@
       <c r="AB87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6487,73 +6701,76 @@
       <c r="AB88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-28900</v>
+      </c>
+      <c r="E89" s="3">
         <v>-42700</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-44400</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-26300</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-40500</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-37400</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-32000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-45100</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-30500</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-37700</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-72100</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-44300</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-42700</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-35500</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-31700</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-39200</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-9700</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-26100</v>
-      </c>
-      <c r="U89" s="3">
-        <v>-200</v>
       </c>
       <c r="V89" s="3">
         <v>-200</v>
       </c>
       <c r="W89" s="3">
-        <v>0</v>
-      </c>
-      <c r="X89" s="3" t="s">
-        <v>3</v>
+        <v>-200</v>
+      </c>
+      <c r="X89" s="3">
+        <v>0</v>
       </c>
       <c r="Y89" s="3" t="s">
         <v>3</v>
@@ -6567,8 +6784,11 @@
       <c r="AB89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6597,62 +6817,63 @@
       <c r="Z90" s="3"/>
       <c r="AA90" s="3"/>
       <c r="AB90" s="3"/>
-    </row>
-    <row r="91" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC90" s="3"/>
+    </row>
+    <row r="91" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-4900</v>
+      </c>
+      <c r="E91" s="3">
         <v>-13100</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-9800</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-6200</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-4000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-8100</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-11100</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-7200</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-2900</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-1300</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-7300</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-6400</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-5100</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-4200</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-3800</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-3100</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-4500</v>
       </c>
-      <c r="T91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="U91" s="3" t="s">
         <v>3</v>
       </c>
@@ -6668,8 +6889,8 @@
       <c r="Y91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Z91" s="3">
-        <v>0</v>
+      <c r="Z91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AA91" s="3">
         <v>0</v>
@@ -6677,8 +6898,11 @@
       <c r="AB91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6757,8 +6981,11 @@
       <c r="AB92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6837,67 +7064,70 @@
       <c r="AB93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-4900</v>
+      </c>
+      <c r="E94" s="3">
         <v>-13100</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-9800</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-6300</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-4000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-8300</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-11100</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-7200</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-2900</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>1900</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-7300</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-6600</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-5100</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-3100</v>
-      </c>
-      <c r="Q94" s="3">
-        <v>-4400</v>
       </c>
       <c r="R94" s="3">
         <v>-4400</v>
       </c>
       <c r="S94" s="3">
+        <v>-4400</v>
+      </c>
+      <c r="T94" s="3">
         <v>-11400</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>170100</v>
       </c>
-      <c r="U94" s="3">
-        <v>0</v>
-      </c>
-      <c r="V94" s="3" t="s">
-        <v>3</v>
+      <c r="V94" s="3">
+        <v>0</v>
       </c>
       <c r="W94" s="3" t="s">
         <v>3</v>
@@ -6911,14 +7141,17 @@
       <c r="Z94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AA94" s="3">
-        <v>0</v>
+      <c r="AA94" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AB94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6947,8 +7180,9 @@
       <c r="Z95" s="3"/>
       <c r="AA95" s="3"/>
       <c r="AB95" s="3"/>
-    </row>
-    <row r="96" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC95" s="3"/>
+    </row>
+    <row r="96" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -6976,8 +7210,8 @@
       <c r="K96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L96" s="3">
-        <v>0</v>
+      <c r="L96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M96" s="3">
         <v>0</v>
@@ -7027,8 +7261,11 @@
       <c r="AB96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7107,8 +7344,11 @@
       <c r="AB97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7187,8 +7427,11 @@
       <c r="AB98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7267,74 +7510,77 @@
       <c r="AB99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>42200</v>
+      </c>
+      <c r="E100" s="3">
         <v>128500</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>27300</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>43900</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>6100</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>57300</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>78000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>60200</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>32500</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>16000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>112900</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>11800</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-1200</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-400</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>106200</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>17600</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-100</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-23300</v>
       </c>
-      <c r="U100" s="3">
-        <v>0</v>
-      </c>
       <c r="V100" s="3">
+        <v>0</v>
+      </c>
+      <c r="W100" s="3">
         <v>177500</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>100</v>
       </c>
-      <c r="X100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y100" s="3" t="s">
         <v>3</v>
       </c>
@@ -7347,8 +7593,11 @@
       <c r="AB100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -7373,17 +7622,17 @@
       <c r="J101" s="3">
         <v>0</v>
       </c>
-      <c r="K101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="L101" s="3">
-        <v>0</v>
+      <c r="K101" s="3">
+        <v>0</v>
+      </c>
+      <c r="L101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M101" s="3">
         <v>0</v>
       </c>
-      <c r="N101" s="3" t="s">
-        <v>3</v>
+      <c r="N101" s="3">
+        <v>0</v>
       </c>
       <c r="O101" s="3" t="s">
         <v>3</v>
@@ -7400,8 +7649,8 @@
       <c r="S101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="T101" s="3">
-        <v>0</v>
+      <c r="T101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="U101" s="3">
         <v>0</v>
@@ -7427,73 +7676,76 @@
       <c r="AB101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:28" x14ac:dyDescent="0.2">
+      <c r="AC101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>8300</v>
+      </c>
+      <c r="E102" s="3">
         <v>72700</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-26900</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>11300</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-38400</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>11600</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>34900</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>7900</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-900</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-19800</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>33500</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-39100</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-49100</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-39000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>70000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-26000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-21100</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>120700</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-200</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>500</v>
       </c>
-      <c r="W102" s="3">
-        <v>0</v>
-      </c>
-      <c r="X102" s="3" t="s">
-        <v>3</v>
+      <c r="X102" s="3">
+        <v>0</v>
       </c>
       <c r="Y102" s="3" t="s">
         <v>3</v>
@@ -7505,6 +7757,9 @@
         <v>3</v>
       </c>
       <c r="AB102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/EOSE_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/EOSE_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="380" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="382" uniqueCount="92">
   <si>
     <t>EOSE</t>
   </si>
@@ -656,112 +656,113 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AC102"/>
+  <dimension ref="A5:AD102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="29" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="30" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:30" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E7" s="2">
         <v>45747</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45657</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45565</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45473</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45382</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45291</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45199</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45107</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45016</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44926</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44834</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44742</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44651</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44561</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44469</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44377</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44286</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44196</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44104</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44012</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43921</v>
       </c>
-      <c r="Y7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="Z7" s="2" t="s">
         <v>3</v>
       </c>
@@ -774,67 +775,70 @@
       <c r="AC7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>15200</v>
+      </c>
+      <c r="E8" s="3">
         <v>10500</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>7300</v>
-      </c>
-      <c r="F8" s="3">
-        <v>900</v>
       </c>
       <c r="G8" s="3">
         <v>900</v>
       </c>
       <c r="H8" s="3">
-        <v>6600</v>
+        <v>900</v>
       </c>
       <c r="I8" s="3">
         <v>6600</v>
       </c>
       <c r="J8" s="3">
+        <v>6600</v>
+      </c>
+      <c r="K8" s="3">
         <v>700</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>200</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>8800</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>2700</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>6100</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>5900</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>3300</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>3100</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>700</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>600</v>
-      </c>
-      <c r="T8" s="3">
-        <v>200</v>
       </c>
       <c r="U8" s="3">
         <v>200</v>
       </c>
-      <c r="V8" s="3" t="s">
-        <v>3</v>
+      <c r="V8" s="3">
+        <v>200</v>
       </c>
       <c r="W8" s="3" t="s">
         <v>3</v>
@@ -851,74 +855,77 @@
       <c r="AA8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AB8" s="3">
-        <v>0</v>
+      <c r="AB8" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AC8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>46200</v>
+      </c>
+      <c r="E9" s="3">
         <v>35000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>30800</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>25800</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>14100</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>28200</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>30400</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>21300</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>11200</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>26900</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>30800</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>50000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>36900</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>35600</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>21100</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>12900</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>12400</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>100</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>5500</v>
       </c>
-      <c r="V9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W9" s="3" t="s">
         <v>3</v>
       </c>
@@ -940,68 +947,71 @@
       <c r="AC9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>-31000</v>
+      </c>
+      <c r="E10" s="3">
         <v>-24500</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>-23500</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>-24900</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>-13200</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>-21600</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>-23700</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>-20600</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>-11000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>-18100</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>-28100</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>-43900</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>-31000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>-32300</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>-18000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>-12200</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>-11800</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>100</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>-5300</v>
       </c>
-      <c r="V10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W10" s="3" t="s">
         <v>3</v>
       </c>
@@ -1023,8 +1033,11 @@
       <c r="AC10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1054,68 +1067,69 @@
       <c r="AA11" s="3"/>
       <c r="AB11" s="3"/>
       <c r="AC11" s="3"/>
-    </row>
-    <row r="12" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD11" s="3"/>
+    </row>
+    <row r="12" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>7200</v>
+      </c>
+      <c r="E12" s="3">
         <v>6800</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>5900</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>7400</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>4300</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>5200</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>5000</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>3200</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>5000</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>5400</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>3600</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>4500</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>5500</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>5000</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>5400</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>5100</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>3600</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>5000</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>14000</v>
       </c>
-      <c r="V12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W12" s="3" t="s">
         <v>3</v>
       </c>
@@ -1137,8 +1151,11 @@
       <c r="AC12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1220,67 +1237,70 @@
       <c r="AC13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>17700</v>
+      </c>
+      <c r="E14" s="3">
         <v>6500</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>-31500</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>6200</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>-68000</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>100</v>
       </c>
-      <c r="I14" s="3">
-        <v>0</v>
-      </c>
       <c r="J14" s="3">
+        <v>0</v>
+      </c>
+      <c r="K14" s="3">
         <v>1000</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>7300</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>2400</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>4300</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>1400</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>2000</v>
       </c>
-      <c r="P14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q14" s="3">
-        <v>0</v>
+      <c r="Q14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="R14" s="3">
+        <v>0</v>
+      </c>
+      <c r="S14" s="3">
         <v>-1300</v>
       </c>
-      <c r="S14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="T14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U14" s="3">
-        <v>0</v>
-      </c>
-      <c r="V14" s="3" t="s">
-        <v>3</v>
+      <c r="U14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="V14" s="3">
+        <v>0</v>
       </c>
       <c r="W14" s="3" t="s">
         <v>3</v>
@@ -1288,8 +1308,8 @@
       <c r="X14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Y14" s="3">
-        <v>0</v>
+      <c r="Y14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Z14" s="3">
         <v>0</v>
@@ -1303,41 +1323,44 @@
       <c r="AC14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:30" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>2900</v>
+      </c>
+      <c r="E15" s="3">
         <v>2700</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>2600</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>2700</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>1400</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>1200</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>2400</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>2200</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>2500</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>2700</v>
       </c>
-      <c r="M15" s="3">
-        <v>0</v>
-      </c>
       <c r="N15" s="3">
         <v>0</v>
       </c>
@@ -1386,8 +1409,11 @@
       <c r="AC15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:30" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1414,76 +1440,77 @@
       <c r="AA16" s="3"/>
       <c r="AB16" s="3"/>
       <c r="AC16" s="3"/>
-    </row>
-    <row r="17" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD16" s="3"/>
+    </row>
+    <row r="17" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>78900</v>
+      </c>
+      <c r="E17" s="3">
         <v>62800</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>53300</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>51000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>29700</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>47700</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>48800</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>37600</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>29400</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>46300</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>51300</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>70600</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>63300</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>55000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>40700</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>25700</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>49800</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>21800</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>37200</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>2000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>100</v>
       </c>
-      <c r="X17" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y17" s="3" t="s">
-        <v>3</v>
+      <c r="Y17" s="3">
+        <v>0</v>
       </c>
       <c r="Z17" s="3" t="s">
         <v>3</v>
@@ -1497,68 +1524,71 @@
       <c r="AC17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-63600</v>
+      </c>
+      <c r="E18" s="3">
         <v>-52400</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-46100</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-50100</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-28800</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-41100</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-42200</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-36900</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-29200</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-37500</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-48600</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-64500</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-57400</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-51700</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-37600</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-25000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-49200</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-21600</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-37000</v>
       </c>
-      <c r="V18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1580,8 +1610,11 @@
       <c r="AC18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1611,68 +1644,69 @@
       <c r="AA19" s="3"/>
       <c r="AB19" s="3"/>
       <c r="AC19" s="3"/>
-    </row>
-    <row r="20" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD19" s="3"/>
+    </row>
+    <row r="20" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>135000</v>
+      </c>
+      <c r="E20" s="3">
         <v>-80000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>248300</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>281100</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>58900</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-3600</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-9600</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-62200</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>75500</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>13100</v>
-      </c>
-      <c r="M20" s="3">
-        <v>-400</v>
       </c>
       <c r="N20" s="3">
         <v>-400</v>
       </c>
       <c r="O20" s="3">
+        <v>-400</v>
+      </c>
+      <c r="P20" s="3">
         <v>3600</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>8400</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>8300</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>10700</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-4700</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>200</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-5900</v>
       </c>
-      <c r="V20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W20" s="3" t="s">
         <v>3</v>
       </c>
@@ -1694,65 +1728,68 @@
       <c r="AC20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>-195700</v>
+      </c>
+      <c r="E21" s="3">
         <v>30200</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-291700</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-328600</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-86300</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-36300</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-30200</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>27500</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-102200</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-47900</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-46000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-63300</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-52500</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-42300</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-28500</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-13700</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-53300</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-21000</v>
       </c>
-      <c r="U21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1777,68 +1814,71 @@
       <c r="AC21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>6600</v>
+      </c>
+      <c r="E22" s="3">
         <v>5900</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>5200</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>5400</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>8400</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>9100</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>8600</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>9400</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>19600</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>18600</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>7600</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>5700</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>2900</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>2500</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>1300</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>3700</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>200</v>
       </c>
-      <c r="T22" s="3">
-        <v>0</v>
-      </c>
       <c r="U22" s="3">
+        <v>0</v>
+      </c>
+      <c r="V22" s="3">
         <v>23800</v>
       </c>
-      <c r="V22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W22" s="3" t="s">
         <v>3</v>
       </c>
@@ -1854,82 +1894,85 @@
       <c r="AA22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AB22" s="3">
-        <v>0</v>
+      <c r="AB22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AC22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-222900</v>
+      </c>
+      <c r="E23" s="3">
         <v>15100</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-268100</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-342900</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-28200</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-46700</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-41200</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>14900</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-131600</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-71600</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-56600</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-70600</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-56700</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-45800</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-30600</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-18100</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-54000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-21500</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-66700</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-2000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-100</v>
       </c>
-      <c r="X23" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y23" s="3" t="s">
-        <v>3</v>
+      <c r="Y23" s="3">
+        <v>0</v>
       </c>
       <c r="Z23" s="3" t="s">
         <v>3</v>
@@ -1943,8 +1986,11 @@
       <c r="AC23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1979,16 +2025,16 @@
         <v>0</v>
       </c>
       <c r="N24" s="3">
+        <v>0</v>
+      </c>
+      <c r="O24" s="3">
         <v>100</v>
       </c>
-      <c r="O24" s="3">
-        <v>0</v>
-      </c>
       <c r="P24" s="3">
         <v>0</v>
       </c>
-      <c r="Q24" s="3" t="s">
-        <v>3</v>
+      <c r="Q24" s="3">
+        <v>0</v>
       </c>
       <c r="R24" s="3" t="s">
         <v>3</v>
@@ -2005,8 +2051,8 @@
       <c r="V24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="W24" s="3">
-        <v>0</v>
+      <c r="W24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="X24" s="3">
         <v>0</v>
@@ -2026,8 +2072,11 @@
       <c r="AC24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2109,76 +2158,79 @@
       <c r="AC25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-222900</v>
+      </c>
+      <c r="E26" s="3">
         <v>15100</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-268100</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-342900</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-28200</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-46700</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-41200</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>14900</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-131600</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-71600</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-56600</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-70700</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-56700</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-45800</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-30600</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-18100</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-54000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-21500</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-66700</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-2000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-100</v>
       </c>
-      <c r="X26" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y26" s="3" t="s">
-        <v>3</v>
+      <c r="Y26" s="3">
+        <v>0</v>
       </c>
       <c r="Z26" s="3" t="s">
         <v>3</v>
@@ -2192,76 +2244,79 @@
       <c r="AC26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-248800</v>
+      </c>
+      <c r="E27" s="3">
         <v>95100</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-481500</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-384100</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-51800</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-46700</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-41200</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>14900</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-131600</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-71600</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-56600</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-70700</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-56700</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-45800</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-30600</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-18100</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-54000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-21500</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-66700</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-2000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-100</v>
       </c>
-      <c r="X27" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y27" s="3" t="s">
-        <v>3</v>
+      <c r="Y27" s="3">
+        <v>0</v>
       </c>
       <c r="Z27" s="3" t="s">
         <v>3</v>
@@ -2275,8 +2330,11 @@
       <c r="AC27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2358,8 +2416,11 @@
       <c r="AC28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2441,8 +2502,11 @@
       <c r="AC29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2524,8 +2588,11 @@
       <c r="AC30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2607,68 +2674,71 @@
       <c r="AC31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-135000</v>
+      </c>
+      <c r="E32" s="3">
         <v>80000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-248300</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-281100</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-58900</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>3600</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>9600</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>62200</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-75500</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-13100</v>
-      </c>
-      <c r="M32" s="3">
-        <v>400</v>
       </c>
       <c r="N32" s="3">
         <v>400</v>
       </c>
       <c r="O32" s="3">
+        <v>400</v>
+      </c>
+      <c r="P32" s="3">
         <v>-3600</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-8400</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-8300</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-10700</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>4700</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-200</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>5900</v>
       </c>
-      <c r="V32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W32" s="3" t="s">
         <v>3</v>
       </c>
@@ -2690,76 +2760,79 @@
       <c r="AC32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-222900</v>
+      </c>
+      <c r="E33" s="3">
         <v>15100</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-268100</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-342900</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-28200</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-46700</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-41200</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>14900</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-131600</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-71600</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-56600</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-70700</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-56700</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-45800</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-30600</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-18100</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-54000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-21500</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-66700</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-2000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-100</v>
       </c>
-      <c r="X33" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y33" s="3" t="s">
-        <v>3</v>
+      <c r="Y33" s="3">
+        <v>0</v>
       </c>
       <c r="Z33" s="3" t="s">
         <v>3</v>
@@ -2773,8 +2846,11 @@
       <c r="AC33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2856,76 +2932,79 @@
       <c r="AC34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-222900</v>
+      </c>
+      <c r="E35" s="3">
         <v>15100</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-268100</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-342900</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-28200</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-46700</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-41200</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>14900</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-131600</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-71600</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-56600</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-70700</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-56700</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-45800</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-30600</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-18100</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-54000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-21500</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-66700</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-2000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-100</v>
       </c>
-      <c r="X35" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y35" s="3" t="s">
-        <v>3</v>
+      <c r="Y35" s="3">
+        <v>0</v>
       </c>
       <c r="Z35" s="3" t="s">
         <v>3</v>
@@ -2939,82 +3018,85 @@
       <c r="AC35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:30" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E38" s="2">
         <v>45747</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45657</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45565</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45473</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45382</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45291</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45199</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45107</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45016</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44926</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44834</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44742</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44651</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44561</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44469</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44377</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44286</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44196</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44104</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44012</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43921</v>
       </c>
-      <c r="Y38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="Z38" s="2" t="s">
         <v>3</v>
       </c>
@@ -3027,8 +3109,11 @@
       <c r="AC38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3058,8 +3143,9 @@
       <c r="AA39" s="3"/>
       <c r="AB39" s="3"/>
       <c r="AC39" s="3"/>
-    </row>
-    <row r="40" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD39" s="3"/>
+    </row>
+    <row r="40" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3089,76 +3175,77 @@
       <c r="AA40" s="3"/>
       <c r="AB40" s="3"/>
       <c r="AC40" s="3"/>
-    </row>
-    <row r="41" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD40" s="3"/>
+    </row>
+    <row r="41" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>120200</v>
+      </c>
+      <c r="E41" s="3">
         <v>82600</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>74300</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>23000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>52500</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>31800</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>69500</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>58000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>23200</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>16100</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>17100</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>38400</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>16300</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>55400</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>104800</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>144200</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>74700</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>100700</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>121900</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>300</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>500</v>
       </c>
-      <c r="X41" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y41" s="3" t="s">
-        <v>3</v>
+      <c r="Y41" s="3">
+        <v>0</v>
       </c>
       <c r="Z41" s="3" t="s">
         <v>3</v>
@@ -3172,8 +3259,11 @@
       <c r="AC41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3255,76 +3345,79 @@
       <c r="AC42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>24400</v>
+      </c>
+      <c r="E43" s="3">
         <v>24300</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>40100</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>82600</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>100800</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>27300</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>20500</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>4300</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>3900</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>7800</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>3600</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>6400</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>3600</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>3700</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>2000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>2400</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>400</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>300</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>100</v>
       </c>
-      <c r="V43" s="3">
-        <v>0</v>
-      </c>
       <c r="W43" s="3">
         <v>0</v>
       </c>
       <c r="X43" s="3">
         <v>0</v>
       </c>
-      <c r="Y43" s="3" t="s">
-        <v>3</v>
+      <c r="Y43" s="3">
+        <v>0</v>
       </c>
       <c r="Z43" s="3" t="s">
         <v>3</v>
@@ -3338,68 +3431,71 @@
       <c r="AC43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>41100</v>
+      </c>
+      <c r="E44" s="3">
         <v>40300</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>32800</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>25900</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>17800</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>14400</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>17100</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>20600</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>16600</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>14100</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>23300</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>23200</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>12900</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>10300</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>13000</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>5000</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>4400</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>100</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>200</v>
       </c>
-      <c r="V44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W44" s="3" t="s">
         <v>3</v>
       </c>
@@ -3415,80 +3511,83 @@
       <c r="AA44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AB44" s="3">
-        <v>0</v>
+      <c r="AB44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AC44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>12600</v>
+      </c>
+      <c r="E45" s="3">
         <v>22900</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>17600</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>13900</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>8600</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>9600</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>10700</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>21400</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>15500</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>7400</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>11300</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>13600</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>27600</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>26800</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>22700</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>17400</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>12200</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>6200</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>5200</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>200</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>300</v>
       </c>
-      <c r="X45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y45" s="3" t="s">
         <v>3</v>
       </c>
@@ -3504,76 +3603,79 @@
       <c r="AC45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>232300</v>
+      </c>
+      <c r="E46" s="3">
         <v>185500</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>179900</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>149200</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>183500</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>87000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>122300</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>108500</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>64000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>50000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>55100</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>81600</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>60500</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>96200</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>142600</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>169100</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>91700</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>107400</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>127400</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>600</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>800</v>
       </c>
-      <c r="X46" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y46" s="3" t="s">
-        <v>3</v>
+      <c r="Y46" s="3">
+        <v>0</v>
       </c>
       <c r="Z46" s="3" t="s">
         <v>3</v>
@@ -3587,8 +3689,11 @@
       <c r="AC46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3619,36 +3724,36 @@
       <c r="L47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M47" s="3">
+      <c r="M47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N47" s="3">
         <v>800</v>
-      </c>
-      <c r="N47" s="3">
-        <v>3700</v>
       </c>
       <c r="O47" s="3">
         <v>3700</v>
       </c>
       <c r="P47" s="3">
-        <v>3500</v>
+        <v>3700</v>
       </c>
       <c r="Q47" s="3">
         <v>3500</v>
       </c>
       <c r="R47" s="3">
+        <v>3500</v>
+      </c>
+      <c r="S47" s="3">
         <v>4700</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>4100</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>11100</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>3700</v>
       </c>
-      <c r="V47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W47" s="3" t="s">
         <v>3</v>
       </c>
@@ -3664,74 +3769,77 @@
       <c r="AA47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AB47" s="3">
-        <v>0</v>
+      <c r="AB47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AC47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>78200</v>
+      </c>
+      <c r="E48" s="3">
         <v>46500</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>48600</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>54600</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>54000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>46500</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>41900</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>24300</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>23900</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>28700</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>31500</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>34400</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>25800</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>19500</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>16400</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>10300</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>8400</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>8000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>5700</v>
       </c>
-      <c r="V48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W48" s="3" t="s">
         <v>3</v>
       </c>
@@ -3747,14 +3855,17 @@
       <c r="AA48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AB48" s="3">
-        <v>0</v>
+      <c r="AB48" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AC48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -3762,7 +3873,7 @@
         <v>4500</v>
       </c>
       <c r="E49" s="3">
-        <v>4600</v>
+        <v>4500</v>
       </c>
       <c r="F49" s="3">
         <v>4600</v>
@@ -3780,13 +3891,13 @@
         <v>4600</v>
       </c>
       <c r="K49" s="3">
-        <v>4700</v>
+        <v>4600</v>
       </c>
       <c r="L49" s="3">
         <v>4700</v>
       </c>
       <c r="M49" s="3">
-        <v>4600</v>
+        <v>4700</v>
       </c>
       <c r="N49" s="3">
         <v>4600</v>
@@ -3807,13 +3918,13 @@
         <v>4600</v>
       </c>
       <c r="T49" s="3">
-        <v>300</v>
+        <v>4600</v>
       </c>
       <c r="U49" s="3">
         <v>300</v>
       </c>
-      <c r="V49" s="3" t="s">
-        <v>3</v>
+      <c r="V49" s="3">
+        <v>300</v>
       </c>
       <c r="W49" s="3" t="s">
         <v>3</v>
@@ -3830,14 +3941,17 @@
       <c r="AA49" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AB49" s="3">
-        <v>0</v>
+      <c r="AB49" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AC49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3919,8 +4033,11 @@
       <c r="AC50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4002,77 +4119,80 @@
       <c r="AC51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>46000</v>
+      </c>
+      <c r="E52" s="3">
         <v>26700</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>26300</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>7300</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>4900</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>17600</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>15700</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>15900</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>15600</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>15500</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>14800</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>14200</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>3200</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>3100</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>2100</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>1400</v>
-      </c>
-      <c r="S52" s="3">
-        <v>1000</v>
       </c>
       <c r="T52" s="3">
         <v>1000</v>
       </c>
       <c r="U52" s="3">
+        <v>1000</v>
+      </c>
+      <c r="V52" s="3">
         <v>1200</v>
-      </c>
-      <c r="V52" s="3">
-        <v>176800</v>
       </c>
       <c r="W52" s="3">
         <v>176800</v>
       </c>
       <c r="X52" s="3">
+        <v>176800</v>
+      </c>
+      <c r="Y52" s="3">
         <v>100</v>
       </c>
-      <c r="Y52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z52" s="3" t="s">
         <v>3</v>
       </c>
@@ -4085,8 +4205,11 @@
       <c r="AC52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4168,77 +4291,80 @@
       <c r="AC53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>361000</v>
+      </c>
+      <c r="E54" s="3">
         <v>263300</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>260300</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>216800</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>248800</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>155700</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>186500</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>154100</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>109000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>99700</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>106800</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>138500</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>97700</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>126900</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>169200</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>190100</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>109900</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>127800</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>138300</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>177300</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>177500</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>100</v>
       </c>
-      <c r="Y54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z54" s="3" t="s">
         <v>3</v>
       </c>
@@ -4251,8 +4377,11 @@
       <c r="AC54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4282,8 +4411,9 @@
       <c r="AA55" s="3"/>
       <c r="AB55" s="3"/>
       <c r="AC55" s="3"/>
-    </row>
-    <row r="56" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD55" s="3"/>
+    </row>
+    <row r="56" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4313,76 +4443,77 @@
       <c r="AA56" s="3"/>
       <c r="AB56" s="3"/>
       <c r="AC56" s="3"/>
-    </row>
-    <row r="57" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD56" s="3"/>
+    </row>
+    <row r="57" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>39700</v>
+      </c>
+      <c r="E57" s="3">
         <v>24300</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>16700</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>24300</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>24100</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>18300</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>20500</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>13800</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>15400</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>32500</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>34700</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>35500</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>29100</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>11700</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>13700</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>13200</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>15200</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>20200</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>11400</v>
       </c>
-      <c r="V57" s="3">
-        <v>0</v>
-      </c>
       <c r="W57" s="3">
         <v>0</v>
       </c>
       <c r="X57" s="3">
         <v>0</v>
       </c>
-      <c r="Y57" s="3" t="s">
-        <v>3</v>
+      <c r="Y57" s="3">
+        <v>0</v>
       </c>
       <c r="Z57" s="3" t="s">
         <v>3</v>
@@ -4396,77 +4527,80 @@
       <c r="AC57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>3300</v>
+      </c>
+      <c r="E58" s="3">
+        <v>3400</v>
+      </c>
+      <c r="F58" s="3">
+        <v>3900</v>
+      </c>
+      <c r="G58" s="3">
+        <v>4300</v>
+      </c>
+      <c r="H58" s="3">
+        <v>5500</v>
+      </c>
+      <c r="I58" s="3">
         <v>5100</v>
       </c>
-      <c r="E58" s="3">
-        <v>3900</v>
-      </c>
-      <c r="F58" s="3">
-        <v>4300</v>
-      </c>
-      <c r="G58" s="3">
-        <v>5500</v>
-      </c>
-      <c r="H58" s="3">
-        <v>5100</v>
-      </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>4900</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>4600</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>4400</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>12400</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>5600</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>2900</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>14000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>6700</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>6600</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>6500</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>6100</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>1200</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>1100</v>
       </c>
-      <c r="V58" s="3">
-        <v>0</v>
-      </c>
       <c r="W58" s="3">
         <v>0</v>
       </c>
       <c r="X58" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y58" s="3">
         <v>100</v>
       </c>
-      <c r="Y58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z58" s="3" t="s">
         <v>3</v>
       </c>
@@ -4479,73 +4613,76 @@
       <c r="AC58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>48800</v>
+        <v>47300</v>
       </c>
       <c r="E59" s="3">
+        <v>50500</v>
+      </c>
+      <c r="F59" s="3">
         <v>32100</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>17100</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>13500</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>11500</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>12600</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>13000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>9000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>6300</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>20300</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>17500</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>16600</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>15500</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>9600</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>1200</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>3400</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>800</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>1700</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>1800</v>
       </c>
-      <c r="W59" s="3">
-        <v>0</v>
-      </c>
-      <c r="X59" s="3" t="s">
-        <v>3</v>
+      <c r="X59" s="3">
+        <v>0</v>
       </c>
       <c r="Y59" s="3" t="s">
         <v>3</v>
@@ -4562,76 +4699,79 @@
       <c r="AC59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>104300</v>
+      </c>
+      <c r="E60" s="3">
         <v>90700</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>65000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>75100</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>68500</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>64900</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>60900</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>46800</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>43000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>65700</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>60600</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>55800</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>59600</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>33800</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>29900</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>20900</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>24600</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>22200</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>14100</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>1900</v>
-      </c>
-      <c r="W60" s="3">
-        <v>100</v>
       </c>
       <c r="X60" s="3">
         <v>100</v>
       </c>
-      <c r="Y60" s="3" t="s">
-        <v>3</v>
+      <c r="Y60" s="3">
+        <v>100</v>
       </c>
       <c r="Z60" s="3" t="s">
         <v>3</v>
@@ -4645,68 +4785,71 @@
       <c r="AC60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>325300</v>
+        <v>445100</v>
       </c>
       <c r="E61" s="3">
+        <v>325200</v>
+      </c>
+      <c r="F61" s="3">
         <v>316600</v>
       </c>
-      <c r="F61" s="3">
-        <v>187000</v>
-      </c>
       <c r="G61" s="3">
-        <v>152800</v>
+        <v>186900</v>
       </c>
       <c r="H61" s="3">
-        <v>206700</v>
+        <v>152700</v>
       </c>
       <c r="I61" s="3">
+        <v>205100</v>
+      </c>
+      <c r="J61" s="3">
         <v>204000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>207500</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>233300</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>202400</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>170400</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>160800</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>90300</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>95300</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>102700</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>106800</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>13500</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>100</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>300</v>
       </c>
-      <c r="V61" s="3">
-        <v>0</v>
-      </c>
       <c r="W61" s="3">
         <v>0</v>
       </c>
@@ -4728,68 +4871,71 @@
       <c r="AC61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>380300</v>
+      </c>
+      <c r="E62" s="3">
         <v>274900</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>456200</v>
       </c>
-      <c r="F62" s="3">
-        <v>369100</v>
-      </c>
       <c r="G62" s="3">
-        <v>173800</v>
+        <v>369200</v>
       </c>
       <c r="H62" s="3">
-        <v>27500</v>
+        <v>173900</v>
       </c>
       <c r="I62" s="3">
+        <v>29100</v>
+      </c>
+      <c r="J62" s="3">
         <v>28900</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>27100</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>61200</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>6300</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>8500</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>10100</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>5700</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>8000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>4200</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>3900</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>3100</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>3700</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>800</v>
       </c>
-      <c r="V62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W62" s="3" t="s">
         <v>3</v>
       </c>
@@ -4805,14 +4951,17 @@
       <c r="AA62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AB62" s="3">
-        <v>0</v>
+      <c r="AB62" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AC62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4894,8 +5043,11 @@
       <c r="AC63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4977,8 +5129,11 @@
       <c r="AC64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5060,76 +5215,79 @@
       <c r="AC65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>931700</v>
+      </c>
+      <c r="E66" s="3">
         <v>694600</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>842100</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>634500</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>399500</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>303400</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>297300</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>282400</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>338500</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>275300</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>239500</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>226800</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>155600</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>137100</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>136700</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>131700</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>41300</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>26000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>15200</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>1900</v>
-      </c>
-      <c r="W66" s="3">
-        <v>100</v>
       </c>
       <c r="X66" s="3">
         <v>100</v>
       </c>
-      <c r="Y66" s="3" t="s">
-        <v>3</v>
+      <c r="Y66" s="3">
+        <v>100</v>
       </c>
       <c r="Z66" s="3" t="s">
         <v>3</v>
@@ -5143,8 +5301,11 @@
       <c r="AC66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5174,8 +5335,9 @@
       <c r="AA67" s="3"/>
       <c r="AB67" s="3"/>
       <c r="AC67" s="3"/>
-    </row>
-    <row r="68" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD67" s="3"/>
+    </row>
+    <row r="68" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5257,8 +5419,11 @@
       <c r="AC68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5340,26 +5505,29 @@
       <c r="AC69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
       <c r="D70" s="3">
+        <v>532300</v>
+      </c>
+      <c r="E70" s="3">
         <v>510900</v>
       </c>
-      <c r="E70" s="3">
+      <c r="F70" s="3">
         <v>488700</v>
       </c>
-      <c r="F70" s="3">
+      <c r="G70" s="3">
         <v>156100</v>
       </c>
-      <c r="G70" s="3">
+      <c r="H70" s="3">
         <v>40100</v>
       </c>
-      <c r="H70" s="3">
-        <v>0</v>
-      </c>
       <c r="I70" s="3">
         <v>0</v>
       </c>
@@ -5423,8 +5591,11 @@
       <c r="AC70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5506,76 +5677,79 @@
       <c r="AC71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-1774000</v>
+      </c>
+      <c r="E72" s="3">
         <v>-1546600</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-1561700</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-1293600</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-950700</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-922600</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-875800</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-834600</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-849600</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-717900</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-646300</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-589700</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-519000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-462300</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-416500</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-385900</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-367800</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-313800</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-290800</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-2000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-100</v>
       </c>
-      <c r="X72" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y72" s="3" t="s">
-        <v>3</v>
+      <c r="Y72" s="3">
+        <v>0</v>
       </c>
       <c r="Z72" s="3" t="s">
         <v>3</v>
@@ -5589,8 +5763,11 @@
       <c r="AC72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5672,8 +5849,11 @@
       <c r="AC73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5755,8 +5935,11 @@
       <c r="AC74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5838,76 +6021,79 @@
       <c r="AC75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>-1103000</v>
+      </c>
+      <c r="E76" s="3">
         <v>-942200</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>-1070500</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>-573800</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>-190800</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>-147700</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>-110800</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>-128300</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>-229500</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>-175600</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>-132700</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>-88300</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>-57800</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>-10200</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>32400</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>58400</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>68600</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>101800</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>123100</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>175500</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>177400</v>
       </c>
-      <c r="X76" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y76" s="3" t="s">
-        <v>3</v>
+      <c r="Y76" s="3">
+        <v>0</v>
       </c>
       <c r="Z76" s="3" t="s">
         <v>3</v>
@@ -5921,8 +6107,11 @@
       <c r="AC76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6004,82 +6193,85 @@
       <c r="AC77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:30" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:30" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45838</v>
+      </c>
+      <c r="E80" s="2">
         <v>45747</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45657</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45565</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45473</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45382</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45291</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45199</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45107</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45016</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44926</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44834</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44742</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44651</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44561</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44469</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44377</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44286</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44196</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44104</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44012</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43921</v>
       </c>
-      <c r="Y80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="Z80" s="2" t="s">
         <v>3</v>
       </c>
@@ -6092,76 +6284,79 @@
       <c r="AC80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-222900</v>
+      </c>
+      <c r="E81" s="3">
         <v>15100</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-268100</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-342900</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-28200</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-46700</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-41200</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>14900</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-131600</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-71600</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-56600</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-70700</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-56700</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-45800</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-30600</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-18100</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-54000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-21500</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-66700</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-2000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-100</v>
       </c>
-      <c r="X81" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y81" s="3" t="s">
-        <v>3</v>
+      <c r="Y81" s="3">
+        <v>0</v>
       </c>
       <c r="Z81" s="3" t="s">
         <v>3</v>
@@ -6175,8 +6370,11 @@
       <c r="AC81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6206,65 +6404,66 @@
       <c r="AA82" s="3"/>
       <c r="AB82" s="3"/>
       <c r="AC82" s="3"/>
-    </row>
-    <row r="83" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD82" s="3"/>
+    </row>
+    <row r="83" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>1700</v>
+      </c>
+      <c r="E83" s="3">
         <v>1500</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>2700</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>2400</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>2700</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>2900</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>3200</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>1800</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>1500</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>1200</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>3000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>1600</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>1300</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>1000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>800</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>700</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>600</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>500</v>
       </c>
-      <c r="U83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V83" s="3" t="s">
         <v>3</v>
       </c>
@@ -6280,8 +6479,8 @@
       <c r="Z83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AA83" s="3">
-        <v>0</v>
+      <c r="AA83" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AB83" s="3">
         <v>0</v>
@@ -6289,8 +6488,11 @@
       <c r="AC83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6372,8 +6574,11 @@
       <c r="AC84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6455,8 +6660,11 @@
       <c r="AC85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6538,8 +6746,11 @@
       <c r="AC86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6621,8 +6832,11 @@
       <c r="AC87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6704,76 +6918,79 @@
       <c r="AC88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-66100</v>
+      </c>
+      <c r="E89" s="3">
         <v>-28900</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-42700</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-44400</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-26300</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-40500</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-37400</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-32000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-45100</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-30500</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-37700</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-72100</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-44300</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-42700</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-35500</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-31700</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-39200</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-9700</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-26100</v>
-      </c>
-      <c r="V89" s="3">
-        <v>-200</v>
       </c>
       <c r="W89" s="3">
         <v>-200</v>
       </c>
       <c r="X89" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y89" s="3" t="s">
-        <v>3</v>
+        <v>-200</v>
+      </c>
+      <c r="Y89" s="3">
+        <v>0</v>
       </c>
       <c r="Z89" s="3" t="s">
         <v>3</v>
@@ -6787,8 +7004,11 @@
       <c r="AC89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6818,65 +7038,66 @@
       <c r="AA90" s="3"/>
       <c r="AB90" s="3"/>
       <c r="AC90" s="3"/>
-    </row>
-    <row r="91" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD90" s="3"/>
+    </row>
+    <row r="91" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-7000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-4900</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-13100</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-9800</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-6200</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-4000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-8100</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-11100</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-7200</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-2900</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-1300</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-7300</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-6400</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-5100</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-4200</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-3800</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-3100</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-4500</v>
       </c>
-      <c r="U91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V91" s="3" t="s">
         <v>3</v>
       </c>
@@ -6892,8 +7113,8 @@
       <c r="Z91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AA91" s="3">
-        <v>0</v>
+      <c r="AA91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AB91" s="3">
         <v>0</v>
@@ -6901,8 +7122,11 @@
       <c r="AC91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6984,8 +7208,11 @@
       <c r="AC92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7067,70 +7294,73 @@
       <c r="AC93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-7000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-4900</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-13100</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-9800</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-6300</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-4000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-8300</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-11100</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-7200</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-2900</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>1900</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-7300</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-6600</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-5100</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-3100</v>
-      </c>
-      <c r="R94" s="3">
-        <v>-4400</v>
       </c>
       <c r="S94" s="3">
         <v>-4400</v>
       </c>
       <c r="T94" s="3">
+        <v>-4400</v>
+      </c>
+      <c r="U94" s="3">
         <v>-11400</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>170100</v>
       </c>
-      <c r="V94" s="3">
-        <v>0</v>
-      </c>
-      <c r="W94" s="3" t="s">
-        <v>3</v>
+      <c r="W94" s="3">
+        <v>0</v>
       </c>
       <c r="X94" s="3" t="s">
         <v>3</v>
@@ -7144,14 +7374,17 @@
       <c r="AA94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AB94" s="3">
-        <v>0</v>
+      <c r="AB94" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AC94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7181,8 +7414,9 @@
       <c r="AA95" s="3"/>
       <c r="AB95" s="3"/>
       <c r="AC95" s="3"/>
-    </row>
-    <row r="96" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD95" s="3"/>
+    </row>
+    <row r="96" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7213,8 +7447,8 @@
       <c r="L96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="M96" s="3">
-        <v>0</v>
+      <c r="M96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N96" s="3">
         <v>0</v>
@@ -7264,8 +7498,11 @@
       <c r="AC96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7347,8 +7584,11 @@
       <c r="AC97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7430,8 +7670,11 @@
       <c r="AC98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7513,77 +7756,80 @@
       <c r="AC99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>144700</v>
+      </c>
+      <c r="E100" s="3">
         <v>42200</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>128500</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>27300</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>43900</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>6100</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>57300</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>78000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>60200</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>32500</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>16000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>112900</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>11800</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-1200</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-400</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>106200</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>17600</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-100</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-23300</v>
       </c>
-      <c r="V100" s="3">
-        <v>0</v>
-      </c>
       <c r="W100" s="3">
+        <v>0</v>
+      </c>
+      <c r="X100" s="3">
         <v>177500</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>100</v>
       </c>
-      <c r="Y100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z100" s="3" t="s">
         <v>3</v>
       </c>
@@ -7596,8 +7842,11 @@
       <c r="AC100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -7625,17 +7874,17 @@
       <c r="K101" s="3">
         <v>0</v>
       </c>
-      <c r="L101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="M101" s="3">
-        <v>0</v>
+      <c r="L101" s="3">
+        <v>0</v>
+      </c>
+      <c r="M101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="N101" s="3">
         <v>0</v>
       </c>
-      <c r="O101" s="3" t="s">
-        <v>3</v>
+      <c r="O101" s="3">
+        <v>0</v>
       </c>
       <c r="P101" s="3" t="s">
         <v>3</v>
@@ -7652,8 +7901,8 @@
       <c r="T101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="U101" s="3">
-        <v>0</v>
+      <c r="U101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="V101" s="3">
         <v>0</v>
@@ -7679,76 +7928,79 @@
       <c r="AC101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:30" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>71500</v>
+      </c>
+      <c r="E102" s="3">
         <v>8300</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>72700</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-26900</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>11300</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-38400</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>11600</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>34900</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>7900</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-900</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-19800</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>33500</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-39100</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-49100</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-39000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>70000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-26000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-21100</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>120700</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-200</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>500</v>
       </c>
-      <c r="X102" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y102" s="3" t="s">
-        <v>3</v>
+      <c r="Y102" s="3">
+        <v>0</v>
       </c>
       <c r="Z102" s="3" t="s">
         <v>3</v>
@@ -7760,6 +8012,9 @@
         <v>3</v>
       </c>
       <c r="AC102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AD102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/EOSE_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/EOSE_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="384" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="386" uniqueCount="92">
   <si>
     <t>EOSE</t>
   </si>
@@ -656,120 +656,120 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AE102"/>
+  <dimension ref="A5:AF102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="31" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="32" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:32" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E7" s="2">
         <v>45930</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45838</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45747</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45657</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45565</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45473</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45382</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45291</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45199</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45107</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45016</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44926</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44834</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44742</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44651</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44561</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44469</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44377</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44286</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44196</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44104</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44012</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43921</v>
       </c>
-      <c r="AA7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AB7" s="2" t="s">
         <v>3</v>
       </c>
@@ -782,73 +782,76 @@
       <c r="AE7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>58000</v>
+      </c>
+      <c r="E8" s="3">
         <v>30500</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>15200</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>10500</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>7300</v>
-      </c>
-      <c r="H8" s="3">
-        <v>900</v>
       </c>
       <c r="I8" s="3">
         <v>900</v>
       </c>
       <c r="J8" s="3">
-        <v>6600</v>
+        <v>900</v>
       </c>
       <c r="K8" s="3">
         <v>6600</v>
       </c>
       <c r="L8" s="3">
+        <v>6600</v>
+      </c>
+      <c r="M8" s="3">
         <v>700</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>200</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>8800</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>2700</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>6100</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>5900</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>3300</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>3100</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>700</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>600</v>
-      </c>
-      <c r="V8" s="3">
-        <v>200</v>
       </c>
       <c r="W8" s="3">
         <v>200</v>
       </c>
-      <c r="X8" s="3" t="s">
-        <v>3</v>
+      <c r="X8" s="3">
+        <v>200</v>
       </c>
       <c r="Y8" s="3" t="s">
         <v>3</v>
@@ -865,80 +868,83 @@
       <c r="AC8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AD8" s="3">
-        <v>0</v>
+      <c r="AD8" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AE8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>112400</v>
+      </c>
+      <c r="E9" s="3">
         <v>64400</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>46200</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>35000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>30800</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>25800</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>14100</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>28200</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>30400</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>21300</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>11200</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>26900</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>30800</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>50000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>36900</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>35600</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>21100</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>12900</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>12400</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>100</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>5500</v>
       </c>
-      <c r="X9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y9" s="3" t="s">
         <v>3</v>
       </c>
@@ -960,74 +966,77 @@
       <c r="AE9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>-54400</v>
+      </c>
+      <c r="E10" s="3">
         <v>-33900</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>-31000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>-24500</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>-23500</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>-24900</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>-13200</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>-21600</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>-23700</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>-20600</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>-11000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>-18100</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>-28100</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>-43900</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>-31000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>-32300</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>-18000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>-12200</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>-11800</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>100</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>-5300</v>
       </c>
-      <c r="X10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y10" s="3" t="s">
         <v>3</v>
       </c>
@@ -1049,8 +1058,11 @@
       <c r="AE10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1082,74 +1094,75 @@
       <c r="AC11" s="3"/>
       <c r="AD11" s="3"/>
       <c r="AE11" s="3"/>
-    </row>
-    <row r="12" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF11" s="3"/>
+    </row>
+    <row r="12" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>7600</v>
+      </c>
+      <c r="E12" s="3">
         <v>6900</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>7200</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>6800</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>5900</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>7400</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>4300</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>5200</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>5000</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>3200</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>5000</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>5400</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>3600</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>4500</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>5500</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>5000</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>5400</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>5100</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>3600</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>5000</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>14000</v>
       </c>
-      <c r="X12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y12" s="3" t="s">
         <v>3</v>
       </c>
@@ -1171,8 +1184,11 @@
       <c r="AE12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1260,73 +1276,76 @@
       <c r="AE13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>7700</v>
+        <v>600</v>
       </c>
       <c r="E14" s="3">
+        <v>7900</v>
+      </c>
+      <c r="F14" s="3">
         <v>17700</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>6500</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>-31500</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>6200</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>-68000</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>100</v>
       </c>
-      <c r="K14" s="3">
-        <v>0</v>
-      </c>
       <c r="L14" s="3">
+        <v>0</v>
+      </c>
+      <c r="M14" s="3">
         <v>1000</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>7300</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>2400</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>4300</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>1400</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>2000</v>
       </c>
-      <c r="R14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="S14" s="3">
-        <v>0</v>
+      <c r="S14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="T14" s="3">
+        <v>0</v>
+      </c>
+      <c r="U14" s="3">
         <v>-1300</v>
       </c>
-      <c r="U14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="V14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="W14" s="3">
-        <v>0</v>
-      </c>
-      <c r="X14" s="3" t="s">
-        <v>3</v>
+      <c r="W14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="X14" s="3">
+        <v>0</v>
       </c>
       <c r="Y14" s="3" t="s">
         <v>3</v>
@@ -1334,8 +1353,8 @@
       <c r="Z14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AA14" s="3">
-        <v>0</v>
+      <c r="AA14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AB14" s="3">
         <v>0</v>
@@ -1349,47 +1368,50 @@
       <c r="AE14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:32" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>5200</v>
+      </c>
+      <c r="E15" s="3">
         <v>3400</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>2900</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>2700</v>
-      </c>
-      <c r="G15" s="3">
-        <v>2600</v>
       </c>
       <c r="H15" s="3">
         <v>2700</v>
       </c>
       <c r="I15" s="3">
+        <v>2700</v>
+      </c>
+      <c r="J15" s="3">
         <v>1400</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>1200</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>2400</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>2200</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>2500</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>2700</v>
       </c>
-      <c r="O15" s="3">
-        <v>0</v>
-      </c>
       <c r="P15" s="3">
         <v>0</v>
       </c>
@@ -1438,8 +1460,11 @@
       <c r="AE15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:32" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1468,82 +1493,83 @@
       <c r="AC16" s="3"/>
       <c r="AD16" s="3"/>
       <c r="AE16" s="3"/>
-    </row>
-    <row r="17" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF16" s="3"/>
+    </row>
+    <row r="17" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>91100</v>
+        <v>142700</v>
       </c>
       <c r="E17" s="3">
+        <v>90900</v>
+      </c>
+      <c r="F17" s="3">
         <v>78900</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>62800</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>53300</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>51000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>29700</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>47700</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>48800</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>37600</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>29400</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>46300</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>51300</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>70600</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>63300</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>55000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>40700</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>25700</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>49800</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>21800</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>37200</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>2000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>100</v>
       </c>
-      <c r="Z17" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA17" s="3" t="s">
-        <v>3</v>
+      <c r="AA17" s="3">
+        <v>0</v>
       </c>
       <c r="AB17" s="3" t="s">
         <v>3</v>
@@ -1557,74 +1583,77 @@
       <c r="AE17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>-60600</v>
+        <v>-84700</v>
       </c>
       <c r="E18" s="3">
+        <v>-60400</v>
+      </c>
+      <c r="F18" s="3">
         <v>-63600</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-52400</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-46100</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-50100</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-28800</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-41100</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-42200</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-36900</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-29200</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-37500</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-48600</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-64500</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-57400</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-51700</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-37600</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-25000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-49200</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-21600</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-37000</v>
       </c>
-      <c r="X18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1646,8 +1675,11 @@
       <c r="AE18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1679,74 +1711,75 @@
       <c r="AC19" s="3"/>
       <c r="AD19" s="3"/>
       <c r="AE19" s="3"/>
-    </row>
-    <row r="20" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF19" s="3"/>
+    </row>
+    <row r="20" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>28500</v>
+      </c>
+      <c r="E20" s="3">
         <v>569000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>135000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-80000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>248300</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>281100</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>58900</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-3600</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-9600</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-62200</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>75500</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>13100</v>
-      </c>
-      <c r="O20" s="3">
-        <v>-400</v>
       </c>
       <c r="P20" s="3">
         <v>-400</v>
       </c>
       <c r="Q20" s="3">
+        <v>-400</v>
+      </c>
+      <c r="R20" s="3">
         <v>3600</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>8400</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>8300</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>10700</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-4700</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>200</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-5900</v>
       </c>
-      <c r="X20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y20" s="3" t="s">
         <v>3</v>
       </c>
@@ -1768,71 +1801,74 @@
       <c r="AE20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>-626300</v>
+        <v>-107900</v>
       </c>
       <c r="E21" s="3">
+        <v>-626100</v>
+      </c>
+      <c r="F21" s="3">
         <v>-195700</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>30200</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-291700</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-328600</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-86300</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-36300</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-30200</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>27500</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-102200</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-47900</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-46000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-63300</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-52500</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-42300</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-28500</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-13700</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-53300</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>-21000</v>
       </c>
-      <c r="W21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1857,74 +1893,77 @@
       <c r="AE21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>12000</v>
+      </c>
+      <c r="E22" s="3">
         <v>4800</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>6600</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>5900</v>
       </c>
-      <c r="G22" s="3">
-        <v>5200</v>
-      </c>
       <c r="H22" s="3">
+        <v>5900</v>
+      </c>
+      <c r="I22" s="3">
         <v>5400</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>8400</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>9100</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>8600</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>9400</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>19600</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>18600</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>7600</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>5700</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>2900</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>2500</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>1300</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>3700</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>200</v>
       </c>
-      <c r="V22" s="3">
-        <v>0</v>
-      </c>
       <c r="W22" s="3">
+        <v>0</v>
+      </c>
+      <c r="X22" s="3">
         <v>23800</v>
       </c>
-      <c r="X22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y22" s="3" t="s">
         <v>3</v>
       </c>
@@ -1940,88 +1979,91 @@
       <c r="AC22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AD22" s="3">
-        <v>0</v>
+      <c r="AD22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AE22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-120400</v>
+      </c>
+      <c r="E23" s="3">
         <v>-641400</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-222900</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>15100</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-268100</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-342900</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-28200</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-46700</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-41200</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>14900</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-131600</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-71600</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-56600</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-70600</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-56700</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-45800</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-30600</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-18100</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-54000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-21500</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-66700</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-2000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-100</v>
       </c>
-      <c r="Z23" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA23" s="3" t="s">
-        <v>3</v>
+      <c r="AA23" s="3">
+        <v>0</v>
       </c>
       <c r="AB23" s="3" t="s">
         <v>3</v>
@@ -2035,8 +2077,11 @@
       <c r="AE23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -2077,16 +2122,16 @@
         <v>0</v>
       </c>
       <c r="P24" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q24" s="3">
         <v>100</v>
       </c>
-      <c r="Q24" s="3">
-        <v>0</v>
-      </c>
       <c r="R24" s="3">
         <v>0</v>
       </c>
-      <c r="S24" s="3" t="s">
-        <v>3</v>
+      <c r="S24" s="3">
+        <v>0</v>
       </c>
       <c r="T24" s="3" t="s">
         <v>3</v>
@@ -2103,8 +2148,8 @@
       <c r="X24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Y24" s="3">
-        <v>0</v>
+      <c r="Y24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Z24" s="3">
         <v>0</v>
@@ -2124,8 +2169,11 @@
       <c r="AE24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2213,82 +2261,85 @@
       <c r="AE25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-120500</v>
+      </c>
+      <c r="E26" s="3">
         <v>-641400</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-222900</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>15100</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-268100</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-342900</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-28200</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-46700</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-41200</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>14900</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-131600</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-71600</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-56600</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-70700</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-56700</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-45800</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-30600</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-18100</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-54000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-21500</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-66700</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-2000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-100</v>
       </c>
-      <c r="Z26" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA26" s="3" t="s">
-        <v>3</v>
+      <c r="AA26" s="3">
+        <v>0</v>
       </c>
       <c r="AB26" s="3" t="s">
         <v>3</v>
@@ -2302,82 +2353,85 @@
       <c r="AE26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-258600</v>
+      </c>
+      <c r="E27" s="3">
         <v>-1332500</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-248800</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>95100</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-481500</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-384100</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-51800</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-46700</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-41200</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>14900</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-131600</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-71600</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-56600</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-70700</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-56700</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-45800</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-30600</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-18100</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-54000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-21500</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-66700</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-2000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-100</v>
       </c>
-      <c r="Z27" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA27" s="3" t="s">
-        <v>3</v>
+      <c r="AA27" s="3">
+        <v>0</v>
       </c>
       <c r="AB27" s="3" t="s">
         <v>3</v>
@@ -2391,8 +2445,11 @@
       <c r="AE27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2480,8 +2537,11 @@
       <c r="AE28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2569,8 +2629,11 @@
       <c r="AE29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2658,8 +2721,11 @@
       <c r="AE30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2747,74 +2813,77 @@
       <c r="AE31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-28500</v>
+      </c>
+      <c r="E32" s="3">
         <v>-569000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-135000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>80000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-248300</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-281100</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-58900</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>3600</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>9600</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>62200</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-75500</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-13100</v>
-      </c>
-      <c r="O32" s="3">
-        <v>400</v>
       </c>
       <c r="P32" s="3">
         <v>400</v>
       </c>
       <c r="Q32" s="3">
+        <v>400</v>
+      </c>
+      <c r="R32" s="3">
         <v>-3600</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-8400</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-8300</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-10700</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>4700</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-200</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>5900</v>
       </c>
-      <c r="X32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y32" s="3" t="s">
         <v>3</v>
       </c>
@@ -2836,82 +2905,85 @@
       <c r="AE32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-120500</v>
+      </c>
+      <c r="E33" s="3">
         <v>-641400</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-222900</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>15100</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-268100</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-342900</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-28200</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-46700</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-41200</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>14900</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-131600</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-71600</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-56600</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-70700</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-56700</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-45800</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-30600</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-18100</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-54000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-21500</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-66700</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-2000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-100</v>
       </c>
-      <c r="Z33" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA33" s="3" t="s">
-        <v>3</v>
+      <c r="AA33" s="3">
+        <v>0</v>
       </c>
       <c r="AB33" s="3" t="s">
         <v>3</v>
@@ -2925,8 +2997,11 @@
       <c r="AE33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3014,82 +3089,85 @@
       <c r="AE34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-120500</v>
+      </c>
+      <c r="E35" s="3">
         <v>-641400</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-222900</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>15100</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-268100</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-342900</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-28200</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-46700</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-41200</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>14900</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-131600</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-71600</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-56600</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-70700</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-56700</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-45800</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-30600</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-18100</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-54000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-21500</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-66700</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-2000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-100</v>
       </c>
-      <c r="Z35" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA35" s="3" t="s">
-        <v>3</v>
+      <c r="AA35" s="3">
+        <v>0</v>
       </c>
       <c r="AB35" s="3" t="s">
         <v>3</v>
@@ -3103,88 +3181,91 @@
       <c r="AE35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:32" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E38" s="2">
         <v>45930</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45838</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45747</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45657</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45565</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45473</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45382</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45291</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45199</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45107</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45016</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44926</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44834</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44742</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44651</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44561</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44469</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44377</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44286</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44196</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44104</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44012</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43921</v>
       </c>
-      <c r="AA38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AB38" s="2" t="s">
         <v>3</v>
       </c>
@@ -3197,8 +3278,11 @@
       <c r="AE38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3230,8 +3314,9 @@
       <c r="AC39" s="3"/>
       <c r="AD39" s="3"/>
       <c r="AE39" s="3"/>
-    </row>
-    <row r="40" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF39" s="3"/>
+    </row>
+    <row r="40" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3263,82 +3348,83 @@
       <c r="AC40" s="3"/>
       <c r="AD40" s="3"/>
       <c r="AE40" s="3"/>
-    </row>
-    <row r="41" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF40" s="3"/>
+    </row>
+    <row r="41" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>568000</v>
+      </c>
+      <c r="E41" s="3">
         <v>58700</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>120200</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>82600</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>74300</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>23000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>52500</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>31800</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>69500</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>58000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>23200</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>16100</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>17100</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>38400</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>16300</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>55400</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>104800</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>144200</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>74700</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>100700</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>121900</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>300</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>500</v>
       </c>
-      <c r="Z41" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA41" s="3" t="s">
-        <v>3</v>
+      <c r="AA41" s="3">
+        <v>0</v>
       </c>
       <c r="AB41" s="3" t="s">
         <v>3</v>
@@ -3352,8 +3438,11 @@
       <c r="AE41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3441,82 +3530,85 @@
       <c r="AE42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>31800</v>
+      </c>
+      <c r="E43" s="3">
         <v>29000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>24400</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>24300</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>40100</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>82600</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>100800</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>27300</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>20500</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>4300</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>3900</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>7800</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>3600</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>6400</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>3600</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>3700</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>2000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>2400</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>400</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>300</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>100</v>
       </c>
-      <c r="X43" s="3">
-        <v>0</v>
-      </c>
       <c r="Y43" s="3">
         <v>0</v>
       </c>
       <c r="Z43" s="3">
         <v>0</v>
       </c>
-      <c r="AA43" s="3" t="s">
-        <v>3</v>
+      <c r="AA43" s="3">
+        <v>0</v>
       </c>
       <c r="AB43" s="3" t="s">
         <v>3</v>
@@ -3530,74 +3622,77 @@
       <c r="AE43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>59000</v>
+      </c>
+      <c r="E44" s="3">
         <v>47600</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>41100</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>40300</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>32800</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>25900</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>17800</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>14400</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>17100</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>20600</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>16600</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>14100</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>23300</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>23200</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>12900</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>10300</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>13000</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>5000</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>4400</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>100</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>200</v>
       </c>
-      <c r="X44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y44" s="3" t="s">
         <v>3</v>
       </c>
@@ -3613,86 +3708,89 @@
       <c r="AC44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AD44" s="3">
-        <v>0</v>
+      <c r="AD44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AE44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>12300</v>
+      </c>
+      <c r="E45" s="3">
         <v>14100</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>12600</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>22900</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>17600</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>13900</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>8600</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>9600</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>10700</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>21400</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>15500</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>7400</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>11300</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>13600</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>27600</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>26800</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>22700</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>17400</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>12200</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>6200</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>5200</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>200</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>300</v>
       </c>
-      <c r="Z45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AA45" s="3" t="s">
         <v>3</v>
       </c>
@@ -3708,82 +3806,85 @@
       <c r="AE45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>708500</v>
+      </c>
+      <c r="E46" s="3">
         <v>188700</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>232300</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>185500</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>179900</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>149200</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>183500</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>87000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>122300</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>108500</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>64000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>50000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>55100</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>81600</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>60500</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>96200</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>142600</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>169100</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>91700</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>107400</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>127400</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>600</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>800</v>
       </c>
-      <c r="Z46" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA46" s="3" t="s">
-        <v>3</v>
+      <c r="AA46" s="3">
+        <v>0</v>
       </c>
       <c r="AB46" s="3" t="s">
         <v>3</v>
@@ -3797,8 +3898,11 @@
       <c r="AE46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3835,36 +3939,36 @@
       <c r="N47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O47" s="3">
+      <c r="O47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P47" s="3">
         <v>800</v>
-      </c>
-      <c r="P47" s="3">
-        <v>3700</v>
       </c>
       <c r="Q47" s="3">
         <v>3700</v>
       </c>
       <c r="R47" s="3">
-        <v>3500</v>
+        <v>3700</v>
       </c>
       <c r="S47" s="3">
         <v>3500</v>
       </c>
       <c r="T47" s="3">
+        <v>3500</v>
+      </c>
+      <c r="U47" s="3">
         <v>4700</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>4100</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>11100</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>3700</v>
       </c>
-      <c r="X47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y47" s="3" t="s">
         <v>3</v>
       </c>
@@ -3880,80 +3984,83 @@
       <c r="AC47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AD47" s="3">
-        <v>0</v>
+      <c r="AD47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AE47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>134800</v>
+      </c>
+      <c r="E48" s="3">
         <v>88300</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>78200</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>46500</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>48600</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>54600</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>54000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>46500</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>41900</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>24300</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>23900</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>28700</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>31500</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>34400</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>25800</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>19500</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>16400</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>10300</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>8400</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>8000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>5700</v>
       </c>
-      <c r="X48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y48" s="3" t="s">
         <v>3</v>
       </c>
@@ -3969,28 +4076,31 @@
       <c r="AC48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AD48" s="3">
-        <v>0</v>
+      <c r="AD48" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AE48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>5300</v>
+      </c>
+      <c r="E49" s="3">
         <v>5400</v>
-      </c>
-      <c r="E49" s="3">
-        <v>4500</v>
       </c>
       <c r="F49" s="3">
         <v>4500</v>
       </c>
       <c r="G49" s="3">
-        <v>4600</v>
+        <v>4500</v>
       </c>
       <c r="H49" s="3">
         <v>4600</v>
@@ -4008,13 +4118,13 @@
         <v>4600</v>
       </c>
       <c r="M49" s="3">
-        <v>4700</v>
+        <v>4600</v>
       </c>
       <c r="N49" s="3">
         <v>4700</v>
       </c>
       <c r="O49" s="3">
-        <v>4600</v>
+        <v>4700</v>
       </c>
       <c r="P49" s="3">
         <v>4600</v>
@@ -4035,13 +4145,13 @@
         <v>4600</v>
       </c>
       <c r="V49" s="3">
-        <v>300</v>
+        <v>4600</v>
       </c>
       <c r="W49" s="3">
         <v>300</v>
       </c>
-      <c r="X49" s="3" t="s">
-        <v>3</v>
+      <c r="X49" s="3">
+        <v>300</v>
       </c>
       <c r="Y49" s="3" t="s">
         <v>3</v>
@@ -4058,14 +4168,17 @@
       <c r="AC49" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AD49" s="3">
-        <v>0</v>
+      <c r="AD49" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AE49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4153,8 +4266,11 @@
       <c r="AE50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4242,83 +4358,86 @@
       <c r="AE51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>35100</v>
+      </c>
+      <c r="E52" s="3">
         <v>45700</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>46000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>26700</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>26300</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>7300</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>4900</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>17600</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>15700</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>15900</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>15600</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>15500</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>14800</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>14200</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>3200</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>3100</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>2100</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>1400</v>
-      </c>
-      <c r="U52" s="3">
-        <v>1000</v>
       </c>
       <c r="V52" s="3">
         <v>1000</v>
       </c>
       <c r="W52" s="3">
+        <v>1000</v>
+      </c>
+      <c r="X52" s="3">
         <v>1200</v>
-      </c>
-      <c r="X52" s="3">
-        <v>176800</v>
       </c>
       <c r="Y52" s="3">
         <v>176800</v>
       </c>
       <c r="Z52" s="3">
+        <v>176800</v>
+      </c>
+      <c r="AA52" s="3">
         <v>100</v>
       </c>
-      <c r="AA52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB52" s="3" t="s">
         <v>3</v>
       </c>
@@ -4331,8 +4450,11 @@
       <c r="AE52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4420,83 +4542,86 @@
       <c r="AE53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>885200</v>
+      </c>
+      <c r="E54" s="3">
         <v>328200</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>361000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>263300</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>260300</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>216800</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>248800</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>155700</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>186500</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>154100</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>109000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>99700</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>106800</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>138500</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>97700</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>126900</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>169200</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>190100</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>109900</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>127800</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>138300</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>177300</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>177500</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>100</v>
       </c>
-      <c r="AA54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB54" s="3" t="s">
         <v>3</v>
       </c>
@@ -4509,8 +4634,11 @@
       <c r="AE54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4542,8 +4670,9 @@
       <c r="AC55" s="3"/>
       <c r="AD55" s="3"/>
       <c r="AE55" s="3"/>
-    </row>
-    <row r="56" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF55" s="3"/>
+    </row>
+    <row r="56" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4575,82 +4704,83 @@
       <c r="AC56" s="3"/>
       <c r="AD56" s="3"/>
       <c r="AE56" s="3"/>
-    </row>
-    <row r="57" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF56" s="3"/>
+    </row>
+    <row r="57" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>99900</v>
+      </c>
+      <c r="E57" s="3">
         <v>51600</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>39700</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>24300</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>16700</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>24300</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>24100</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>18300</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>20500</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>13800</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>15400</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>32500</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>34700</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>35500</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>29100</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>11700</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>13700</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>13200</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>15200</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>20200</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>11400</v>
       </c>
-      <c r="X57" s="3">
-        <v>0</v>
-      </c>
       <c r="Y57" s="3">
         <v>0</v>
       </c>
       <c r="Z57" s="3">
         <v>0</v>
       </c>
-      <c r="AA57" s="3" t="s">
-        <v>3</v>
+      <c r="AA57" s="3">
+        <v>0</v>
       </c>
       <c r="AB57" s="3" t="s">
         <v>3</v>
@@ -4664,83 +4794,86 @@
       <c r="AE57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>2400</v>
+      </c>
+      <c r="E58" s="3">
         <v>2900</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>3300</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>3400</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>3900</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>4300</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>5500</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>5100</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>4900</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>4600</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>4400</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>12400</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>5600</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>2900</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>14000</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>6700</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>6600</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>6500</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>6100</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>1200</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>1100</v>
       </c>
-      <c r="X58" s="3">
-        <v>0</v>
-      </c>
       <c r="Y58" s="3">
         <v>0</v>
       </c>
       <c r="Z58" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA58" s="3">
         <v>100</v>
       </c>
-      <c r="AA58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB58" s="3" t="s">
         <v>3</v>
       </c>
@@ -4753,79 +4886,82 @@
       <c r="AE58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>31000</v>
+      </c>
+      <c r="E59" s="3">
         <v>28700</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>47300</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>50500</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>32100</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>17100</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>13500</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>11500</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>12600</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>13000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>9000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>6300</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>20300</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>17500</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>16600</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>15500</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>9600</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>1200</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>3400</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>800</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>1700</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>1800</v>
       </c>
-      <c r="Y59" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z59" s="3" t="s">
-        <v>3</v>
+      <c r="Z59" s="3">
+        <v>0</v>
       </c>
       <c r="AA59" s="3" t="s">
         <v>3</v>
@@ -4842,82 +4978,85 @@
       <c r="AE59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>143500</v>
+      </c>
+      <c r="E60" s="3">
         <v>103400</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>104300</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>90700</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>65000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>75100</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>68500</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>64900</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>60900</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>46800</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>43000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>65700</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>60600</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>55800</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>59600</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>33800</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>29900</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>20900</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>24600</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>22200</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>14100</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>1900</v>
-      </c>
-      <c r="Y60" s="3">
-        <v>100</v>
       </c>
       <c r="Z60" s="3">
         <v>100</v>
       </c>
-      <c r="AA60" s="3" t="s">
-        <v>3</v>
+      <c r="AA60" s="3">
+        <v>100</v>
       </c>
       <c r="AB60" s="3" t="s">
         <v>3</v>
@@ -4931,74 +5070,77 @@
       <c r="AE60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>832300</v>
+      </c>
+      <c r="E61" s="3">
         <v>448100</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>445100</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>325200</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>316600</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>186900</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>152700</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>205100</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>204000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>207500</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>233300</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>202400</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>170400</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>160800</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>90300</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>95300</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>102700</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>106800</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>13500</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>100</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>300</v>
       </c>
-      <c r="X61" s="3">
-        <v>0</v>
-      </c>
       <c r="Y61" s="3">
         <v>0</v>
       </c>
@@ -5020,74 +5162,77 @@
       <c r="AE61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>784200</v>
+      </c>
+      <c r="E62" s="3">
         <v>871300</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>380300</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>274900</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>456200</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>369200</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>173900</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>29100</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>28900</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>27100</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>61200</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>6300</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>8500</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>10100</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>5700</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>8000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>4200</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>3900</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>3100</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>3700</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>800</v>
       </c>
-      <c r="X62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y62" s="3" t="s">
         <v>3</v>
       </c>
@@ -5103,14 +5248,17 @@
       <c r="AC62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AD62" s="3">
-        <v>0</v>
+      <c r="AD62" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AE62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5198,8 +5346,11 @@
       <c r="AE63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5287,8 +5438,11 @@
       <c r="AE64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5376,82 +5530,85 @@
       <c r="AE65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>1762500</v>
+      </c>
+      <c r="E66" s="3">
         <v>1425200</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>931700</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>694600</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>842100</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>634500</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>399500</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>303400</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>297300</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>282400</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>338500</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>275300</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>239500</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>226800</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>155600</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>137100</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>136700</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>131700</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>41300</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>26000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>15200</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>1900</v>
-      </c>
-      <c r="Y66" s="3">
-        <v>100</v>
       </c>
       <c r="Z66" s="3">
         <v>100</v>
       </c>
-      <c r="AA66" s="3" t="s">
-        <v>3</v>
+      <c r="AA66" s="3">
+        <v>100</v>
       </c>
       <c r="AB66" s="3" t="s">
         <v>3</v>
@@ -5465,8 +5622,11 @@
       <c r="AE66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5498,8 +5658,9 @@
       <c r="AC67" s="3"/>
       <c r="AD67" s="3"/>
       <c r="AE67" s="3"/>
-    </row>
-    <row r="68" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF67" s="3"/>
+    </row>
+    <row r="68" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5587,8 +5748,11 @@
       <c r="AE68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5676,32 +5840,35 @@
       <c r="AE69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
       <c r="D70" s="3">
+        <v>1361500</v>
+      </c>
+      <c r="E70" s="3">
         <v>1223400</v>
       </c>
-      <c r="E70" s="3">
+      <c r="F70" s="3">
         <v>532300</v>
       </c>
-      <c r="F70" s="3">
+      <c r="G70" s="3">
         <v>510900</v>
       </c>
-      <c r="G70" s="3">
+      <c r="H70" s="3">
         <v>488700</v>
       </c>
-      <c r="H70" s="3">
+      <c r="I70" s="3">
         <v>156100</v>
       </c>
-      <c r="I70" s="3">
+      <c r="J70" s="3">
         <v>40100</v>
       </c>
-      <c r="J70" s="3">
-        <v>0</v>
-      </c>
       <c r="K70" s="3">
         <v>0</v>
       </c>
@@ -5765,8 +5932,11 @@
       <c r="AE70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5854,82 +6024,85 @@
       <c r="AE71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-2535800</v>
+      </c>
+      <c r="E72" s="3">
         <v>-2415400</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-1774000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-1546600</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-1561700</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-1293600</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-950700</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-922600</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-875800</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-834600</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-849600</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-717900</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-646300</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-589700</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-519000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-462300</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-416500</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-385900</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-367800</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-313800</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-290800</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-2000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-100</v>
       </c>
-      <c r="Z72" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA72" s="3" t="s">
-        <v>3</v>
+      <c r="AA72" s="3">
+        <v>0</v>
       </c>
       <c r="AB72" s="3" t="s">
         <v>3</v>
@@ -5943,8 +6116,11 @@
       <c r="AE72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6032,8 +6208,11 @@
       <c r="AE73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6121,8 +6300,11 @@
       <c r="AE74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6210,82 +6392,85 @@
       <c r="AE75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>-2238900</v>
+      </c>
+      <c r="E76" s="3">
         <v>-2320400</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>-1103000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>-942200</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>-1070500</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>-573800</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>-190800</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>-147700</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>-110800</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>-128300</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>-229500</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>-175600</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>-132700</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>-88300</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>-57800</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>-10200</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>32400</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>58400</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>68600</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>101800</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>123100</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>175500</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>177400</v>
       </c>
-      <c r="Z76" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA76" s="3" t="s">
-        <v>3</v>
+      <c r="AA76" s="3">
+        <v>0</v>
       </c>
       <c r="AB76" s="3" t="s">
         <v>3</v>
@@ -6299,8 +6484,11 @@
       <c r="AE76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6388,88 +6576,91 @@
       <c r="AE77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:31" x14ac:dyDescent="0.2">
+      <c r="AF77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:32" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:31" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:32" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E80" s="2">
         <v>45930</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45838</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45747</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45657</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45565</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45473</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45382</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45291</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45199</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45107</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45016</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44926</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44834</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44742</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44651</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44561</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44469</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44377</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44286</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44196</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44104</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44012</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43921</v>
       </c>
-      <c r="AA80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AB80" s="2" t="s">
         <v>3</v>
       </c>
@@ -6482,82 +6673,85 @@
       <c r="AE80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-120500</v>
+      </c>
+      <c r="E81" s="3">
         <v>-641400</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-222900</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>15100</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-268100</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-342900</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-28200</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-46700</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-41200</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>14900</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-131600</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-71600</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-56600</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-70700</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-56700</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-45800</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-30600</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-18100</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-54000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-21500</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-66700</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-2000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-100</v>
       </c>
-      <c r="Z81" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA81" s="3" t="s">
-        <v>3</v>
+      <c r="AA81" s="3">
+        <v>0</v>
       </c>
       <c r="AB81" s="3" t="s">
         <v>3</v>
@@ -6571,8 +6765,11 @@
       <c r="AE81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6604,71 +6801,72 @@
       <c r="AC82" s="3"/>
       <c r="AD82" s="3"/>
       <c r="AE82" s="3"/>
-    </row>
-    <row r="83" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF82" s="3"/>
+    </row>
+    <row r="83" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>2900</v>
+      </c>
+      <c r="E83" s="3">
         <v>3000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>1700</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>1500</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>2700</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>2400</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>2700</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>2900</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>3200</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>1800</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>1500</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>1200</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>3000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>1600</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>1300</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>1000</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>800</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>700</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>600</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>500</v>
       </c>
-      <c r="W83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X83" s="3" t="s">
         <v>3</v>
       </c>
@@ -6684,8 +6882,8 @@
       <c r="AB83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AC83" s="3">
-        <v>0</v>
+      <c r="AC83" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AD83" s="3">
         <v>0</v>
@@ -6693,8 +6891,11 @@
       <c r="AE83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6782,8 +6983,11 @@
       <c r="AE84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6871,8 +7075,11 @@
       <c r="AE85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6960,8 +7167,11 @@
       <c r="AE86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7049,8 +7259,11 @@
       <c r="AE87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7138,82 +7351,85 @@
       <c r="AE88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-50300</v>
+      </c>
+      <c r="E89" s="3">
         <v>-65900</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-66100</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-28900</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-42700</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-44400</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-26300</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-40500</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-37400</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-32000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-45100</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-30500</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-37700</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-72100</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-44300</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-42700</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-35500</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-31700</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-39200</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-9700</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-26100</v>
-      </c>
-      <c r="X89" s="3">
-        <v>-200</v>
       </c>
       <c r="Y89" s="3">
         <v>-200</v>
       </c>
       <c r="Z89" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA89" s="3" t="s">
-        <v>3</v>
+        <v>-200</v>
+      </c>
+      <c r="AA89" s="3">
+        <v>0</v>
       </c>
       <c r="AB89" s="3" t="s">
         <v>3</v>
@@ -7227,8 +7443,11 @@
       <c r="AE89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7260,71 +7479,72 @@
       <c r="AC90" s="3"/>
       <c r="AD90" s="3"/>
       <c r="AE90" s="3"/>
-    </row>
-    <row r="91" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF90" s="3"/>
+    </row>
+    <row r="91" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-25000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-16800</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-7000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-4900</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-13100</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-9800</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-6200</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-4000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-8100</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-11100</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-7200</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-2900</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-1300</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-7300</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-6400</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-5100</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-4200</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-3800</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-3100</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-4500</v>
       </c>
-      <c r="W91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="X91" s="3" t="s">
         <v>3</v>
       </c>
@@ -7340,8 +7560,8 @@
       <c r="AB91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AC91" s="3">
-        <v>0</v>
+      <c r="AC91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AD91" s="3">
         <v>0</v>
@@ -7349,8 +7569,11 @@
       <c r="AE91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7438,8 +7661,11 @@
       <c r="AE92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7527,76 +7753,79 @@
       <c r="AE93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-25000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-17800</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-7000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-4900</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-13100</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-9800</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-6300</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-4000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-8300</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-11100</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-7200</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-2900</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>1900</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-7300</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-6600</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-5100</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-3100</v>
-      </c>
-      <c r="T94" s="3">
-        <v>-4400</v>
       </c>
       <c r="U94" s="3">
         <v>-4400</v>
       </c>
       <c r="V94" s="3">
+        <v>-4400</v>
+      </c>
+      <c r="W94" s="3">
         <v>-11400</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>170100</v>
       </c>
-      <c r="X94" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y94" s="3" t="s">
-        <v>3</v>
+      <c r="Y94" s="3">
+        <v>0</v>
       </c>
       <c r="Z94" s="3" t="s">
         <v>3</v>
@@ -7610,14 +7839,17 @@
       <c r="AC94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AD94" s="3">
-        <v>0</v>
+      <c r="AD94" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AE94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7649,8 +7881,9 @@
       <c r="AC95" s="3"/>
       <c r="AD95" s="3"/>
       <c r="AE95" s="3"/>
-    </row>
-    <row r="96" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF95" s="3"/>
+    </row>
+    <row r="96" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7687,8 +7920,8 @@
       <c r="N96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O96" s="3">
-        <v>0</v>
+      <c r="O96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P96" s="3">
         <v>0</v>
@@ -7738,8 +7971,11 @@
       <c r="AE96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7827,8 +8063,11 @@
       <c r="AE97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7916,8 +8155,11 @@
       <c r="AE98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8005,83 +8247,86 @@
       <c r="AE99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>573000</v>
+      </c>
+      <c r="E100" s="3">
         <v>27300</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>144700</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>42200</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>128500</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>27300</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>43900</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>6100</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>57300</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>78000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>60200</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>32500</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>16000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>112900</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>11800</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-1200</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-400</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>106200</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>17600</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-100</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-23300</v>
       </c>
-      <c r="X100" s="3">
-        <v>0</v>
-      </c>
       <c r="Y100" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z100" s="3">
         <v>177500</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>100</v>
       </c>
-      <c r="AA100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB100" s="3" t="s">
         <v>3</v>
       </c>
@@ -8094,8 +8339,11 @@
       <c r="AE100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -8129,17 +8377,17 @@
       <c r="M101" s="3">
         <v>0</v>
       </c>
-      <c r="N101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="O101" s="3">
-        <v>0</v>
+      <c r="N101" s="3">
+        <v>0</v>
+      </c>
+      <c r="O101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P101" s="3">
         <v>0</v>
       </c>
-      <c r="Q101" s="3" t="s">
-        <v>3</v>
+      <c r="Q101" s="3">
+        <v>0</v>
       </c>
       <c r="R101" s="3" t="s">
         <v>3</v>
@@ -8156,8 +8404,8 @@
       <c r="V101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="W101" s="3">
-        <v>0</v>
+      <c r="W101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="X101" s="3">
         <v>0</v>
@@ -8183,82 +8431,85 @@
       <c r="AE101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:31" x14ac:dyDescent="0.2">
+      <c r="AF101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:32" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>497800</v>
+      </c>
+      <c r="E102" s="3">
         <v>-56400</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>71500</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>8300</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>72700</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-26900</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>11300</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-38400</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>11600</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>34900</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>7900</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-900</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-19800</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>33500</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-39100</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-49100</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-39000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>70000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-26000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-21100</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>120700</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-200</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>500</v>
       </c>
-      <c r="Z102" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA102" s="3" t="s">
-        <v>3</v>
+      <c r="AA102" s="3">
+        <v>0</v>
       </c>
       <c r="AB102" s="3" t="s">
         <v>3</v>
@@ -8270,6 +8521,9 @@
         <v>3</v>
       </c>
       <c r="AE102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AF102" s="3" t="s">
         <v>3</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/EOSE_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/EOSE_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="386" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="388" uniqueCount="92">
   <si>
     <t>EOSE</t>
   </si>
@@ -656,123 +656,124 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AF102"/>
+  <dimension ref="A5:AG102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="32" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="33" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E7" s="2">
         <v>46022</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45930</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45838</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45747</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45657</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45565</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45473</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45382</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45291</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45199</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45107</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45016</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44926</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44834</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44742</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44651</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44561</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44469</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44377</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44286</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44196</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44104</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>44012</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43921</v>
       </c>
-      <c r="AB7" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AC7" s="2" t="s">
         <v>3</v>
       </c>
@@ -785,76 +786,79 @@
       <c r="AF7" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="8" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG7" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>57000</v>
+      </c>
+      <c r="E8" s="3">
         <v>58000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>30500</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>15200</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>10500</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>7300</v>
-      </c>
-      <c r="I8" s="3">
-        <v>900</v>
       </c>
       <c r="J8" s="3">
         <v>900</v>
       </c>
       <c r="K8" s="3">
-        <v>6600</v>
+        <v>900</v>
       </c>
       <c r="L8" s="3">
         <v>6600</v>
       </c>
       <c r="M8" s="3">
+        <v>6600</v>
+      </c>
+      <c r="N8" s="3">
         <v>700</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>200</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>8800</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>2700</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>6100</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>5900</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>3300</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>3100</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>700</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>600</v>
-      </c>
-      <c r="W8" s="3">
-        <v>200</v>
       </c>
       <c r="X8" s="3">
         <v>200</v>
       </c>
-      <c r="Y8" s="3" t="s">
-        <v>3</v>
+      <c r="Y8" s="3">
+        <v>200</v>
       </c>
       <c r="Z8" s="3" t="s">
         <v>3</v>
@@ -871,83 +875,86 @@
       <c r="AD8" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AE8" s="3">
-        <v>0</v>
+      <c r="AE8" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AF8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>101400</v>
+      </c>
+      <c r="E9" s="3">
         <v>112400</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>64400</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>46200</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>35000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>30800</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>25800</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>14100</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>28200</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>30400</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>21300</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>11200</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>26900</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>30800</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>50000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>36900</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>35600</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>21100</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>12900</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>12400</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>100</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>5500</v>
       </c>
-      <c r="Y9" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z9" s="3" t="s">
         <v>3</v>
       </c>
@@ -969,77 +976,80 @@
       <c r="AF9" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="10" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG9" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>-44400</v>
+      </c>
+      <c r="E10" s="3">
         <v>-54400</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>-33900</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>-31000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>-24500</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>-23500</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>-24900</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>-13200</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>-21600</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>-23700</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>-20600</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>-11000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>-18100</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>-28100</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>-43900</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>-31000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>-32300</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>-18000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>-12200</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>-11800</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>100</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>-5300</v>
       </c>
-      <c r="Y10" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z10" s="3" t="s">
         <v>3</v>
       </c>
@@ -1061,8 +1071,11 @@
       <c r="AF10" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG10" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -1095,77 +1108,78 @@
       <c r="AD11" s="3"/>
       <c r="AE11" s="3"/>
       <c r="AF11" s="3"/>
-    </row>
-    <row r="12" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG11" s="3"/>
+    </row>
+    <row r="12" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>10700</v>
+      </c>
+      <c r="E12" s="3">
         <v>7600</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>6900</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>7200</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>6800</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>5900</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>7400</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>4300</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>5200</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>5000</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>3200</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>5000</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>5400</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>3600</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>4500</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>5500</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>5000</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>5400</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>5100</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>3600</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>5000</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>14000</v>
       </c>
-      <c r="Y12" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z12" s="3" t="s">
         <v>3</v>
       </c>
@@ -1187,8 +1201,11 @@
       <c r="AF12" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG12" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1279,76 +1296,79 @@
       <c r="AF13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>4300</v>
+      </c>
+      <c r="E14" s="3">
         <v>600</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>7900</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>17700</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>6500</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>-31500</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>6200</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>-68000</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>100</v>
       </c>
-      <c r="L14" s="3">
-        <v>0</v>
-      </c>
       <c r="M14" s="3">
+        <v>0</v>
+      </c>
+      <c r="N14" s="3">
         <v>1000</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>7300</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>2400</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>4300</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>1400</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>2000</v>
       </c>
-      <c r="S14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="T14" s="3">
-        <v>0</v>
+      <c r="T14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="U14" s="3">
+        <v>0</v>
+      </c>
+      <c r="V14" s="3">
         <v>-1300</v>
       </c>
-      <c r="V14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="W14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="X14" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y14" s="3" t="s">
-        <v>3</v>
+      <c r="X14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y14" s="3">
+        <v>0</v>
       </c>
       <c r="Z14" s="3" t="s">
         <v>3</v>
@@ -1356,8 +1376,8 @@
       <c r="AA14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AB14" s="3">
-        <v>0</v>
+      <c r="AB14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AC14" s="3">
         <v>0</v>
@@ -1371,22 +1391,25 @@
       <c r="AF14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>5400</v>
+      </c>
+      <c r="E15" s="3">
         <v>5200</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>3400</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>2900</v>
-      </c>
-      <c r="G15" s="3">
-        <v>2700</v>
       </c>
       <c r="H15" s="3">
         <v>2700</v>
@@ -1395,26 +1418,26 @@
         <v>2700</v>
       </c>
       <c r="J15" s="3">
+        <v>2700</v>
+      </c>
+      <c r="K15" s="3">
         <v>1400</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>1200</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>2400</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>2200</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>2500</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>2700</v>
       </c>
-      <c r="P15" s="3">
-        <v>0</v>
-      </c>
       <c r="Q15" s="3">
         <v>0</v>
       </c>
@@ -1463,8 +1486,11 @@
       <c r="AF15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:33" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1494,85 +1520,86 @@
       <c r="AD16" s="3"/>
       <c r="AE16" s="3"/>
       <c r="AF16" s="3"/>
-    </row>
-    <row r="17" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG16" s="3"/>
+    </row>
+    <row r="17" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>136200</v>
+      </c>
+      <c r="E17" s="3">
         <v>142700</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>90900</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>78900</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>62800</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>53300</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>51000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>29700</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>47700</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>48800</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>37600</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>29400</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>46300</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>51300</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>70600</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>63300</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>55000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>40700</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>25700</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>49800</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>21800</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>37200</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>2000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>100</v>
       </c>
-      <c r="AA17" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB17" s="3" t="s">
-        <v>3</v>
+      <c r="AB17" s="3">
+        <v>0</v>
       </c>
       <c r="AC17" s="3" t="s">
         <v>3</v>
@@ -1586,77 +1613,80 @@
       <c r="AF17" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG17" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-79200</v>
+      </c>
+      <c r="E18" s="3">
         <v>-84700</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-60400</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-63600</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-52400</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-46100</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-50100</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-28800</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-41100</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-42200</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-36900</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-29200</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-37500</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-48600</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-64500</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-57400</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-51700</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-37600</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-25000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-49200</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-21600</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>-37000</v>
       </c>
-      <c r="Y18" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z18" s="3" t="s">
         <v>3</v>
       </c>
@@ -1678,8 +1708,11 @@
       <c r="AF18" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG18" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1712,77 +1745,78 @@
       <c r="AD19" s="3"/>
       <c r="AE19" s="3"/>
       <c r="AF19" s="3"/>
-    </row>
-    <row r="20" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG19" s="3"/>
+    </row>
+    <row r="20" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-601900</v>
+      </c>
+      <c r="E20" s="3">
         <v>28500</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>569000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>135000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-80000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>248300</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>281100</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>58900</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-3600</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-9600</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-62200</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>75500</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>13100</v>
-      </c>
-      <c r="P20" s="3">
-        <v>-400</v>
       </c>
       <c r="Q20" s="3">
         <v>-400</v>
       </c>
       <c r="R20" s="3">
+        <v>-400</v>
+      </c>
+      <c r="S20" s="3">
         <v>3600</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>8400</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>8300</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>10700</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-4700</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>200</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-5900</v>
       </c>
-      <c r="Y20" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z20" s="3" t="s">
         <v>3</v>
       </c>
@@ -1804,74 +1838,77 @@
       <c r="AF20" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG20" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>528000</v>
+      </c>
+      <c r="E21" s="3">
         <v>-107900</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-626100</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-195700</v>
       </c>
-      <c r="G21" s="3">
-        <v>30200</v>
-      </c>
       <c r="H21" s="3">
+        <v>30300</v>
+      </c>
+      <c r="I21" s="3">
         <v>-291700</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-328600</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-86300</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-36300</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-30200</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>27500</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-102200</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>-47900</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-46000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-63300</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>-52500</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-42300</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-28500</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-13700</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>-53300</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>-21000</v>
       </c>
-      <c r="X21" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y21" s="3" t="s">
         <v>3</v>
       </c>
@@ -1896,77 +1933,80 @@
       <c r="AF21" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="22" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG21" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>12200</v>
+      </c>
+      <c r="E22" s="3">
         <v>12000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>4800</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>6600</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
+        <v>6800</v>
+      </c>
+      <c r="I22" s="3">
         <v>5900</v>
       </c>
-      <c r="H22" s="3">
-        <v>5900</v>
-      </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>5400</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>8400</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>9100</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>8600</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>9400</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>19600</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>18600</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>7600</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>5700</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>2900</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>2500</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>1300</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>3700</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>200</v>
       </c>
-      <c r="W22" s="3">
-        <v>0</v>
-      </c>
       <c r="X22" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y22" s="3">
         <v>23800</v>
       </c>
-      <c r="Y22" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z22" s="3" t="s">
         <v>3</v>
       </c>
@@ -1982,91 +2022,94 @@
       <c r="AD22" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AE22" s="3">
-        <v>0</v>
+      <c r="AE22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AF22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>508900</v>
+      </c>
+      <c r="E23" s="3">
         <v>-120400</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-641400</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-222900</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>15100</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-268100</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-342900</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-28200</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-46700</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-41200</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>14900</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-131600</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-71600</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-56600</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-70600</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-56700</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-45800</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-30600</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-18100</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-54000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-21500</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-66700</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-2000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-100</v>
       </c>
-      <c r="AA23" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB23" s="3" t="s">
-        <v>3</v>
+      <c r="AB23" s="3">
+        <v>0</v>
       </c>
       <c r="AC23" s="3" t="s">
         <v>3</v>
@@ -2080,8 +2123,11 @@
       <c r="AF23" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG23" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -2125,16 +2171,16 @@
         <v>0</v>
       </c>
       <c r="Q24" s="3">
+        <v>0</v>
+      </c>
+      <c r="R24" s="3">
         <v>100</v>
       </c>
-      <c r="R24" s="3">
-        <v>0</v>
-      </c>
       <c r="S24" s="3">
         <v>0</v>
       </c>
-      <c r="T24" s="3" t="s">
-        <v>3</v>
+      <c r="T24" s="3">
+        <v>0</v>
       </c>
       <c r="U24" s="3" t="s">
         <v>3</v>
@@ -2151,8 +2197,8 @@
       <c r="Y24" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Z24" s="3">
-        <v>0</v>
+      <c r="Z24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AA24" s="3">
         <v>0</v>
@@ -2172,8 +2218,11 @@
       <c r="AF24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2264,85 +2313,88 @@
       <c r="AF25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>508900</v>
+      </c>
+      <c r="E26" s="3">
         <v>-120500</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-641400</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-222900</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>15100</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-268100</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-342900</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-28200</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-46700</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-41200</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>14900</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-131600</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-71600</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-56600</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-70700</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-56700</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-45800</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-30600</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-18100</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-54000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-21500</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-66700</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-2000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-100</v>
       </c>
-      <c r="AA26" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB26" s="3" t="s">
-        <v>3</v>
+      <c r="AB26" s="3">
+        <v>0</v>
       </c>
       <c r="AC26" s="3" t="s">
         <v>3</v>
@@ -2356,85 +2408,88 @@
       <c r="AF26" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG26" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>826600</v>
+      </c>
+      <c r="E27" s="3">
         <v>-258600</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-1332500</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-248800</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>95100</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-481500</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-384100</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-51800</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-46700</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-41200</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>14900</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-131600</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-71600</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-56600</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-70700</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-56700</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-45800</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-30600</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-18100</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-54000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-21500</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-66700</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-2000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-100</v>
       </c>
-      <c r="AA27" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB27" s="3" t="s">
-        <v>3</v>
+      <c r="AB27" s="3">
+        <v>0</v>
       </c>
       <c r="AC27" s="3" t="s">
         <v>3</v>
@@ -2448,8 +2503,11 @@
       <c r="AF27" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG27" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2540,8 +2598,11 @@
       <c r="AF28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2632,8 +2693,11 @@
       <c r="AF29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2724,8 +2788,11 @@
       <c r="AF30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2816,77 +2883,80 @@
       <c r="AF31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>601900</v>
+      </c>
+      <c r="E32" s="3">
         <v>-28500</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-569000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-135000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>80000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-248300</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-281100</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-58900</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>3600</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>9600</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>62200</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-75500</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-13100</v>
-      </c>
-      <c r="P32" s="3">
-        <v>400</v>
       </c>
       <c r="Q32" s="3">
         <v>400</v>
       </c>
       <c r="R32" s="3">
+        <v>400</v>
+      </c>
+      <c r="S32" s="3">
         <v>-3600</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-8400</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-8300</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-10700</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>4700</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-200</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>5900</v>
       </c>
-      <c r="Y32" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z32" s="3" t="s">
         <v>3</v>
       </c>
@@ -2908,85 +2978,88 @@
       <c r="AF32" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG32" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>508900</v>
+      </c>
+      <c r="E33" s="3">
         <v>-120500</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-641400</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-222900</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>15100</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-268100</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-342900</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-28200</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-46700</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-41200</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>14900</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-131600</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-71600</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-56600</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-70700</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-56700</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-45800</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-30600</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-18100</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-54000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-21500</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-66700</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-2000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-100</v>
       </c>
-      <c r="AA33" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB33" s="3" t="s">
-        <v>3</v>
+      <c r="AB33" s="3">
+        <v>0</v>
       </c>
       <c r="AC33" s="3" t="s">
         <v>3</v>
@@ -3000,8 +3073,11 @@
       <c r="AF33" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG33" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3092,85 +3168,88 @@
       <c r="AF34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>508900</v>
+      </c>
+      <c r="E35" s="3">
         <v>-120500</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-641400</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-222900</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>15100</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-268100</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-342900</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-28200</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-46700</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-41200</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>14900</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-131600</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-71600</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-56600</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-70700</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-56700</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-45800</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-30600</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-18100</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-54000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-21500</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-66700</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-2000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-100</v>
       </c>
-      <c r="AA35" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB35" s="3" t="s">
-        <v>3</v>
+      <c r="AB35" s="3">
+        <v>0</v>
       </c>
       <c r="AC35" s="3" t="s">
         <v>3</v>
@@ -3184,91 +3263,94 @@
       <c r="AF35" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG35" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E38" s="2">
         <v>46022</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45930</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45838</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45747</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45657</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45565</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45473</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45382</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45291</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45199</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45107</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45016</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44926</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44834</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44742</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44651</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44561</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44469</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44377</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44286</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44196</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44104</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>44012</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43921</v>
       </c>
-      <c r="AB38" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AC38" s="2" t="s">
         <v>3</v>
       </c>
@@ -3281,8 +3363,11 @@
       <c r="AF38" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="39" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG38" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3315,8 +3400,9 @@
       <c r="AD39" s="3"/>
       <c r="AE39" s="3"/>
       <c r="AF39" s="3"/>
-    </row>
-    <row r="40" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG39" s="3"/>
+    </row>
+    <row r="40" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3349,85 +3435,86 @@
       <c r="AD40" s="3"/>
       <c r="AE40" s="3"/>
       <c r="AF40" s="3"/>
-    </row>
-    <row r="41" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG40" s="3"/>
+    </row>
+    <row r="41" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>410700</v>
+      </c>
+      <c r="E41" s="3">
         <v>568000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>58700</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>120200</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>82600</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>74300</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>23000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>52500</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>31800</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>69500</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>58000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>23200</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>16100</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>17100</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>38400</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>16300</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>55400</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>104800</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>144200</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>74700</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>100700</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>121900</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>300</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>500</v>
       </c>
-      <c r="AA41" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB41" s="3" t="s">
-        <v>3</v>
+      <c r="AB41" s="3">
+        <v>0</v>
       </c>
       <c r="AC41" s="3" t="s">
         <v>3</v>
@@ -3441,8 +3528,11 @@
       <c r="AF41" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG41" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3533,85 +3623,88 @@
       <c r="AF42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>64600</v>
+      </c>
+      <c r="E43" s="3">
         <v>31800</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>29000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>24400</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>24300</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>40100</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>82600</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>100800</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>27300</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>20500</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>4300</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>3900</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>7800</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>3600</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>6400</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>3600</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>3700</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>2000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>2400</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>400</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>300</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>100</v>
       </c>
-      <c r="Y43" s="3">
-        <v>0</v>
-      </c>
       <c r="Z43" s="3">
         <v>0</v>
       </c>
       <c r="AA43" s="3">
         <v>0</v>
       </c>
-      <c r="AB43" s="3" t="s">
-        <v>3</v>
+      <c r="AB43" s="3">
+        <v>0</v>
       </c>
       <c r="AC43" s="3" t="s">
         <v>3</v>
@@ -3625,77 +3718,80 @@
       <c r="AF43" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="44" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG43" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>58700</v>
+      </c>
+      <c r="E44" s="3">
         <v>59000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>47600</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>41100</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>40300</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>32800</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>25900</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>17800</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>14400</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>17100</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>20600</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>16600</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>14100</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>23300</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>23200</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>12900</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>10300</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>13000</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>5000</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>4400</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>100</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>200</v>
       </c>
-      <c r="Y44" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z44" s="3" t="s">
         <v>3</v>
       </c>
@@ -3711,89 +3807,92 @@
       <c r="AD44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AE44" s="3">
-        <v>0</v>
+      <c r="AE44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AF44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>12800</v>
+      </c>
+      <c r="E45" s="3">
         <v>12300</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>14100</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>12600</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>22900</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>17600</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>13900</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>8600</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>9600</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>10700</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>21400</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>15500</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>7400</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>11300</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>13600</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>27600</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>26800</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>22700</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>17400</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>12200</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>6200</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>5200</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>200</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>300</v>
       </c>
-      <c r="AA45" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AB45" s="3" t="s">
         <v>3</v>
       </c>
@@ -3809,85 +3908,88 @@
       <c r="AF45" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="46" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG45" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="46" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>590000</v>
+      </c>
+      <c r="E46" s="3">
         <v>708500</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>188700</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>232300</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>185500</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>179900</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>149200</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>183500</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>87000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>122300</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>108500</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>64000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>50000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>55100</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>81600</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>60500</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>96200</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>142600</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>169100</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>91700</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>107400</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>127400</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>600</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>800</v>
       </c>
-      <c r="AA46" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB46" s="3" t="s">
-        <v>3</v>
+      <c r="AB46" s="3">
+        <v>0</v>
       </c>
       <c r="AC46" s="3" t="s">
         <v>3</v>
@@ -3901,8 +4003,11 @@
       <c r="AF46" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG46" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="47" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3942,36 +4047,36 @@
       <c r="O47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P47" s="3">
+      <c r="P47" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q47" s="3">
         <v>800</v>
-      </c>
-      <c r="Q47" s="3">
-        <v>3700</v>
       </c>
       <c r="R47" s="3">
         <v>3700</v>
       </c>
       <c r="S47" s="3">
-        <v>3500</v>
+        <v>3700</v>
       </c>
       <c r="T47" s="3">
         <v>3500</v>
       </c>
       <c r="U47" s="3">
+        <v>3500</v>
+      </c>
+      <c r="V47" s="3">
         <v>4700</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>4100</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>11100</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>3700</v>
       </c>
-      <c r="Y47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z47" s="3" t="s">
         <v>3</v>
       </c>
@@ -3987,83 +4092,86 @@
       <c r="AD47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AE47" s="3">
-        <v>0</v>
+      <c r="AE47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AF47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>167200</v>
+      </c>
+      <c r="E48" s="3">
         <v>134800</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>88300</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>78200</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>46500</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>48600</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>54600</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>54000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>46500</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>41900</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>24300</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>23900</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>28700</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>31500</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>34400</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>25800</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>19500</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>16400</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>10300</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>8400</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>8000</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>5700</v>
       </c>
-      <c r="Y48" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z48" s="3" t="s">
         <v>3</v>
       </c>
@@ -4079,31 +4187,34 @@
       <c r="AD48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AE48" s="3">
-        <v>0</v>
+      <c r="AE48" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AF48" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="49" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG48" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>5600</v>
+      </c>
+      <c r="E49" s="3">
         <v>5300</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>5400</v>
-      </c>
-      <c r="F49" s="3">
-        <v>4500</v>
       </c>
       <c r="G49" s="3">
         <v>4500</v>
       </c>
       <c r="H49" s="3">
-        <v>4600</v>
+        <v>4500</v>
       </c>
       <c r="I49" s="3">
         <v>4600</v>
@@ -4121,13 +4232,13 @@
         <v>4600</v>
       </c>
       <c r="N49" s="3">
-        <v>4700</v>
+        <v>4600</v>
       </c>
       <c r="O49" s="3">
         <v>4700</v>
       </c>
       <c r="P49" s="3">
-        <v>4600</v>
+        <v>4700</v>
       </c>
       <c r="Q49" s="3">
         <v>4600</v>
@@ -4148,13 +4259,13 @@
         <v>4600</v>
       </c>
       <c r="W49" s="3">
-        <v>300</v>
+        <v>4600</v>
       </c>
       <c r="X49" s="3">
         <v>300</v>
       </c>
-      <c r="Y49" s="3" t="s">
-        <v>3</v>
+      <c r="Y49" s="3">
+        <v>300</v>
       </c>
       <c r="Z49" s="3" t="s">
         <v>3</v>
@@ -4171,14 +4282,17 @@
       <c r="AD49" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AE49" s="3">
-        <v>0</v>
+      <c r="AE49" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AF49" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG49" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4269,8 +4383,11 @@
       <c r="AF50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4361,86 +4478,89 @@
       <c r="AF51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>36500</v>
+      </c>
+      <c r="E52" s="3">
         <v>35100</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>45700</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>46000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>26700</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>26300</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>7300</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>4900</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>17600</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>15700</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>15900</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>15600</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>15500</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>14800</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>14200</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>3200</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>3100</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>2100</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>1400</v>
-      </c>
-      <c r="V52" s="3">
-        <v>1000</v>
       </c>
       <c r="W52" s="3">
         <v>1000</v>
       </c>
       <c r="X52" s="3">
+        <v>1000</v>
+      </c>
+      <c r="Y52" s="3">
         <v>1200</v>
-      </c>
-      <c r="Y52" s="3">
-        <v>176800</v>
       </c>
       <c r="Z52" s="3">
         <v>176800</v>
       </c>
       <c r="AA52" s="3">
+        <v>176800</v>
+      </c>
+      <c r="AB52" s="3">
         <v>100</v>
       </c>
-      <c r="AB52" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC52" s="3" t="s">
         <v>3</v>
       </c>
@@ -4453,8 +4573,11 @@
       <c r="AF52" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="53" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG52" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4545,86 +4668,89 @@
       <c r="AF53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>799300</v>
+      </c>
+      <c r="E54" s="3">
         <v>885200</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>328200</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>361000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>263300</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>260300</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>216800</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>248800</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>155700</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>186500</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>154100</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>109000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>99700</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>106800</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>138500</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>97700</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>126900</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>169200</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>190100</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>109900</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>127800</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>138300</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>177300</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>177500</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>100</v>
       </c>
-      <c r="AB54" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC54" s="3" t="s">
         <v>3</v>
       </c>
@@ -4637,8 +4763,11 @@
       <c r="AF54" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="55" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG54" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4671,8 +4800,9 @@
       <c r="AD55" s="3"/>
       <c r="AE55" s="3"/>
       <c r="AF55" s="3"/>
-    </row>
-    <row r="56" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG55" s="3"/>
+    </row>
+    <row r="56" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4705,85 +4835,86 @@
       <c r="AD56" s="3"/>
       <c r="AE56" s="3"/>
       <c r="AF56" s="3"/>
-    </row>
-    <row r="57" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG56" s="3"/>
+    </row>
+    <row r="57" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>77100</v>
+      </c>
+      <c r="E57" s="3">
         <v>99900</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>51600</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>39700</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>24300</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>16700</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>24300</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>24100</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>18300</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>20500</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>13800</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>15400</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>32500</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>34700</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>35500</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>29100</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>11700</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>13700</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>13200</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>15200</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>20200</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>11400</v>
       </c>
-      <c r="Y57" s="3">
-        <v>0</v>
-      </c>
       <c r="Z57" s="3">
         <v>0</v>
       </c>
       <c r="AA57" s="3">
         <v>0</v>
       </c>
-      <c r="AB57" s="3" t="s">
-        <v>3</v>
+      <c r="AB57" s="3">
+        <v>0</v>
       </c>
       <c r="AC57" s="3" t="s">
         <v>3</v>
@@ -4797,86 +4928,89 @@
       <c r="AF57" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="58" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG57" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>2000</v>
+      </c>
+      <c r="E58" s="3">
         <v>2400</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>2900</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>3300</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>3400</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>3900</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>4300</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>5500</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>5100</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>4900</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>4600</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>4400</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>12400</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>5600</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>2900</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>14000</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>6700</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>6600</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>6500</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>6100</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>1200</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>1100</v>
       </c>
-      <c r="Y58" s="3">
-        <v>0</v>
-      </c>
       <c r="Z58" s="3">
         <v>0</v>
       </c>
       <c r="AA58" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB58" s="3">
         <v>100</v>
       </c>
-      <c r="AB58" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC58" s="3" t="s">
         <v>3</v>
       </c>
@@ -4889,82 +5023,85 @@
       <c r="AF58" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="59" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG58" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>29600</v>
+      </c>
+      <c r="E59" s="3">
         <v>31000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>28700</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>47300</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>50500</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>32100</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>17100</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>13500</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>11500</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>12600</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>13000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>9000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>6300</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>20300</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>17500</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>16600</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>15500</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>9600</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>1200</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>3400</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>800</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>1700</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>1800</v>
       </c>
-      <c r="Z59" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA59" s="3" t="s">
-        <v>3</v>
+      <c r="AA59" s="3">
+        <v>0</v>
       </c>
       <c r="AB59" s="3" t="s">
         <v>3</v>
@@ -4981,85 +5118,88 @@
       <c r="AF59" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="60" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG59" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>125300</v>
+      </c>
+      <c r="E60" s="3">
         <v>143500</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>103400</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>104300</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>90700</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>65000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>75100</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>68500</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>64900</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>60900</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>46800</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>43000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>65700</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>60600</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>55800</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>59600</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>33800</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>29900</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>20900</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>24600</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>22200</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>14100</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>1900</v>
-      </c>
-      <c r="Z60" s="3">
-        <v>100</v>
       </c>
       <c r="AA60" s="3">
         <v>100</v>
       </c>
-      <c r="AB60" s="3" t="s">
-        <v>3</v>
+      <c r="AB60" s="3">
+        <v>100</v>
       </c>
       <c r="AC60" s="3" t="s">
         <v>3</v>
@@ -5073,77 +5213,80 @@
       <c r="AF60" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="61" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG60" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="61" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>640900</v>
+      </c>
+      <c r="E61" s="3">
         <v>832300</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>448100</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>445100</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>325200</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>316600</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>186900</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>152700</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>205100</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>204000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>207500</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>233300</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>202400</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>170400</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>160800</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>90300</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>95300</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>102700</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>106800</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>13500</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>100</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>300</v>
       </c>
-      <c r="Y61" s="3">
-        <v>0</v>
-      </c>
       <c r="Z61" s="3">
         <v>0</v>
       </c>
@@ -5165,77 +5308,80 @@
       <c r="AF61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>316700</v>
+      </c>
+      <c r="E62" s="3">
         <v>784200</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>871300</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>380300</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>274900</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>456200</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>369200</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>173900</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>29100</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>28900</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>27100</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>61200</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>6300</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>8500</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>10100</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>5700</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>8000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>4200</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>3900</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>3100</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>3700</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>800</v>
       </c>
-      <c r="Y62" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Z62" s="3" t="s">
         <v>3</v>
       </c>
@@ -5251,14 +5397,17 @@
       <c r="AD62" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AE62" s="3">
-        <v>0</v>
+      <c r="AE62" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AF62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5349,8 +5498,11 @@
       <c r="AF63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5441,8 +5593,11 @@
       <c r="AF64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5533,85 +5688,88 @@
       <c r="AF65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>1085100</v>
+      </c>
+      <c r="E66" s="3">
         <v>1762500</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>1425200</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>931700</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>694600</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>842100</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>634500</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>399500</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>303400</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>297300</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>282400</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>338500</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>275300</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>239500</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>226800</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>155600</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>137100</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>136700</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>131700</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>41300</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>26000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>15200</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>1900</v>
-      </c>
-      <c r="Z66" s="3">
-        <v>100</v>
       </c>
       <c r="AA66" s="3">
         <v>100</v>
       </c>
-      <c r="AB66" s="3" t="s">
-        <v>3</v>
+      <c r="AB66" s="3">
+        <v>100</v>
       </c>
       <c r="AC66" s="3" t="s">
         <v>3</v>
@@ -5625,8 +5783,11 @@
       <c r="AF66" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="67" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG66" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="67" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5659,8 +5820,9 @@
       <c r="AD67" s="3"/>
       <c r="AE67" s="3"/>
       <c r="AF67" s="3"/>
-    </row>
-    <row r="68" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG67" s="3"/>
+    </row>
+    <row r="68" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5751,8 +5913,11 @@
       <c r="AF68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5843,35 +6008,38 @@
       <c r="AF69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
       <c r="D70" s="3">
+        <v>582700</v>
+      </c>
+      <c r="E70" s="3">
         <v>1361500</v>
       </c>
-      <c r="E70" s="3">
+      <c r="F70" s="3">
         <v>1223400</v>
       </c>
-      <c r="F70" s="3">
+      <c r="G70" s="3">
         <v>532300</v>
       </c>
-      <c r="G70" s="3">
+      <c r="H70" s="3">
         <v>510900</v>
       </c>
-      <c r="H70" s="3">
+      <c r="I70" s="3">
         <v>488700</v>
       </c>
-      <c r="I70" s="3">
+      <c r="J70" s="3">
         <v>156100</v>
       </c>
-      <c r="J70" s="3">
+      <c r="K70" s="3">
         <v>40100</v>
       </c>
-      <c r="K70" s="3">
-        <v>0</v>
-      </c>
       <c r="L70" s="3">
         <v>0</v>
       </c>
@@ -5935,8 +6103,11 @@
       <c r="AF70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6027,85 +6198,88 @@
       <c r="AF71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-2026900</v>
+      </c>
+      <c r="E72" s="3">
         <v>-2535800</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-2415400</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-1774000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-1546600</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-1561700</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-1293600</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-950700</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-922600</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-875800</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-834600</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-849600</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-717900</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-646300</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-589700</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-519000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-462300</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-416500</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-385900</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-367800</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-313800</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-290800</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-2000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-100</v>
       </c>
-      <c r="AA72" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB72" s="3" t="s">
-        <v>3</v>
+      <c r="AB72" s="3">
+        <v>0</v>
       </c>
       <c r="AC72" s="3" t="s">
         <v>3</v>
@@ -6119,8 +6293,11 @@
       <c r="AF72" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG72" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="73" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6211,8 +6388,11 @@
       <c r="AF73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6303,8 +6483,11 @@
       <c r="AF74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6395,85 +6578,88 @@
       <c r="AF75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>-868400</v>
+      </c>
+      <c r="E76" s="3">
         <v>-2238900</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>-2320400</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>-1103000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>-942200</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>-1070500</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>-573800</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>-190800</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>-147700</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>-110800</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>-128300</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>-229500</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>-175600</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>-132700</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>-88300</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>-57800</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>-10200</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>32400</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>58400</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>68600</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>101800</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>123100</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>175500</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>177400</v>
       </c>
-      <c r="AA76" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB76" s="3" t="s">
-        <v>3</v>
+      <c r="AB76" s="3">
+        <v>0</v>
       </c>
       <c r="AC76" s="3" t="s">
         <v>3</v>
@@ -6487,8 +6673,11 @@
       <c r="AF76" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="77" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG76" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="77" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6579,91 +6768,94 @@
       <c r="AF77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E80" s="2">
         <v>46022</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45930</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45838</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45747</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45657</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45565</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45473</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45382</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45291</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45199</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45107</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45016</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44926</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44834</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44742</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44651</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44561</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44469</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44377</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44286</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44196</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44104</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>44012</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43921</v>
       </c>
-      <c r="AB80" s="2" t="s">
-        <v>3</v>
-      </c>
       <c r="AC80" s="2" t="s">
         <v>3</v>
       </c>
@@ -6676,85 +6868,88 @@
       <c r="AF80" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="81" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG80" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="81" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>508900</v>
+      </c>
+      <c r="E81" s="3">
         <v>-120500</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-641400</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-222900</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>15100</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-268100</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-342900</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-28200</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-46700</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-41200</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>14900</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-131600</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-71600</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-56600</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-70700</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-56700</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-45800</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-30600</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-18100</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-54000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-21500</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-66700</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-2000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-100</v>
       </c>
-      <c r="AA81" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB81" s="3" t="s">
-        <v>3</v>
+      <c r="AB81" s="3">
+        <v>0</v>
       </c>
       <c r="AC81" s="3" t="s">
         <v>3</v>
@@ -6768,8 +6963,11 @@
       <c r="AF81" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="82" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG81" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6802,74 +7000,75 @@
       <c r="AD82" s="3"/>
       <c r="AE82" s="3"/>
       <c r="AF82" s="3"/>
-    </row>
-    <row r="83" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG82" s="3"/>
+    </row>
+    <row r="83" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>3000</v>
+      </c>
+      <c r="E83" s="3">
         <v>2900</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>3000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>1700</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>1500</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>2700</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>2400</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>2700</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>2900</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>3200</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>1800</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>1500</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>1200</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>3000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>1600</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>1300</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>1000</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>800</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>700</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>600</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>500</v>
       </c>
-      <c r="X83" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y83" s="3" t="s">
         <v>3</v>
       </c>
@@ -6885,8 +7084,8 @@
       <c r="AC83" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AD83" s="3">
-        <v>0</v>
+      <c r="AD83" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AE83" s="3">
         <v>0</v>
@@ -6894,8 +7093,11 @@
       <c r="AF83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6986,8 +7188,11 @@
       <c r="AF84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7078,8 +7283,11 @@
       <c r="AF85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7170,8 +7378,11 @@
       <c r="AF86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7262,8 +7473,11 @@
       <c r="AF87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7354,85 +7568,88 @@
       <c r="AF88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-119700</v>
+      </c>
+      <c r="E89" s="3">
         <v>-50300</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-65900</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-66100</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-28900</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-42700</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-44400</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-26300</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-40500</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-37400</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-32000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-45100</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-30500</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-37700</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-72100</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-44300</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-42700</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-35500</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-31700</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-39200</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-9700</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-26100</v>
-      </c>
-      <c r="Y89" s="3">
-        <v>-200</v>
       </c>
       <c r="Z89" s="3">
         <v>-200</v>
       </c>
       <c r="AA89" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB89" s="3" t="s">
-        <v>3</v>
+        <v>-200</v>
+      </c>
+      <c r="AB89" s="3">
+        <v>0</v>
       </c>
       <c r="AC89" s="3" t="s">
         <v>3</v>
@@ -7446,8 +7663,11 @@
       <c r="AF89" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="90" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG89" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="90" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7480,74 +7700,75 @@
       <c r="AD90" s="3"/>
       <c r="AE90" s="3"/>
       <c r="AF90" s="3"/>
-    </row>
-    <row r="91" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG90" s="3"/>
+    </row>
+    <row r="91" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-35100</v>
+      </c>
+      <c r="E91" s="3">
         <v>-25000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-16800</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-7000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-4900</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-13100</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-9800</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-6200</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-4000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-8100</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-11100</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-7200</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-2900</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-1300</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-7300</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-6400</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-5100</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-4200</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-3800</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-3100</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-4500</v>
       </c>
-      <c r="X91" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="Y91" s="3" t="s">
         <v>3</v>
       </c>
@@ -7563,8 +7784,8 @@
       <c r="AC91" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AD91" s="3">
-        <v>0</v>
+      <c r="AD91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AE91" s="3">
         <v>0</v>
@@ -7572,8 +7793,11 @@
       <c r="AF91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7664,8 +7888,11 @@
       <c r="AF92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7756,79 +7983,82 @@
       <c r="AF93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-35100</v>
+      </c>
+      <c r="E94" s="3">
         <v>-25000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-17800</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-7000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-4900</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-13100</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-9800</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-6300</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-4000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-8300</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-11100</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-7200</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-2900</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>1900</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-7300</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-6600</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-5100</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-3100</v>
-      </c>
-      <c r="U94" s="3">
-        <v>-4400</v>
       </c>
       <c r="V94" s="3">
         <v>-4400</v>
       </c>
       <c r="W94" s="3">
+        <v>-4400</v>
+      </c>
+      <c r="X94" s="3">
         <v>-11400</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>170100</v>
       </c>
-      <c r="Y94" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z94" s="3" t="s">
-        <v>3</v>
+      <c r="Z94" s="3">
+        <v>0</v>
       </c>
       <c r="AA94" s="3" t="s">
         <v>3</v>
@@ -7842,14 +8072,17 @@
       <c r="AD94" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="AE94" s="3">
-        <v>0</v>
+      <c r="AE94" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="AF94" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="95" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG94" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7882,8 +8115,9 @@
       <c r="AD95" s="3"/>
       <c r="AE95" s="3"/>
       <c r="AF95" s="3"/>
-    </row>
-    <row r="96" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG95" s="3"/>
+    </row>
+    <row r="96" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7923,8 +8157,8 @@
       <c r="O96" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P96" s="3">
-        <v>0</v>
+      <c r="P96" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q96" s="3">
         <v>0</v>
@@ -7974,8 +8208,11 @@
       <c r="AF96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8066,8 +8303,11 @@
       <c r="AF97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8158,8 +8398,11 @@
       <c r="AF98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8250,86 +8493,89 @@
       <c r="AF99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>2700</v>
+      </c>
+      <c r="E100" s="3">
         <v>573000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>27300</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>144700</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>42200</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>128500</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>27300</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>43900</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>6100</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>57300</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>78000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>60200</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>32500</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>16000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>112900</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>11800</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-1200</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-400</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>106200</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>17600</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-100</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-23300</v>
       </c>
-      <c r="Y100" s="3">
-        <v>0</v>
-      </c>
       <c r="Z100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA100" s="3">
         <v>177500</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>100</v>
       </c>
-      <c r="AB100" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="AC100" s="3" t="s">
         <v>3</v>
       </c>
@@ -8342,8 +8588,11 @@
       <c r="AF100" s="3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="101" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG100" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -8380,17 +8629,17 @@
       <c r="N101" s="3">
         <v>0</v>
       </c>
-      <c r="O101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P101" s="3">
-        <v>0</v>
+      <c r="O101" s="3">
+        <v>0</v>
+      </c>
+      <c r="P101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q101" s="3">
         <v>0</v>
       </c>
-      <c r="R101" s="3" t="s">
-        <v>3</v>
+      <c r="R101" s="3">
+        <v>0</v>
       </c>
       <c r="S101" s="3" t="s">
         <v>3</v>
@@ -8407,8 +8656,8 @@
       <c r="W101" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="X101" s="3">
-        <v>0</v>
+      <c r="X101" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Y101" s="3">
         <v>0</v>
@@ -8434,85 +8683,88 @@
       <c r="AF101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-152200</v>
+      </c>
+      <c r="E102" s="3">
         <v>497800</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-56400</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>71500</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>8300</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>72700</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-26900</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>11300</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-38400</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>11600</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>34900</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>7900</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-900</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-19800</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>33500</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-39100</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-49100</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-39000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>70000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-26000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-21100</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>120700</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-200</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>500</v>
       </c>
-      <c r="AA102" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB102" s="3" t="s">
-        <v>3</v>
+      <c r="AB102" s="3">
+        <v>0</v>
       </c>
       <c r="AC102" s="3" t="s">
         <v>3</v>
@@ -8524,6 +8776,9 @@
         <v>3</v>
       </c>
       <c r="AF102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="AG102" s="3" t="s">
         <v>3</v>
       </c>
     </row>
